--- a/design/runes-workbook.xlsx
+++ b/design/runes-workbook.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Code\lifesteal-crawler\design\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABB16B55-4B22-4F59-8175-B2EFEA02C327}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8CD343A-0BDF-4F02-AB73-3F3F09B3BA9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Read Me" sheetId="1" r:id="rId1"/>
@@ -18,26 +18,27 @@
     <sheet name="Alignment" sheetId="22" r:id="rId3"/>
     <sheet name="Base Runes" sheetId="3" r:id="rId4"/>
     <sheet name="Universal Runes" sheetId="4" r:id="rId5"/>
-    <sheet name="Water" sheetId="5" r:id="rId6"/>
-    <sheet name="Fire" sheetId="6" r:id="rId7"/>
-    <sheet name="Earth" sheetId="7" r:id="rId8"/>
-    <sheet name="Wind" sheetId="8" r:id="rId9"/>
-    <sheet name="Lightning" sheetId="9" r:id="rId10"/>
-    <sheet name="Ice" sheetId="10" r:id="rId11"/>
-    <sheet name="Dark" sheetId="11" r:id="rId12"/>
-    <sheet name="Metal" sheetId="12" r:id="rId13"/>
-    <sheet name="Blood" sheetId="13" r:id="rId14"/>
-    <sheet name="Life" sheetId="14" r:id="rId15"/>
-    <sheet name="Death" sheetId="15" r:id="rId16"/>
-    <sheet name="Nature" sheetId="16" r:id="rId17"/>
-    <sheet name="Light" sheetId="17" r:id="rId18"/>
-    <sheet name="Dream" sheetId="18" r:id="rId19"/>
-    <sheet name="Poison" sheetId="19" r:id="rId20"/>
-    <sheet name="Disease" sheetId="20" r:id="rId21"/>
-    <sheet name="Slider Links" sheetId="21" r:id="rId22"/>
+    <sheet name="Bond Rules" sheetId="23" r:id="rId6"/>
+    <sheet name="Water" sheetId="5" r:id="rId7"/>
+    <sheet name="Fire" sheetId="6" r:id="rId8"/>
+    <sheet name="Earth" sheetId="7" r:id="rId9"/>
+    <sheet name="Wind" sheetId="8" r:id="rId10"/>
+    <sheet name="Lightning" sheetId="9" r:id="rId11"/>
+    <sheet name="Ice" sheetId="10" r:id="rId12"/>
+    <sheet name="Dark" sheetId="11" r:id="rId13"/>
+    <sheet name="Metal" sheetId="12" r:id="rId14"/>
+    <sheet name="Blood" sheetId="13" r:id="rId15"/>
+    <sheet name="Life" sheetId="14" r:id="rId16"/>
+    <sheet name="Death" sheetId="15" r:id="rId17"/>
+    <sheet name="Nature" sheetId="16" r:id="rId18"/>
+    <sheet name="Light" sheetId="17" r:id="rId19"/>
+    <sheet name="Dream" sheetId="18" r:id="rId20"/>
+    <sheet name="Poison" sheetId="19" r:id="rId21"/>
+    <sheet name="Disease" sheetId="20" r:id="rId22"/>
+    <sheet name="Slider Links" sheetId="21" r:id="rId23"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Base Runes'!$A$1:$J$167</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Base Runes'!$A$1:$N$167</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Universal Runes'!$A$1:$G$57</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -176,7 +177,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2066" uniqueCount="1259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2268" uniqueCount="1293">
   <si>
     <t>Passage rune workbook</t>
   </si>
@@ -3953,6 +3954,108 @@
   </si>
   <si>
     <t>The sliders are Excel controls. Edit this file in Excel; regenerating it with tools/design/build_runes_workbook.py would remove them and your edits.</t>
+  </si>
+  <si>
+    <t>Bond rules</t>
+  </si>
+  <si>
+    <t>Role</t>
+  </si>
+  <si>
+    <t>Valence</t>
+  </si>
+  <si>
+    <t>Electronegativity spread</t>
+  </si>
+  <si>
+    <t>What the role means</t>
+  </si>
+  <si>
+    <t>The chemistry it mirrors</t>
+  </si>
+  <si>
+    <t>Cap</t>
+  </si>
+  <si>
+    <t>Ends a structure: a finisher, or a pure state.</t>
+  </si>
+  <si>
+    <t>Hydrogen, fluorine, sodium: one bond, and the most extreme pull or push.</t>
+  </si>
+  <si>
+    <t>Link</t>
+  </si>
+  <si>
+    <t>Takes something in and passes it on.</t>
+  </si>
+  <si>
+    <t>Oxygen: two bonds.</t>
+  </si>
+  <si>
+    <t>Branch</t>
+  </si>
+  <si>
+    <t>Spreads, splits or multiplies.</t>
+  </si>
+  <si>
+    <t>Nitrogen: three bonds.</t>
+  </si>
+  <si>
+    <t>Frame</t>
+  </si>
+  <si>
+    <t>Holds a structure together.</t>
+  </si>
+  <si>
+    <t>Carbon: four bonds and a middling pull, the backbone that bonds with almost anything.</t>
+  </si>
+  <si>
+    <t>Electronegativity centre</t>
+  </si>
+  <si>
+    <t>A rune's electronegativity = centre + draw x its role's spread. Draw runs from -1 (the rune gives or releases outward) to +1 (it takes or holds inward). Valence comes from the role. So a Cap sits at the extremes (1.0 to 4.0) and a Frame near the centre (2.1 to 2.9), as in real chemistry: the elements with the fewest bonds pull hardest or give most easily, and carbon, with four, sits in the middle and bonds with everything.</t>
+  </si>
+  <si>
+    <t>Bond kind</t>
+  </si>
+  <si>
+    <t>Difference from</t>
+  </si>
+  <si>
+    <t>What it means in a word</t>
+  </si>
+  <si>
+    <t>Even</t>
+  </si>
+  <si>
+    <t>The two runes blend equally.</t>
+  </si>
+  <si>
+    <t>Polar</t>
+  </si>
+  <si>
+    <t>The rune with more pull dominates; the other colours it.</t>
+  </si>
+  <si>
+    <t>Ionic</t>
+  </si>
+  <si>
+    <t>One rune hands its effect to the other outright: a transfer.</t>
+  </si>
+  <si>
+    <t>Single bonds only, no handedness (Brent, 2026-10-22). Bond strength (Pauling: the bigger the difference, the stronger the bond) and how affinity alignment multiplies it are not given numbers yet.</t>
+  </si>
+  <si>
+    <t>Draw (-1 gives ... +1 takes)</t>
+  </si>
+  <si>
+    <t>Electronegativity</t>
+  </si>
+  <si>
+    <t>Valence and electronegativity (added 2026-10-22)</t>
+  </si>
+  <si>
+    <t>Base Runes columns K-N. You set each rune's Role (Cap, Link, Branch, Frame) and Draw (-1 gives or releases ... +1 takes or holds); Valence and Electronegativity follow by the rules on the Bond Rules sheet, where the numbers behind them can be changed.</t>
   </si>
 </sst>
 </file>
@@ -3962,7 +4065,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="\+0.0;\-0.0;0.0"/>
   </numFmts>
-  <fonts count="27" x14ac:knownFonts="1">
+  <fonts count="30" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4118,6 +4221,26 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -4170,7 +4293,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -4280,15 +4403,49 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment textRotation="90"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -8948,7 +9105,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A29"/>
+  <dimension ref="A1:A32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="120" customWidth="1"/>
@@ -9089,12 +9246,404 @@
         <v>1258</v>
       </c>
     </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" s="46"/>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" s="55" t="s">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A32" s="46" t="s">
+        <v>1292</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <sheetPr>
+    <tabColor rgb="FF7FB8A4"/>
+  </sheetPr>
+  <dimension ref="A1:J17"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="11" customWidth="1"/>
+    <col min="5" max="6" width="46" customWidth="1"/>
+    <col min="7" max="7" width="16" customWidth="1"/>
+    <col min="8" max="8" width="40" customWidth="1"/>
+    <col min="9" max="10" width="30" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A1" s="25" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="60" t="s">
+        <v>1072</v>
+      </c>
+      <c r="B2" s="59"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
+    </row>
+    <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="58" t="s">
+        <v>1037</v>
+      </c>
+      <c r="B3" s="59"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
+    </row>
+    <row r="5" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>979</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>980</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>981</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>982</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="26">
+        <v>1</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="C6" s="27" t="str">
+        <f>IFERROR(INDEX('Base Runes'!$D:$D,MATCH($B6,'Base Runes'!$A:$A,0)),"")</f>
+        <v>Gust</v>
+      </c>
+      <c r="D6" s="28" t="str">
+        <f>IFERROR(INDEX('Base Runes'!$E:$E,MATCH($B6,'Base Runes'!$A:$A,0)),"")</f>
+        <v>ᛄ</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>1073</v>
+      </c>
+      <c r="F6" s="30"/>
+      <c r="G6" s="11" t="str">
+        <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B6,'Base Runes'!$A:$A,0)),"")</f>
+        <v>Lull</v>
+      </c>
+      <c r="H6" s="30"/>
+      <c r="I6" s="10" t="s">
+        <v>1074</v>
+      </c>
+      <c r="J6" s="10"/>
+    </row>
+    <row r="7" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="26">
+        <v>1</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="C7" s="27" t="str">
+        <f>IFERROR(INDEX('Base Runes'!$D:$D,MATCH($B7,'Base Runes'!$A:$A,0)),"")</f>
+        <v>Lull</v>
+      </c>
+      <c r="D7" s="28" t="str">
+        <f>IFERROR(INDEX('Base Runes'!$E:$E,MATCH($B7,'Base Runes'!$A:$A,0)),"")</f>
+        <v>ᛅ</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>1075</v>
+      </c>
+      <c r="F7" s="30"/>
+      <c r="G7" s="11" t="str">
+        <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B7,'Base Runes'!$A:$A,0)),"")</f>
+        <v>Gust</v>
+      </c>
+      <c r="H7" s="30"/>
+      <c r="I7" s="10"/>
+      <c r="J7" s="10"/>
+    </row>
+    <row r="8" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="26">
+        <v>2</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>243</v>
+      </c>
+      <c r="C8" s="27" t="str">
+        <f>IFERROR(INDEX('Base Runes'!$D:$D,MATCH($B8,'Base Runes'!$A:$A,0)),"")</f>
+        <v>Updraft</v>
+      </c>
+      <c r="D8" s="28" t="str">
+        <f>IFERROR(INDEX('Base Runes'!$E:$E,MATCH($B8,'Base Runes'!$A:$A,0)),"")</f>
+        <v>ᛆ</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>1076</v>
+      </c>
+      <c r="F8" s="30"/>
+      <c r="G8" s="11" t="str">
+        <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B8,'Base Runes'!$A:$A,0)),"")</f>
+        <v>Downdraft</v>
+      </c>
+      <c r="H8" s="30"/>
+      <c r="I8" s="10" t="s">
+        <v>244</v>
+      </c>
+      <c r="J8" s="10"/>
+    </row>
+    <row r="9" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="26">
+        <v>2</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>246</v>
+      </c>
+      <c r="C9" s="27" t="str">
+        <f>IFERROR(INDEX('Base Runes'!$D:$D,MATCH($B9,'Base Runes'!$A:$A,0)),"")</f>
+        <v>Downdraft</v>
+      </c>
+      <c r="D9" s="28" t="str">
+        <f>IFERROR(INDEX('Base Runes'!$E:$E,MATCH($B9,'Base Runes'!$A:$A,0)),"")</f>
+        <v>ᛇ</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>1077</v>
+      </c>
+      <c r="F9" s="30"/>
+      <c r="G9" s="11" t="str">
+        <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B9,'Base Runes'!$A:$A,0)),"")</f>
+        <v>Updraft</v>
+      </c>
+      <c r="H9" s="30"/>
+      <c r="I9" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="J9" s="10"/>
+    </row>
+    <row r="10" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="26">
+        <v>3</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="C10" s="27" t="str">
+        <f>IFERROR(INDEX('Base Runes'!$D:$D,MATCH($B10,'Base Runes'!$A:$A,0)),"")</f>
+        <v>Shear</v>
+      </c>
+      <c r="D10" s="28" t="str">
+        <f>IFERROR(INDEX('Base Runes'!$E:$E,MATCH($B10,'Base Runes'!$A:$A,0)),"")</f>
+        <v>ᛈ</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>1078</v>
+      </c>
+      <c r="F10" s="30"/>
+      <c r="G10" s="11" t="str">
+        <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B10,'Base Runes'!$A:$A,0)),"")</f>
+        <v>Buffer</v>
+      </c>
+      <c r="H10" s="30"/>
+      <c r="I10" s="10" t="s">
+        <v>1079</v>
+      </c>
+      <c r="J10" s="10"/>
+    </row>
+    <row r="11" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="26">
+        <v>3</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="C11" s="27" t="str">
+        <f>IFERROR(INDEX('Base Runes'!$D:$D,MATCH($B11,'Base Runes'!$A:$A,0)),"")</f>
+        <v>Buffer</v>
+      </c>
+      <c r="D11" s="28" t="str">
+        <f>IFERROR(INDEX('Base Runes'!$E:$E,MATCH($B11,'Base Runes'!$A:$A,0)),"")</f>
+        <v>ᛉ</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>1080</v>
+      </c>
+      <c r="F11" s="30"/>
+      <c r="G11" s="11" t="str">
+        <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B11,'Base Runes'!$A:$A,0)),"")</f>
+        <v>Shear</v>
+      </c>
+      <c r="H11" s="30"/>
+      <c r="I11" s="10" t="s">
+        <v>1081</v>
+      </c>
+      <c r="J11" s="10"/>
+    </row>
+    <row r="12" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="26">
+        <v>4</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>259</v>
+      </c>
+      <c r="C12" s="27" t="str">
+        <f>IFERROR(INDEX('Base Runes'!$D:$D,MATCH($B12,'Base Runes'!$A:$A,0)),"")</f>
+        <v>Tailwind</v>
+      </c>
+      <c r="D12" s="28" t="str">
+        <f>IFERROR(INDEX('Base Runes'!$E:$E,MATCH($B12,'Base Runes'!$A:$A,0)),"")</f>
+        <v>ᛊ</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>1082</v>
+      </c>
+      <c r="F12" s="30"/>
+      <c r="G12" s="11" t="str">
+        <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B12,'Base Runes'!$A:$A,0)),"")</f>
+        <v>Headwind</v>
+      </c>
+      <c r="H12" s="30"/>
+      <c r="I12" s="10" t="s">
+        <v>260</v>
+      </c>
+      <c r="J12" s="10"/>
+    </row>
+    <row r="13" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="26">
+        <v>4</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>262</v>
+      </c>
+      <c r="C13" s="27" t="str">
+        <f>IFERROR(INDEX('Base Runes'!$D:$D,MATCH($B13,'Base Runes'!$A:$A,0)),"")</f>
+        <v>Headwind</v>
+      </c>
+      <c r="D13" s="28" t="str">
+        <f>IFERROR(INDEX('Base Runes'!$E:$E,MATCH($B13,'Base Runes'!$A:$A,0)),"")</f>
+        <v>ᛋ</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>1083</v>
+      </c>
+      <c r="F13" s="30"/>
+      <c r="G13" s="11" t="str">
+        <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B13,'Base Runes'!$A:$A,0)),"")</f>
+        <v>Tailwind</v>
+      </c>
+      <c r="H13" s="30"/>
+      <c r="I13" s="10"/>
+      <c r="J13" s="10"/>
+    </row>
+    <row r="14" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="26">
+        <v>5</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>267</v>
+      </c>
+      <c r="C14" s="27" t="str">
+        <f>IFERROR(INDEX('Base Runes'!$D:$D,MATCH($B14,'Base Runes'!$A:$A,0)),"")</f>
+        <v>Whirl</v>
+      </c>
+      <c r="D14" s="28" t="str">
+        <f>IFERROR(INDEX('Base Runes'!$E:$E,MATCH($B14,'Base Runes'!$A:$A,0)),"")</f>
+        <v>ᛌ</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>1084</v>
+      </c>
+      <c r="F14" s="30"/>
+      <c r="G14" s="11" t="str">
+        <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B14,'Base Runes'!$A:$A,0)),"")</f>
+        <v>Disperse</v>
+      </c>
+      <c r="H14" s="30"/>
+      <c r="I14" s="10"/>
+      <c r="J14" s="10"/>
+    </row>
+    <row r="15" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="26">
+        <v>5</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="C15" s="27" t="str">
+        <f>IFERROR(INDEX('Base Runes'!$D:$D,MATCH($B15,'Base Runes'!$A:$A,0)),"")</f>
+        <v>Disperse</v>
+      </c>
+      <c r="D15" s="28" t="str">
+        <f>IFERROR(INDEX('Base Runes'!$E:$E,MATCH($B15,'Base Runes'!$A:$A,0)),"")</f>
+        <v>ᛍ</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>1085</v>
+      </c>
+      <c r="F15" s="30"/>
+      <c r="G15" s="11" t="str">
+        <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B15,'Base Runes'!$A:$A,0)),"")</f>
+        <v>Whirl</v>
+      </c>
+      <c r="H15" s="30"/>
+      <c r="I15" s="10"/>
+      <c r="J15" s="10"/>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="29" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A2:J2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <sheetPr>
     <tabColor rgb="FFE8C547"/>
@@ -9118,32 +9667,32 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="45" t="s">
+      <c r="A2" s="60" t="s">
         <v>1086</v>
       </c>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="44"/>
-      <c r="H2" s="44"/>
-      <c r="I2" s="44"/>
-      <c r="J2" s="44"/>
+      <c r="B2" s="59"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
     </row>
     <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="43" t="s">
+      <c r="A3" s="58" t="s">
         <v>1037</v>
       </c>
-      <c r="B3" s="44"/>
-      <c r="C3" s="44"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
-      <c r="G3" s="44"/>
-      <c r="H3" s="44"/>
-      <c r="I3" s="44"/>
-      <c r="J3" s="44"/>
+      <c r="B3" s="59"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
     </row>
     <row r="5" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
@@ -9471,7 +10020,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <sheetPr>
     <tabColor rgb="FFA8D8EA"/>
@@ -9495,32 +10044,32 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="45" t="s">
+      <c r="A2" s="60" t="s">
         <v>1102</v>
       </c>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="44"/>
-      <c r="H2" s="44"/>
-      <c r="I2" s="44"/>
-      <c r="J2" s="44"/>
+      <c r="B2" s="59"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
     </row>
     <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="43" t="s">
+      <c r="A3" s="58" t="s">
         <v>1103</v>
       </c>
-      <c r="B3" s="44"/>
-      <c r="C3" s="44"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
-      <c r="G3" s="44"/>
-      <c r="H3" s="44"/>
-      <c r="I3" s="44"/>
-      <c r="J3" s="44"/>
+      <c r="B3" s="59"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
     </row>
     <row r="5" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
@@ -9838,7 +10387,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <sheetPr>
     <tabColor rgb="FF3B3355"/>
@@ -9862,32 +10411,32 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="45" t="s">
+      <c r="A2" s="60" t="s">
         <v>1114</v>
       </c>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="44"/>
-      <c r="H2" s="44"/>
-      <c r="I2" s="44"/>
-      <c r="J2" s="44"/>
+      <c r="B2" s="59"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
     </row>
     <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="43" t="s">
+      <c r="A3" s="58" t="s">
         <v>1115</v>
       </c>
-      <c r="B3" s="44"/>
-      <c r="C3" s="44"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
-      <c r="G3" s="44"/>
-      <c r="H3" s="44"/>
-      <c r="I3" s="44"/>
-      <c r="J3" s="44"/>
+      <c r="B3" s="59"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
     </row>
     <row r="5" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
@@ -10205,7 +10754,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <sheetPr>
     <tabColor rgb="FF8C9399"/>
@@ -10229,32 +10778,32 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="45" t="s">
+      <c r="A2" s="60" t="s">
         <v>1126</v>
       </c>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="44"/>
-      <c r="H2" s="44"/>
-      <c r="I2" s="44"/>
-      <c r="J2" s="44"/>
+      <c r="B2" s="59"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
     </row>
     <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="43" t="s">
+      <c r="A3" s="58" t="s">
         <v>1127</v>
       </c>
-      <c r="B3" s="44"/>
-      <c r="C3" s="44"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
-      <c r="G3" s="44"/>
-      <c r="H3" s="44"/>
-      <c r="I3" s="44"/>
-      <c r="J3" s="44"/>
+      <c r="B3" s="59"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
     </row>
     <row r="5" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
@@ -10572,7 +11121,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <sheetPr>
     <tabColor rgb="FF8B1E2D"/>
@@ -10596,32 +11145,32 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="45" t="s">
+      <c r="A2" s="60" t="s">
         <v>1138</v>
       </c>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="44"/>
-      <c r="H2" s="44"/>
-      <c r="I2" s="44"/>
-      <c r="J2" s="44"/>
+      <c r="B2" s="59"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
     </row>
     <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="43" t="s">
+      <c r="A3" s="58" t="s">
         <v>1139</v>
       </c>
-      <c r="B3" s="44"/>
-      <c r="C3" s="44"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
-      <c r="G3" s="44"/>
-      <c r="H3" s="44"/>
-      <c r="I3" s="44"/>
-      <c r="J3" s="44"/>
+      <c r="B3" s="59"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
     </row>
     <row r="5" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
@@ -10939,7 +11488,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <sheetPr>
     <tabColor rgb="FF6BBF59"/>
@@ -10963,32 +11512,32 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="45" t="s">
+      <c r="A2" s="60" t="s">
         <v>1150</v>
       </c>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="44"/>
-      <c r="H2" s="44"/>
-      <c r="I2" s="44"/>
-      <c r="J2" s="44"/>
+      <c r="B2" s="59"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
     </row>
     <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="43" t="s">
+      <c r="A3" s="58" t="s">
         <v>1151</v>
       </c>
-      <c r="B3" s="44"/>
-      <c r="C3" s="44"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
-      <c r="G3" s="44"/>
-      <c r="H3" s="44"/>
-      <c r="I3" s="44"/>
-      <c r="J3" s="44"/>
+      <c r="B3" s="59"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
     </row>
     <row r="5" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
@@ -11306,7 +11855,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <sheetPr>
     <tabColor rgb="FF4A4A4A"/>
@@ -11330,32 +11879,32 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="45" t="s">
+      <c r="A2" s="60" t="s">
         <v>1162</v>
       </c>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="44"/>
-      <c r="H2" s="44"/>
-      <c r="I2" s="44"/>
-      <c r="J2" s="44"/>
+      <c r="B2" s="59"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
     </row>
     <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="43" t="s">
+      <c r="A3" s="58" t="s">
         <v>1163</v>
       </c>
-      <c r="B3" s="44"/>
-      <c r="C3" s="44"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
-      <c r="G3" s="44"/>
-      <c r="H3" s="44"/>
-      <c r="I3" s="44"/>
-      <c r="J3" s="44"/>
+      <c r="B3" s="59"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
     </row>
     <row r="5" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
@@ -11673,7 +12222,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <sheetPr>
     <tabColor rgb="FF3E7B3A"/>
@@ -11697,32 +12246,32 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="45" t="s">
+      <c r="A2" s="60" t="s">
         <v>1174</v>
       </c>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="44"/>
-      <c r="H2" s="44"/>
-      <c r="I2" s="44"/>
-      <c r="J2" s="44"/>
+      <c r="B2" s="59"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
     </row>
     <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="43" t="s">
+      <c r="A3" s="58" t="s">
         <v>1175</v>
       </c>
-      <c r="B3" s="44"/>
-      <c r="C3" s="44"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
-      <c r="G3" s="44"/>
-      <c r="H3" s="44"/>
-      <c r="I3" s="44"/>
-      <c r="J3" s="44"/>
+      <c r="B3" s="59"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
     </row>
     <row r="5" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
@@ -12040,7 +12589,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <sheetPr>
     <tabColor rgb="FFF5E6A8"/>
@@ -12064,32 +12613,32 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="45" t="s">
+      <c r="A2" s="60" t="s">
         <v>1186</v>
       </c>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="44"/>
-      <c r="H2" s="44"/>
-      <c r="I2" s="44"/>
-      <c r="J2" s="44"/>
+      <c r="B2" s="59"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
     </row>
     <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="43" t="s">
+      <c r="A3" s="58" t="s">
         <v>1187</v>
       </c>
-      <c r="B3" s="44"/>
-      <c r="C3" s="44"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
-      <c r="G3" s="44"/>
-      <c r="H3" s="44"/>
-      <c r="I3" s="44"/>
-      <c r="J3" s="44"/>
+      <c r="B3" s="59"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
     </row>
     <row r="5" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
@@ -12388,373 +12937,6 @@
       <c r="G15" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B15,'Base Runes'!$A:$A,0)),"")</f>
         <v>Halo</v>
-      </c>
-      <c r="H15" s="30"/>
-      <c r="I15" s="10"/>
-      <c r="J15" s="10"/>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="29" t="s">
-        <v>1035</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A3:J3"/>
-    <mergeCell ref="A2:J2"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
-  <sheetPr>
-    <tabColor rgb="FF9B7FD4"/>
-  </sheetPr>
-  <dimension ref="A1:J17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="11" customWidth="1"/>
-    <col min="5" max="6" width="46" customWidth="1"/>
-    <col min="7" max="7" width="16" customWidth="1"/>
-    <col min="8" max="8" width="40" customWidth="1"/>
-    <col min="9" max="10" width="30" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A1" s="25" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="45" t="s">
-        <v>1198</v>
-      </c>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="44"/>
-      <c r="H2" s="44"/>
-      <c r="I2" s="44"/>
-      <c r="J2" s="44"/>
-    </row>
-    <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="43" t="s">
-        <v>1199</v>
-      </c>
-      <c r="B3" s="44"/>
-      <c r="C3" s="44"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
-      <c r="G3" s="44"/>
-      <c r="H3" s="44"/>
-      <c r="I3" s="44"/>
-      <c r="J3" s="44"/>
-    </row>
-    <row r="5" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>979</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>980</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>981</v>
-      </c>
-      <c r="I5" s="8" t="s">
-        <v>982</v>
-      </c>
-      <c r="J5" s="8" t="s">
-        <v>983</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="26">
-        <v>1</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>634</v>
-      </c>
-      <c r="C6" s="27" t="str">
-        <f>IFERROR(INDEX('Base Runes'!$D:$D,MATCH($B6,'Base Runes'!$A:$A,0)),"")</f>
-        <v>Sleep</v>
-      </c>
-      <c r="D6" s="31" t="str">
-        <f>IFERROR(INDEX('Base Runes'!$E:$E,MATCH($B6,'Base Runes'!$A:$A,0)),"")</f>
-        <v>🝐</v>
-      </c>
-      <c r="E6" s="10" t="s">
-        <v>1200</v>
-      </c>
-      <c r="F6" s="30"/>
-      <c r="G6" s="11" t="str">
-        <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B6,'Base Runes'!$A:$A,0)),"")</f>
-        <v>Wake</v>
-      </c>
-      <c r="H6" s="30"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="10"/>
-    </row>
-    <row r="7" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="26">
-        <v>1</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>637</v>
-      </c>
-      <c r="C7" s="27" t="str">
-        <f>IFERROR(INDEX('Base Runes'!$D:$D,MATCH($B7,'Base Runes'!$A:$A,0)),"")</f>
-        <v>Wake</v>
-      </c>
-      <c r="D7" s="31" t="str">
-        <f>IFERROR(INDEX('Base Runes'!$E:$E,MATCH($B7,'Base Runes'!$A:$A,0)),"")</f>
-        <v>🝑</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>1201</v>
-      </c>
-      <c r="F7" s="30"/>
-      <c r="G7" s="11" t="str">
-        <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B7,'Base Runes'!$A:$A,0)),"")</f>
-        <v>Sleep</v>
-      </c>
-      <c r="H7" s="30"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="10"/>
-    </row>
-    <row r="8" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="26">
-        <v>2</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>642</v>
-      </c>
-      <c r="C8" s="27" t="str">
-        <f>IFERROR(INDEX('Base Runes'!$D:$D,MATCH($B8,'Base Runes'!$A:$A,0)),"")</f>
-        <v>Phantasm</v>
-      </c>
-      <c r="D8" s="31" t="str">
-        <f>IFERROR(INDEX('Base Runes'!$E:$E,MATCH($B8,'Base Runes'!$A:$A,0)),"")</f>
-        <v>🝒</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>1202</v>
-      </c>
-      <c r="F8" s="30"/>
-      <c r="G8" s="11" t="str">
-        <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B8,'Base Runes'!$A:$A,0)),"")</f>
-        <v>Dispel</v>
-      </c>
-      <c r="H8" s="30"/>
-      <c r="I8" s="10"/>
-      <c r="J8" s="10"/>
-    </row>
-    <row r="9" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="26">
-        <v>2</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>645</v>
-      </c>
-      <c r="C9" s="27" t="str">
-        <f>IFERROR(INDEX('Base Runes'!$D:$D,MATCH($B9,'Base Runes'!$A:$A,0)),"")</f>
-        <v>Dispel</v>
-      </c>
-      <c r="D9" s="31" t="str">
-        <f>IFERROR(INDEX('Base Runes'!$E:$E,MATCH($B9,'Base Runes'!$A:$A,0)),"")</f>
-        <v>🝓</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>1203</v>
-      </c>
-      <c r="F9" s="30"/>
-      <c r="G9" s="11" t="str">
-        <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B9,'Base Runes'!$A:$A,0)),"")</f>
-        <v>Phantasm</v>
-      </c>
-      <c r="H9" s="30"/>
-      <c r="I9" s="10"/>
-      <c r="J9" s="10"/>
-    </row>
-    <row r="10" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="26">
-        <v>3</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>650</v>
-      </c>
-      <c r="C10" s="27" t="str">
-        <f>IFERROR(INDEX('Base Runes'!$D:$D,MATCH($B10,'Base Runes'!$A:$A,0)),"")</f>
-        <v>Nightmare</v>
-      </c>
-      <c r="D10" s="31" t="str">
-        <f>IFERROR(INDEX('Base Runes'!$E:$E,MATCH($B10,'Base Runes'!$A:$A,0)),"")</f>
-        <v>🝔</v>
-      </c>
-      <c r="E10" s="10" t="s">
-        <v>1204</v>
-      </c>
-      <c r="F10" s="30"/>
-      <c r="G10" s="11" t="str">
-        <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B10,'Base Runes'!$A:$A,0)),"")</f>
-        <v>Reverie</v>
-      </c>
-      <c r="H10" s="30"/>
-      <c r="I10" s="10"/>
-      <c r="J10" s="10"/>
-    </row>
-    <row r="11" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="26">
-        <v>3</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>653</v>
-      </c>
-      <c r="C11" s="27" t="str">
-        <f>IFERROR(INDEX('Base Runes'!$D:$D,MATCH($B11,'Base Runes'!$A:$A,0)),"")</f>
-        <v>Reverie</v>
-      </c>
-      <c r="D11" s="31" t="str">
-        <f>IFERROR(INDEX('Base Runes'!$E:$E,MATCH($B11,'Base Runes'!$A:$A,0)),"")</f>
-        <v>🝕</v>
-      </c>
-      <c r="E11" s="10" t="s">
-        <v>1205</v>
-      </c>
-      <c r="F11" s="30"/>
-      <c r="G11" s="11" t="str">
-        <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B11,'Base Runes'!$A:$A,0)),"")</f>
-        <v>Nightmare</v>
-      </c>
-      <c r="H11" s="30"/>
-      <c r="I11" s="10"/>
-      <c r="J11" s="10"/>
-    </row>
-    <row r="12" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="26">
-        <v>4</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>658</v>
-      </c>
-      <c r="C12" s="27" t="str">
-        <f>IFERROR(INDEX('Base Runes'!$D:$D,MATCH($B12,'Base Runes'!$A:$A,0)),"")</f>
-        <v>Muddle</v>
-      </c>
-      <c r="D12" s="31" t="str">
-        <f>IFERROR(INDEX('Base Runes'!$E:$E,MATCH($B12,'Base Runes'!$A:$A,0)),"")</f>
-        <v>🝖</v>
-      </c>
-      <c r="E12" s="10" t="s">
-        <v>1206</v>
-      </c>
-      <c r="F12" s="30"/>
-      <c r="G12" s="11" t="str">
-        <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B12,'Base Runes'!$A:$A,0)),"")</f>
-        <v>Clarify</v>
-      </c>
-      <c r="H12" s="30"/>
-      <c r="I12" s="10"/>
-      <c r="J12" s="10"/>
-    </row>
-    <row r="13" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="26">
-        <v>4</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>661</v>
-      </c>
-      <c r="C13" s="27" t="str">
-        <f>IFERROR(INDEX('Base Runes'!$D:$D,MATCH($B13,'Base Runes'!$A:$A,0)),"")</f>
-        <v>Clarify</v>
-      </c>
-      <c r="D13" s="31" t="str">
-        <f>IFERROR(INDEX('Base Runes'!$E:$E,MATCH($B13,'Base Runes'!$A:$A,0)),"")</f>
-        <v>🝗</v>
-      </c>
-      <c r="E13" s="10" t="s">
-        <v>1207</v>
-      </c>
-      <c r="F13" s="30"/>
-      <c r="G13" s="11" t="str">
-        <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B13,'Base Runes'!$A:$A,0)),"")</f>
-        <v>Muddle</v>
-      </c>
-      <c r="H13" s="30"/>
-      <c r="I13" s="10"/>
-      <c r="J13" s="10"/>
-    </row>
-    <row r="14" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="26">
-        <v>5</v>
-      </c>
-      <c r="B14" s="10" t="s">
-        <v>666</v>
-      </c>
-      <c r="C14" s="27" t="str">
-        <f>IFERROR(INDEX('Base Runes'!$D:$D,MATCH($B14,'Base Runes'!$A:$A,0)),"")</f>
-        <v>Whisper</v>
-      </c>
-      <c r="D14" s="31" t="str">
-        <f>IFERROR(INDEX('Base Runes'!$E:$E,MATCH($B14,'Base Runes'!$A:$A,0)),"")</f>
-        <v>🝘</v>
-      </c>
-      <c r="E14" s="10" t="s">
-        <v>1208</v>
-      </c>
-      <c r="F14" s="30"/>
-      <c r="G14" s="11" t="str">
-        <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B14,'Base Runes'!$A:$A,0)),"")</f>
-        <v>Shut</v>
-      </c>
-      <c r="H14" s="30"/>
-      <c r="I14" s="10"/>
-      <c r="J14" s="10"/>
-    </row>
-    <row r="15" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="26">
-        <v>5</v>
-      </c>
-      <c r="B15" s="10" t="s">
-        <v>669</v>
-      </c>
-      <c r="C15" s="27" t="str">
-        <f>IFERROR(INDEX('Base Runes'!$D:$D,MATCH($B15,'Base Runes'!$A:$A,0)),"")</f>
-        <v>Shut</v>
-      </c>
-      <c r="D15" s="31" t="str">
-        <f>IFERROR(INDEX('Base Runes'!$E:$E,MATCH($B15,'Base Runes'!$A:$A,0)),"")</f>
-        <v>🝙</v>
-      </c>
-      <c r="E15" s="10" t="s">
-        <v>1209</v>
-      </c>
-      <c r="F15" s="30"/>
-      <c r="G15" s="11" t="str">
-        <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B15,'Base Runes'!$A:$A,0)),"")</f>
-        <v>Whisper</v>
       </c>
       <c r="H15" s="30"/>
       <c r="I15" s="10"/>
@@ -15434,6 +15616,373 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
+  <sheetPr>
+    <tabColor rgb="FF9B7FD4"/>
+  </sheetPr>
+  <dimension ref="A1:J17"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="11" customWidth="1"/>
+    <col min="5" max="6" width="46" customWidth="1"/>
+    <col min="7" max="7" width="16" customWidth="1"/>
+    <col min="8" max="8" width="40" customWidth="1"/>
+    <col min="9" max="10" width="30" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A1" s="25" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="60" t="s">
+        <v>1198</v>
+      </c>
+      <c r="B2" s="59"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
+    </row>
+    <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="58" t="s">
+        <v>1199</v>
+      </c>
+      <c r="B3" s="59"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
+    </row>
+    <row r="5" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>979</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>980</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>981</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>982</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="26">
+        <v>1</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>634</v>
+      </c>
+      <c r="C6" s="27" t="str">
+        <f>IFERROR(INDEX('Base Runes'!$D:$D,MATCH($B6,'Base Runes'!$A:$A,0)),"")</f>
+        <v>Sleep</v>
+      </c>
+      <c r="D6" s="31" t="str">
+        <f>IFERROR(INDEX('Base Runes'!$E:$E,MATCH($B6,'Base Runes'!$A:$A,0)),"")</f>
+        <v>🝐</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>1200</v>
+      </c>
+      <c r="F6" s="30"/>
+      <c r="G6" s="11" t="str">
+        <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B6,'Base Runes'!$A:$A,0)),"")</f>
+        <v>Wake</v>
+      </c>
+      <c r="H6" s="30"/>
+      <c r="I6" s="10"/>
+      <c r="J6" s="10"/>
+    </row>
+    <row r="7" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="26">
+        <v>1</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>637</v>
+      </c>
+      <c r="C7" s="27" t="str">
+        <f>IFERROR(INDEX('Base Runes'!$D:$D,MATCH($B7,'Base Runes'!$A:$A,0)),"")</f>
+        <v>Wake</v>
+      </c>
+      <c r="D7" s="31" t="str">
+        <f>IFERROR(INDEX('Base Runes'!$E:$E,MATCH($B7,'Base Runes'!$A:$A,0)),"")</f>
+        <v>🝑</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>1201</v>
+      </c>
+      <c r="F7" s="30"/>
+      <c r="G7" s="11" t="str">
+        <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B7,'Base Runes'!$A:$A,0)),"")</f>
+        <v>Sleep</v>
+      </c>
+      <c r="H7" s="30"/>
+      <c r="I7" s="10"/>
+      <c r="J7" s="10"/>
+    </row>
+    <row r="8" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="26">
+        <v>2</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>642</v>
+      </c>
+      <c r="C8" s="27" t="str">
+        <f>IFERROR(INDEX('Base Runes'!$D:$D,MATCH($B8,'Base Runes'!$A:$A,0)),"")</f>
+        <v>Phantasm</v>
+      </c>
+      <c r="D8" s="31" t="str">
+        <f>IFERROR(INDEX('Base Runes'!$E:$E,MATCH($B8,'Base Runes'!$A:$A,0)),"")</f>
+        <v>🝒</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>1202</v>
+      </c>
+      <c r="F8" s="30"/>
+      <c r="G8" s="11" t="str">
+        <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B8,'Base Runes'!$A:$A,0)),"")</f>
+        <v>Dispel</v>
+      </c>
+      <c r="H8" s="30"/>
+      <c r="I8" s="10"/>
+      <c r="J8" s="10"/>
+    </row>
+    <row r="9" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="26">
+        <v>2</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>645</v>
+      </c>
+      <c r="C9" s="27" t="str">
+        <f>IFERROR(INDEX('Base Runes'!$D:$D,MATCH($B9,'Base Runes'!$A:$A,0)),"")</f>
+        <v>Dispel</v>
+      </c>
+      <c r="D9" s="31" t="str">
+        <f>IFERROR(INDEX('Base Runes'!$E:$E,MATCH($B9,'Base Runes'!$A:$A,0)),"")</f>
+        <v>🝓</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>1203</v>
+      </c>
+      <c r="F9" s="30"/>
+      <c r="G9" s="11" t="str">
+        <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B9,'Base Runes'!$A:$A,0)),"")</f>
+        <v>Phantasm</v>
+      </c>
+      <c r="H9" s="30"/>
+      <c r="I9" s="10"/>
+      <c r="J9" s="10"/>
+    </row>
+    <row r="10" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="26">
+        <v>3</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>650</v>
+      </c>
+      <c r="C10" s="27" t="str">
+        <f>IFERROR(INDEX('Base Runes'!$D:$D,MATCH($B10,'Base Runes'!$A:$A,0)),"")</f>
+        <v>Nightmare</v>
+      </c>
+      <c r="D10" s="31" t="str">
+        <f>IFERROR(INDEX('Base Runes'!$E:$E,MATCH($B10,'Base Runes'!$A:$A,0)),"")</f>
+        <v>🝔</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>1204</v>
+      </c>
+      <c r="F10" s="30"/>
+      <c r="G10" s="11" t="str">
+        <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B10,'Base Runes'!$A:$A,0)),"")</f>
+        <v>Reverie</v>
+      </c>
+      <c r="H10" s="30"/>
+      <c r="I10" s="10"/>
+      <c r="J10" s="10"/>
+    </row>
+    <row r="11" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="26">
+        <v>3</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>653</v>
+      </c>
+      <c r="C11" s="27" t="str">
+        <f>IFERROR(INDEX('Base Runes'!$D:$D,MATCH($B11,'Base Runes'!$A:$A,0)),"")</f>
+        <v>Reverie</v>
+      </c>
+      <c r="D11" s="31" t="str">
+        <f>IFERROR(INDEX('Base Runes'!$E:$E,MATCH($B11,'Base Runes'!$A:$A,0)),"")</f>
+        <v>🝕</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>1205</v>
+      </c>
+      <c r="F11" s="30"/>
+      <c r="G11" s="11" t="str">
+        <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B11,'Base Runes'!$A:$A,0)),"")</f>
+        <v>Nightmare</v>
+      </c>
+      <c r="H11" s="30"/>
+      <c r="I11" s="10"/>
+      <c r="J11" s="10"/>
+    </row>
+    <row r="12" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="26">
+        <v>4</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>658</v>
+      </c>
+      <c r="C12" s="27" t="str">
+        <f>IFERROR(INDEX('Base Runes'!$D:$D,MATCH($B12,'Base Runes'!$A:$A,0)),"")</f>
+        <v>Muddle</v>
+      </c>
+      <c r="D12" s="31" t="str">
+        <f>IFERROR(INDEX('Base Runes'!$E:$E,MATCH($B12,'Base Runes'!$A:$A,0)),"")</f>
+        <v>🝖</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>1206</v>
+      </c>
+      <c r="F12" s="30"/>
+      <c r="G12" s="11" t="str">
+        <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B12,'Base Runes'!$A:$A,0)),"")</f>
+        <v>Clarify</v>
+      </c>
+      <c r="H12" s="30"/>
+      <c r="I12" s="10"/>
+      <c r="J12" s="10"/>
+    </row>
+    <row r="13" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="26">
+        <v>4</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>661</v>
+      </c>
+      <c r="C13" s="27" t="str">
+        <f>IFERROR(INDEX('Base Runes'!$D:$D,MATCH($B13,'Base Runes'!$A:$A,0)),"")</f>
+        <v>Clarify</v>
+      </c>
+      <c r="D13" s="31" t="str">
+        <f>IFERROR(INDEX('Base Runes'!$E:$E,MATCH($B13,'Base Runes'!$A:$A,0)),"")</f>
+        <v>🝗</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>1207</v>
+      </c>
+      <c r="F13" s="30"/>
+      <c r="G13" s="11" t="str">
+        <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B13,'Base Runes'!$A:$A,0)),"")</f>
+        <v>Muddle</v>
+      </c>
+      <c r="H13" s="30"/>
+      <c r="I13" s="10"/>
+      <c r="J13" s="10"/>
+    </row>
+    <row r="14" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="26">
+        <v>5</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>666</v>
+      </c>
+      <c r="C14" s="27" t="str">
+        <f>IFERROR(INDEX('Base Runes'!$D:$D,MATCH($B14,'Base Runes'!$A:$A,0)),"")</f>
+        <v>Whisper</v>
+      </c>
+      <c r="D14" s="31" t="str">
+        <f>IFERROR(INDEX('Base Runes'!$E:$E,MATCH($B14,'Base Runes'!$A:$A,0)),"")</f>
+        <v>🝘</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>1208</v>
+      </c>
+      <c r="F14" s="30"/>
+      <c r="G14" s="11" t="str">
+        <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B14,'Base Runes'!$A:$A,0)),"")</f>
+        <v>Shut</v>
+      </c>
+      <c r="H14" s="30"/>
+      <c r="I14" s="10"/>
+      <c r="J14" s="10"/>
+    </row>
+    <row r="15" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="26">
+        <v>5</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>669</v>
+      </c>
+      <c r="C15" s="27" t="str">
+        <f>IFERROR(INDEX('Base Runes'!$D:$D,MATCH($B15,'Base Runes'!$A:$A,0)),"")</f>
+        <v>Shut</v>
+      </c>
+      <c r="D15" s="31" t="str">
+        <f>IFERROR(INDEX('Base Runes'!$E:$E,MATCH($B15,'Base Runes'!$A:$A,0)),"")</f>
+        <v>🝙</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>1209</v>
+      </c>
+      <c r="F15" s="30"/>
+      <c r="G15" s="11" t="str">
+        <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B15,'Base Runes'!$A:$A,0)),"")</f>
+        <v>Whisper</v>
+      </c>
+      <c r="H15" s="30"/>
+      <c r="I15" s="10"/>
+      <c r="J15" s="10"/>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="29" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A2:J2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <sheetPr>
     <tabColor rgb="FF7CB342"/>
@@ -15457,32 +16006,32 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="45" t="s">
+      <c r="A2" s="60" t="s">
         <v>1210</v>
       </c>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="44"/>
-      <c r="H2" s="44"/>
-      <c r="I2" s="44"/>
-      <c r="J2" s="44"/>
+      <c r="B2" s="59"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
     </row>
     <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="43" t="s">
+      <c r="A3" s="58" t="s">
         <v>1187</v>
       </c>
-      <c r="B3" s="44"/>
-      <c r="C3" s="44"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
-      <c r="G3" s="44"/>
-      <c r="H3" s="44"/>
-      <c r="I3" s="44"/>
-      <c r="J3" s="44"/>
+      <c r="B3" s="59"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
     </row>
     <row r="5" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
@@ -15800,7 +16349,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
   <sheetPr>
     <tabColor rgb="FF6B6B3A"/>
@@ -15824,32 +16373,32 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="45" t="s">
+      <c r="A2" s="60" t="s">
         <v>1221</v>
       </c>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="44"/>
-      <c r="H2" s="44"/>
-      <c r="I2" s="44"/>
-      <c r="J2" s="44"/>
+      <c r="B2" s="59"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
     </row>
     <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="43" t="s">
+      <c r="A3" s="58" t="s">
         <v>1222</v>
       </c>
-      <c r="B3" s="44"/>
-      <c r="C3" s="44"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
-      <c r="G3" s="44"/>
-      <c r="H3" s="44"/>
-      <c r="I3" s="44"/>
-      <c r="J3" s="44"/>
+      <c r="B3" s="59"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
     </row>
     <row r="5" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
@@ -16167,7 +16716,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31D58E66-72D9-418F-A057-C953B478D617}">
   <dimension ref="A1:K19"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
@@ -16890,7 +17439,7 @@
   <sheetData>
     <row r="1" spans="1:17" ht="50.25" x14ac:dyDescent="0.2">
       <c r="A1" s="33"/>
-      <c r="B1" s="46" t="str">
+      <c r="B1" s="43" t="str">
         <f>'Slider Links'!A2</f>
         <v>Water</v>
       </c>
@@ -18132,7 +18681,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:J167"/>
+  <dimension ref="A1:N167"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -18144,9 +18693,13 @@
     <col min="8" max="8" width="11" customWidth="1"/>
     <col min="9" max="9" width="60" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
+    <col min="11" max="11" width="9.7109375" customWidth="1"/>
+    <col min="12" max="12" width="15.7109375" customWidth="1"/>
+    <col min="13" max="13" width="9.7109375" customWidth="1"/>
+    <col min="14" max="14" width="13.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
         <v>82</v>
       </c>
@@ -18177,8 +18730,20 @@
       <c r="J1" s="8" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K1" s="36" t="s">
+        <v>1260</v>
+      </c>
+      <c r="L1" s="36" t="s">
+        <v>1289</v>
+      </c>
+      <c r="M1" s="36" t="s">
+        <v>1261</v>
+      </c>
+      <c r="N1" s="36" t="s">
+        <v>1290</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
         <v>91</v>
       </c>
@@ -18212,8 +18777,22 @@
       <c r="J2" s="21" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K2" s="51" t="s">
+        <v>1268</v>
+      </c>
+      <c r="L2" s="52">
+        <v>-0.6</v>
+      </c>
+      <c r="M2" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K2,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>2</v>
+      </c>
+      <c r="N2" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L2*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K2,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
         <v>94</v>
       </c>
@@ -18247,8 +18826,22 @@
       <c r="J3" s="21" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K3" s="51" t="s">
+        <v>1268</v>
+      </c>
+      <c r="L3" s="52">
+        <v>0.6</v>
+      </c>
+      <c r="M3" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K3,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>2</v>
+      </c>
+      <c r="N3" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L3*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K3,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="16" t="s">
         <v>99</v>
       </c>
@@ -18282,8 +18875,22 @@
       <c r="J4" s="21" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K4" s="51" t="s">
+        <v>1268</v>
+      </c>
+      <c r="L4" s="52">
+        <v>-0.3</v>
+      </c>
+      <c r="M4" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K4,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>2</v>
+      </c>
+      <c r="N4" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L4*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K4,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
         <v>102</v>
       </c>
@@ -18317,8 +18924,22 @@
       <c r="J5" s="21" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K5" s="51" t="s">
+        <v>1274</v>
+      </c>
+      <c r="L5" s="52">
+        <v>0.3</v>
+      </c>
+      <c r="M5" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K5,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>4</v>
+      </c>
+      <c r="N5" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L5*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K5,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2.62</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
         <v>107</v>
       </c>
@@ -18352,8 +18973,22 @@
       <c r="J6" s="21" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K6" s="51" t="s">
+        <v>1268</v>
+      </c>
+      <c r="L6" s="52">
+        <v>-0.5</v>
+      </c>
+      <c r="M6" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K6,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>2</v>
+      </c>
+      <c r="N6" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L6*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K6,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
         <v>110</v>
       </c>
@@ -18387,8 +19022,22 @@
       <c r="J7" s="21" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K7" s="51" t="s">
+        <v>1265</v>
+      </c>
+      <c r="L7" s="52">
+        <v>0.8</v>
+      </c>
+      <c r="M7" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K7,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>1</v>
+      </c>
+      <c r="N7" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L7*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K7,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="16" t="s">
         <v>115</v>
       </c>
@@ -18422,8 +19071,22 @@
       <c r="J8" s="21" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K8" s="51" t="s">
+        <v>1268</v>
+      </c>
+      <c r="L8" s="52">
+        <v>0.5</v>
+      </c>
+      <c r="M8" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K8,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>2</v>
+      </c>
+      <c r="N8" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L8*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K8,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
         <v>118</v>
       </c>
@@ -18457,8 +19120,22 @@
       <c r="J9" s="21" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K9" s="51" t="s">
+        <v>1271</v>
+      </c>
+      <c r="L9" s="52">
+        <v>-0.7</v>
+      </c>
+      <c r="M9" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K9,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>3</v>
+      </c>
+      <c r="N9" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L9*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K9,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2.0099999999999998</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
         <v>123</v>
       </c>
@@ -18492,8 +19169,22 @@
       <c r="J10" s="21" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K10" s="51" t="s">
+        <v>1274</v>
+      </c>
+      <c r="L10" s="52">
+        <v>-0.4</v>
+      </c>
+      <c r="M10" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K10,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>4</v>
+      </c>
+      <c r="N10" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L10*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K10,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2.34</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
         <v>126</v>
       </c>
@@ -18527,8 +19218,22 @@
       <c r="J11" s="21" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K11" s="51" t="s">
+        <v>1265</v>
+      </c>
+      <c r="L11" s="52">
+        <v>0.6</v>
+      </c>
+      <c r="M11" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K11,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>1</v>
+      </c>
+      <c r="N11" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L11*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K11,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="16" t="s">
         <v>131</v>
       </c>
@@ -18562,8 +19267,22 @@
       <c r="J12" s="21" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K12" s="51" t="s">
+        <v>1268</v>
+      </c>
+      <c r="L12" s="52">
+        <v>-0.2</v>
+      </c>
+      <c r="M12" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K12,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>2</v>
+      </c>
+      <c r="N12" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L12*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K12,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="16" t="s">
         <v>134</v>
       </c>
@@ -18597,8 +19316,22 @@
       <c r="J13" s="21" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K13" s="51" t="s">
+        <v>1271</v>
+      </c>
+      <c r="L13" s="52">
+        <v>0.4</v>
+      </c>
+      <c r="M13" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K13,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>3</v>
+      </c>
+      <c r="N13" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L13*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K13,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2.78</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
         <v>139</v>
       </c>
@@ -18632,8 +19365,22 @@
       <c r="J14" s="21" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="15" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K14" s="51" t="s">
+        <v>1268</v>
+      </c>
+      <c r="L14" s="52">
+        <v>0.4</v>
+      </c>
+      <c r="M14" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K14,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>2</v>
+      </c>
+      <c r="N14" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L14*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K14,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="16" t="s">
         <v>142</v>
       </c>
@@ -18667,8 +19414,22 @@
       <c r="J15" s="21" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K15" s="51" t="s">
+        <v>1274</v>
+      </c>
+      <c r="L15" s="52">
+        <v>-0.3</v>
+      </c>
+      <c r="M15" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K15,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>4</v>
+      </c>
+      <c r="N15" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L15*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K15,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2.38</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="16" t="s">
         <v>147</v>
       </c>
@@ -18702,8 +19463,22 @@
       <c r="J16" s="21" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K16" s="51" t="s">
+        <v>1265</v>
+      </c>
+      <c r="L16" s="52">
+        <v>0.9</v>
+      </c>
+      <c r="M16" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K16,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>1</v>
+      </c>
+      <c r="N16" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L16*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K16,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>3.85</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="16" t="s">
         <v>150</v>
       </c>
@@ -18737,8 +19512,22 @@
       <c r="J17" s="21" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K17" s="51" t="s">
+        <v>1268</v>
+      </c>
+      <c r="L17" s="52">
+        <v>-0.5</v>
+      </c>
+      <c r="M17" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K17,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>2</v>
+      </c>
+      <c r="N17" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L17*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K17,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="16" t="s">
         <v>155</v>
       </c>
@@ -18772,8 +19561,22 @@
       <c r="J18" s="21" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="19" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K18" s="51" t="s">
+        <v>1268</v>
+      </c>
+      <c r="L18" s="52">
+        <v>-0.5</v>
+      </c>
+      <c r="M18" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K18,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>2</v>
+      </c>
+      <c r="N18" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L18*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K18,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="16" t="s">
         <v>158</v>
       </c>
@@ -18807,8 +19610,22 @@
       <c r="J19" s="21" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="20" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K19" s="51" t="s">
+        <v>1265</v>
+      </c>
+      <c r="L19" s="52">
+        <v>0.7</v>
+      </c>
+      <c r="M19" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K19,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>1</v>
+      </c>
+      <c r="N19" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L19*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K19,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>3.55</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="16" t="s">
         <v>163</v>
       </c>
@@ -18842,8 +19659,22 @@
       <c r="J20" s="21" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="21" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K20" s="51" t="s">
+        <v>1271</v>
+      </c>
+      <c r="L20" s="52">
+        <v>-0.9</v>
+      </c>
+      <c r="M20" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K20,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>3</v>
+      </c>
+      <c r="N20" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L20*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K20,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>1.87</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="s">
         <v>166</v>
       </c>
@@ -18877,8 +19708,22 @@
       <c r="J21" s="21" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="22" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K21" s="51" t="s">
+        <v>1268</v>
+      </c>
+      <c r="L21" s="52">
+        <v>0.9</v>
+      </c>
+      <c r="M21" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K21,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>2</v>
+      </c>
+      <c r="N21" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L21*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K21,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="16" t="s">
         <v>171</v>
       </c>
@@ -18912,8 +19757,22 @@
       <c r="J22" s="21" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="23" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K22" s="51" t="s">
+        <v>1268</v>
+      </c>
+      <c r="L22" s="52">
+        <v>0.8</v>
+      </c>
+      <c r="M22" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K22,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>2</v>
+      </c>
+      <c r="N22" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L22*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K22,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="16" t="s">
         <v>174</v>
       </c>
@@ -18947,8 +19806,22 @@
       <c r="J23" s="21" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="24" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K23" s="51" t="s">
+        <v>1274</v>
+      </c>
+      <c r="L23" s="52">
+        <v>0.2</v>
+      </c>
+      <c r="M23" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K23,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>4</v>
+      </c>
+      <c r="N23" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L23*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K23,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2.58</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="16" t="s">
         <v>179</v>
       </c>
@@ -18982,8 +19855,22 @@
       <c r="J24" s="21" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="25" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K24" s="51" t="s">
+        <v>1271</v>
+      </c>
+      <c r="L24" s="52">
+        <v>-1</v>
+      </c>
+      <c r="M24" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K24,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>3</v>
+      </c>
+      <c r="N24" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L24*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K24,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="16" t="s">
         <v>182</v>
       </c>
@@ -19017,8 +19904,22 @@
       <c r="J25" s="21" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="26" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K25" s="51" t="s">
+        <v>1265</v>
+      </c>
+      <c r="L25" s="52">
+        <v>1</v>
+      </c>
+      <c r="M25" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K25,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>1</v>
+      </c>
+      <c r="N25" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L25*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K25,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="16" t="s">
         <v>187</v>
       </c>
@@ -19052,8 +19953,22 @@
       <c r="J26" s="21" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="27" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K26" s="51" t="s">
+        <v>1271</v>
+      </c>
+      <c r="L26" s="52">
+        <v>-0.6</v>
+      </c>
+      <c r="M26" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K26,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>3</v>
+      </c>
+      <c r="N26" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L26*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K26,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2.08</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="16" t="s">
         <v>190</v>
       </c>
@@ -19087,8 +20002,22 @@
       <c r="J27" s="21" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="28" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K27" s="51" t="s">
+        <v>1268</v>
+      </c>
+      <c r="L27" s="52">
+        <v>0.3</v>
+      </c>
+      <c r="M27" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K27,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>2</v>
+      </c>
+      <c r="N27" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L27*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K27,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="16" t="s">
         <v>195</v>
       </c>
@@ -19122,8 +20051,22 @@
       <c r="J28" s="21" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="29" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K28" s="51" t="s">
+        <v>1274</v>
+      </c>
+      <c r="L28" s="52">
+        <v>-0.2</v>
+      </c>
+      <c r="M28" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K28,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>4</v>
+      </c>
+      <c r="N28" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L28*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K28,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2.42</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="16" t="s">
         <v>198</v>
       </c>
@@ -19157,8 +20100,22 @@
       <c r="J29" s="21" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="30" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K29" s="51" t="s">
+        <v>1268</v>
+      </c>
+      <c r="L29" s="52">
+        <v>0.5</v>
+      </c>
+      <c r="M29" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K29,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>2</v>
+      </c>
+      <c r="N29" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L29*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K29,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
         <v>203</v>
       </c>
@@ -19192,8 +20149,22 @@
       <c r="J30" s="21" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="31" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K30" s="51" t="s">
+        <v>1274</v>
+      </c>
+      <c r="L30" s="52">
+        <v>0.4</v>
+      </c>
+      <c r="M30" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K30,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>4</v>
+      </c>
+      <c r="N30" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L30*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K30,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2.66</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="16" t="s">
         <v>206</v>
       </c>
@@ -19227,8 +20198,22 @@
       <c r="J31" s="21" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="32" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K31" s="51" t="s">
+        <v>1271</v>
+      </c>
+      <c r="L31" s="52">
+        <v>-0.6</v>
+      </c>
+      <c r="M31" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K31,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>3</v>
+      </c>
+      <c r="N31" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L31*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K31,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2.08</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="16" t="s">
         <v>211</v>
       </c>
@@ -19262,8 +20247,22 @@
       <c r="J32" s="21" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="33" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K32" s="51" t="s">
+        <v>1274</v>
+      </c>
+      <c r="L32" s="52">
+        <v>0.6</v>
+      </c>
+      <c r="M32" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K32,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>4</v>
+      </c>
+      <c r="N32" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L32*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K32,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2.74</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="16" t="s">
         <v>214</v>
       </c>
@@ -19297,8 +20296,22 @@
       <c r="J33" s="21" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="34" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K33" s="51" t="s">
+        <v>1271</v>
+      </c>
+      <c r="L33" s="52">
+        <v>-0.7</v>
+      </c>
+      <c r="M33" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K33,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>3</v>
+      </c>
+      <c r="N33" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L33*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K33,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2.0099999999999998</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="16" t="s">
         <v>219</v>
       </c>
@@ -19332,8 +20345,22 @@
       <c r="J34" s="21" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="35" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K34" s="51" t="s">
+        <v>1268</v>
+      </c>
+      <c r="L34" s="52">
+        <v>0.7</v>
+      </c>
+      <c r="M34" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K34,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>2</v>
+      </c>
+      <c r="N34" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L34*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K34,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="16" t="s">
         <v>222</v>
       </c>
@@ -19367,8 +20394,22 @@
       <c r="J35" s="21" t="s">
         <v>226</v>
       </c>
-    </row>
-    <row r="36" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K35" s="51" t="s">
+        <v>1268</v>
+      </c>
+      <c r="L35" s="52">
+        <v>-0.7</v>
+      </c>
+      <c r="M35" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K35,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>2</v>
+      </c>
+      <c r="N35" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L35*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K35,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="16" t="s">
         <v>227</v>
       </c>
@@ -19402,8 +20443,22 @@
       <c r="J36" s="21" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="37" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K36" s="51" t="s">
+        <v>1268</v>
+      </c>
+      <c r="L36" s="52">
+        <v>0.4</v>
+      </c>
+      <c r="M36" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K36,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>2</v>
+      </c>
+      <c r="N36" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L36*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K36,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="16" t="s">
         <v>230</v>
       </c>
@@ -19437,8 +20492,22 @@
       <c r="J37" s="21" t="s">
         <v>234</v>
       </c>
-    </row>
-    <row r="38" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K37" s="51" t="s">
+        <v>1271</v>
+      </c>
+      <c r="L37" s="52">
+        <v>-0.5</v>
+      </c>
+      <c r="M37" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K37,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>3</v>
+      </c>
+      <c r="N37" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L37*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K37,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2.15</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="16" t="s">
         <v>235</v>
       </c>
@@ -19472,8 +20541,22 @@
       <c r="J38" s="21" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="39" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K38" s="51" t="s">
+        <v>1268</v>
+      </c>
+      <c r="L38" s="52">
+        <v>-0.6</v>
+      </c>
+      <c r="M38" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K38,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>2</v>
+      </c>
+      <c r="N38" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L38*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K38,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="16" t="s">
         <v>238</v>
       </c>
@@ -19507,8 +20590,22 @@
       <c r="J39" s="21" t="s">
         <v>242</v>
       </c>
-    </row>
-    <row r="40" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K39" s="51" t="s">
+        <v>1265</v>
+      </c>
+      <c r="L39" s="52">
+        <v>0.5</v>
+      </c>
+      <c r="M39" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K39,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>1</v>
+      </c>
+      <c r="N39" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L39*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K39,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="16" t="s">
         <v>243</v>
       </c>
@@ -19542,8 +20639,22 @@
       <c r="J40" s="21" t="s">
         <v>247</v>
       </c>
-    </row>
-    <row r="41" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K40" s="51" t="s">
+        <v>1268</v>
+      </c>
+      <c r="L40" s="52">
+        <v>-0.4</v>
+      </c>
+      <c r="M40" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K40,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>2</v>
+      </c>
+      <c r="N40" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L40*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K40,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="16" t="s">
         <v>246</v>
       </c>
@@ -19577,8 +20688,22 @@
       <c r="J41" s="21" t="s">
         <v>250</v>
       </c>
-    </row>
-    <row r="42" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K41" s="51" t="s">
+        <v>1268</v>
+      </c>
+      <c r="L41" s="52">
+        <v>0.5</v>
+      </c>
+      <c r="M41" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K41,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>2</v>
+      </c>
+      <c r="N41" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L41*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K41,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="16" t="s">
         <v>251</v>
       </c>
@@ -19612,8 +20737,22 @@
       <c r="J42" s="21" t="s">
         <v>255</v>
       </c>
-    </row>
-    <row r="43" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K42" s="51" t="s">
+        <v>1268</v>
+      </c>
+      <c r="L42" s="52">
+        <v>0.3</v>
+      </c>
+      <c r="M42" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K42,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>2</v>
+      </c>
+      <c r="N42" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L42*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K42,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="16" t="s">
         <v>254</v>
       </c>
@@ -19647,8 +20786,22 @@
       <c r="J43" s="21" t="s">
         <v>258</v>
       </c>
-    </row>
-    <row r="44" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K43" s="51" t="s">
+        <v>1274</v>
+      </c>
+      <c r="L43" s="52">
+        <v>-0.2</v>
+      </c>
+      <c r="M43" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K43,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>4</v>
+      </c>
+      <c r="N43" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L43*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K43,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2.42</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="16" t="s">
         <v>259</v>
       </c>
@@ -19682,8 +20835,22 @@
       <c r="J44" s="21" t="s">
         <v>263</v>
       </c>
-    </row>
-    <row r="45" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K44" s="51" t="s">
+        <v>1268</v>
+      </c>
+      <c r="L44" s="52">
+        <v>-0.5</v>
+      </c>
+      <c r="M44" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K44,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>2</v>
+      </c>
+      <c r="N44" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L44*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K44,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="16" t="s">
         <v>262</v>
       </c>
@@ -19717,8 +20884,22 @@
       <c r="J45" s="21" t="s">
         <v>266</v>
       </c>
-    </row>
-    <row r="46" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K45" s="51" t="s">
+        <v>1268</v>
+      </c>
+      <c r="L45" s="52">
+        <v>0.6</v>
+      </c>
+      <c r="M45" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K45,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>2</v>
+      </c>
+      <c r="N45" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L45*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K45,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="16" t="s">
         <v>267</v>
       </c>
@@ -19752,8 +20933,22 @@
       <c r="J46" s="21" t="s">
         <v>271</v>
       </c>
-    </row>
-    <row r="47" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K46" s="51" t="s">
+        <v>1274</v>
+      </c>
+      <c r="L46" s="52">
+        <v>0.4</v>
+      </c>
+      <c r="M46" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K46,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>4</v>
+      </c>
+      <c r="N46" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L46*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K46,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2.66</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="16" t="s">
         <v>270</v>
       </c>
@@ -19787,8 +20982,22 @@
       <c r="J47" s="21" t="s">
         <v>274</v>
       </c>
-    </row>
-    <row r="48" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K47" s="51" t="s">
+        <v>1271</v>
+      </c>
+      <c r="L47" s="52">
+        <v>-0.9</v>
+      </c>
+      <c r="M47" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K47,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>3</v>
+      </c>
+      <c r="N47" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L47*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K47,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>1.87</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="16" t="s">
         <v>275</v>
       </c>
@@ -19822,8 +21031,22 @@
       <c r="J48" s="21" t="s">
         <v>279</v>
       </c>
-    </row>
-    <row r="49" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K48" s="51" t="s">
+        <v>1274</v>
+      </c>
+      <c r="L48" s="52">
+        <v>0.6</v>
+      </c>
+      <c r="M48" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K48,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>4</v>
+      </c>
+      <c r="N48" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L48*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K48,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2.74</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="16" t="s">
         <v>278</v>
       </c>
@@ -19857,8 +21080,22 @@
       <c r="J49" s="21" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="50" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K49" s="51" t="s">
+        <v>1265</v>
+      </c>
+      <c r="L49" s="52">
+        <v>-1</v>
+      </c>
+      <c r="M49" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K49,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>1</v>
+      </c>
+      <c r="N49" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L49*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K49,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="16" t="s">
         <v>283</v>
       </c>
@@ -19892,8 +21129,22 @@
       <c r="J50" s="21" t="s">
         <v>287</v>
       </c>
-    </row>
-    <row r="51" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K50" s="51" t="s">
+        <v>1271</v>
+      </c>
+      <c r="L50" s="52">
+        <v>-0.5</v>
+      </c>
+      <c r="M50" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K50,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>3</v>
+      </c>
+      <c r="N50" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L50*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K50,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2.15</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="16" t="s">
         <v>286</v>
       </c>
@@ -19927,8 +21178,22 @@
       <c r="J51" s="21" t="s">
         <v>290</v>
       </c>
-    </row>
-    <row r="52" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K51" s="51" t="s">
+        <v>1265</v>
+      </c>
+      <c r="L51" s="52">
+        <v>0.3</v>
+      </c>
+      <c r="M51" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K51,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>1</v>
+      </c>
+      <c r="N51" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L51*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K51,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2.95</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="16" t="s">
         <v>291</v>
       </c>
@@ -19962,8 +21227,22 @@
       <c r="J52" s="21" t="s">
         <v>295</v>
       </c>
-    </row>
-    <row r="53" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K52" s="51" t="s">
+        <v>1268</v>
+      </c>
+      <c r="L52" s="52">
+        <v>0.8</v>
+      </c>
+      <c r="M52" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K52,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>2</v>
+      </c>
+      <c r="N52" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L52*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K52,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="16" t="s">
         <v>294</v>
       </c>
@@ -19997,8 +21276,22 @@
       <c r="J53" s="21" t="s">
         <v>298</v>
       </c>
-    </row>
-    <row r="54" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K53" s="51" t="s">
+        <v>1268</v>
+      </c>
+      <c r="L53" s="52">
+        <v>-0.8</v>
+      </c>
+      <c r="M53" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K53,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>2</v>
+      </c>
+      <c r="N53" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L53*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K53,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="16" t="s">
         <v>299</v>
       </c>
@@ -20032,8 +21325,22 @@
       <c r="J54" s="21" t="s">
         <v>303</v>
       </c>
-    </row>
-    <row r="55" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K54" s="51" t="s">
+        <v>1268</v>
+      </c>
+      <c r="L54" s="52">
+        <v>-0.4</v>
+      </c>
+      <c r="M54" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K54,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>2</v>
+      </c>
+      <c r="N54" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L54*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K54,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="16" t="s">
         <v>302</v>
       </c>
@@ -20067,8 +21374,22 @@
       <c r="J55" s="21" t="s">
         <v>306</v>
       </c>
-    </row>
-    <row r="56" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K55" s="51" t="s">
+        <v>1265</v>
+      </c>
+      <c r="L55" s="52">
+        <v>0.7</v>
+      </c>
+      <c r="M55" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K55,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>1</v>
+      </c>
+      <c r="N55" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L55*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K55,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>3.55</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="16" t="s">
         <v>307</v>
       </c>
@@ -20102,8 +21423,22 @@
       <c r="J56" s="21" t="s">
         <v>311</v>
       </c>
-    </row>
-    <row r="57" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K56" s="51" t="s">
+        <v>1271</v>
+      </c>
+      <c r="L56" s="52">
+        <v>0.5</v>
+      </c>
+      <c r="M56" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K56,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>3</v>
+      </c>
+      <c r="N56" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L56*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K56,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2.85</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="16" t="s">
         <v>310</v>
       </c>
@@ -20137,8 +21472,22 @@
       <c r="J57" s="21" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="58" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K57" s="51" t="s">
+        <v>1271</v>
+      </c>
+      <c r="L57" s="52">
+        <v>-0.4</v>
+      </c>
+      <c r="M57" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K57,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>3</v>
+      </c>
+      <c r="N57" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L57*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K57,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2.2200000000000002</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="16" t="s">
         <v>315</v>
       </c>
@@ -20172,8 +21521,22 @@
       <c r="J58" s="21" t="s">
         <v>319</v>
       </c>
-    </row>
-    <row r="59" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K58" s="51" t="s">
+        <v>1274</v>
+      </c>
+      <c r="L58" s="52">
+        <v>0.5</v>
+      </c>
+      <c r="M58" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K58,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>4</v>
+      </c>
+      <c r="N58" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L58*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K58,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="16" t="s">
         <v>318</v>
       </c>
@@ -20207,8 +21570,22 @@
       <c r="J59" s="21" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="60" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K59" s="51" t="s">
+        <v>1268</v>
+      </c>
+      <c r="L59" s="52">
+        <v>-0.6</v>
+      </c>
+      <c r="M59" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K59,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>2</v>
+      </c>
+      <c r="N59" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L59*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K59,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="16" t="s">
         <v>323</v>
       </c>
@@ -20242,8 +21619,22 @@
       <c r="J60" s="21" t="s">
         <v>327</v>
       </c>
-    </row>
-    <row r="61" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K60" s="51" t="s">
+        <v>1274</v>
+      </c>
+      <c r="L60" s="52">
+        <v>0.3</v>
+      </c>
+      <c r="M60" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K60,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>4</v>
+      </c>
+      <c r="N60" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L60*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K60,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2.62</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="16" t="s">
         <v>326</v>
       </c>
@@ -20277,8 +21668,22 @@
       <c r="J61" s="21" t="s">
         <v>330</v>
       </c>
-    </row>
-    <row r="62" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K61" s="51" t="s">
+        <v>1271</v>
+      </c>
+      <c r="L61" s="52">
+        <v>-0.9</v>
+      </c>
+      <c r="M61" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K61,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>3</v>
+      </c>
+      <c r="N61" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L61*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K61,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>1.87</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="16" t="s">
         <v>331</v>
       </c>
@@ -20312,8 +21717,22 @@
       <c r="J62" s="21" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="63" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K62" s="51" t="s">
+        <v>1268</v>
+      </c>
+      <c r="L62" s="52">
+        <v>0.4</v>
+      </c>
+      <c r="M62" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K62,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>2</v>
+      </c>
+      <c r="N62" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L62*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K62,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="16" t="s">
         <v>334</v>
       </c>
@@ -20347,8 +21766,22 @@
       <c r="J63" s="21" t="s">
         <v>338</v>
       </c>
-    </row>
-    <row r="64" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K63" s="51" t="s">
+        <v>1268</v>
+      </c>
+      <c r="L63" s="52">
+        <v>-0.5</v>
+      </c>
+      <c r="M63" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K63,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>2</v>
+      </c>
+      <c r="N63" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L63*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K63,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="16" t="s">
         <v>339</v>
       </c>
@@ -20382,8 +21815,22 @@
       <c r="J64" s="21" t="s">
         <v>343</v>
       </c>
-    </row>
-    <row r="65" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K64" s="51" t="s">
+        <v>1268</v>
+      </c>
+      <c r="L64" s="52">
+        <v>-0.3</v>
+      </c>
+      <c r="M64" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K64,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>2</v>
+      </c>
+      <c r="N64" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L64*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K64,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="16" t="s">
         <v>342</v>
       </c>
@@ -20417,8 +21864,22 @@
       <c r="J65" s="21" t="s">
         <v>346</v>
       </c>
-    </row>
-    <row r="66" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K65" s="51" t="s">
+        <v>1274</v>
+      </c>
+      <c r="L65" s="52">
+        <v>0.3</v>
+      </c>
+      <c r="M65" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K65,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>4</v>
+      </c>
+      <c r="N65" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L65*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K65,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2.62</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="16" t="s">
         <v>347</v>
       </c>
@@ -20452,8 +21913,22 @@
       <c r="J66" s="21" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="67" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K66" s="51" t="s">
+        <v>1265</v>
+      </c>
+      <c r="L66" s="52">
+        <v>1</v>
+      </c>
+      <c r="M66" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K66,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>1</v>
+      </c>
+      <c r="N66" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L66*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K66,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="16" t="s">
         <v>350</v>
       </c>
@@ -20487,8 +21962,22 @@
       <c r="J67" s="21" t="s">
         <v>354</v>
       </c>
-    </row>
-    <row r="68" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K67" s="51" t="s">
+        <v>1268</v>
+      </c>
+      <c r="L67" s="52">
+        <v>-0.2</v>
+      </c>
+      <c r="M67" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K67,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>2</v>
+      </c>
+      <c r="N67" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L67*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K67,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="16" t="s">
         <v>355</v>
       </c>
@@ -20522,8 +22011,22 @@
       <c r="J68" s="21" t="s">
         <v>359</v>
       </c>
-    </row>
-    <row r="69" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K68" s="51" t="s">
+        <v>1268</v>
+      </c>
+      <c r="L68" s="52">
+        <v>0.5</v>
+      </c>
+      <c r="M68" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K68,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>2</v>
+      </c>
+      <c r="N68" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L68*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K68,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="16" t="s">
         <v>358</v>
       </c>
@@ -20557,8 +22060,22 @@
       <c r="J69" s="21" t="s">
         <v>362</v>
       </c>
-    </row>
-    <row r="70" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K69" s="51" t="s">
+        <v>1271</v>
+      </c>
+      <c r="L69" s="52">
+        <v>-0.6</v>
+      </c>
+      <c r="M69" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K69,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>3</v>
+      </c>
+      <c r="N69" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L69*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K69,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2.08</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="16" t="s">
         <v>363</v>
       </c>
@@ -20592,8 +22109,22 @@
       <c r="J70" s="21" t="s">
         <v>367</v>
       </c>
-    </row>
-    <row r="71" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K70" s="51" t="s">
+        <v>1274</v>
+      </c>
+      <c r="L70" s="52">
+        <v>0.3</v>
+      </c>
+      <c r="M70" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K70,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>4</v>
+      </c>
+      <c r="N70" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L70*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K70,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2.62</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="16" t="s">
         <v>366</v>
       </c>
@@ -20627,8 +22158,22 @@
       <c r="J71" s="21" t="s">
         <v>370</v>
       </c>
-    </row>
-    <row r="72" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K71" s="51" t="s">
+        <v>1265</v>
+      </c>
+      <c r="L71" s="52">
+        <v>-0.4</v>
+      </c>
+      <c r="M71" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K71,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>1</v>
+      </c>
+      <c r="N71" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L71*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K71,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="72" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="16" t="s">
         <v>371</v>
       </c>
@@ -20662,8 +22207,22 @@
       <c r="J72" s="21" t="s">
         <v>375</v>
       </c>
-    </row>
-    <row r="73" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K72" s="51" t="s">
+        <v>1268</v>
+      </c>
+      <c r="L72" s="52">
+        <v>-0.3</v>
+      </c>
+      <c r="M72" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K72,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>2</v>
+      </c>
+      <c r="N72" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L72*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K72,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="16" t="s">
         <v>374</v>
       </c>
@@ -20697,8 +22256,22 @@
       <c r="J73" s="21" t="s">
         <v>378</v>
       </c>
-    </row>
-    <row r="74" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K73" s="51" t="s">
+        <v>1265</v>
+      </c>
+      <c r="L73" s="52">
+        <v>0.9</v>
+      </c>
+      <c r="M73" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K73,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>1</v>
+      </c>
+      <c r="N73" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L73*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K73,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>3.85</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="16" t="s">
         <v>379</v>
       </c>
@@ -20732,8 +22305,22 @@
       <c r="J74" s="21" t="s">
         <v>383</v>
       </c>
-    </row>
-    <row r="75" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K74" s="51" t="s">
+        <v>1265</v>
+      </c>
+      <c r="L74" s="52">
+        <v>1</v>
+      </c>
+      <c r="M74" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K74,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>1</v>
+      </c>
+      <c r="N74" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L74*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K74,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="16" t="s">
         <v>382</v>
       </c>
@@ -20767,8 +22354,22 @@
       <c r="J75" s="21" t="s">
         <v>386</v>
       </c>
-    </row>
-    <row r="76" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K75" s="51" t="s">
+        <v>1271</v>
+      </c>
+      <c r="L75" s="52">
+        <v>-1</v>
+      </c>
+      <c r="M75" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K75,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>3</v>
+      </c>
+      <c r="N75" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L75*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K75,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="76" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="16" t="s">
         <v>387</v>
       </c>
@@ -20802,8 +22403,22 @@
       <c r="J76" s="21" t="s">
         <v>391</v>
       </c>
-    </row>
-    <row r="77" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K76" s="51" t="s">
+        <v>1271</v>
+      </c>
+      <c r="L76" s="52">
+        <v>-0.5</v>
+      </c>
+      <c r="M76" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K76,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>3</v>
+      </c>
+      <c r="N76" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L76*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K76,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2.15</v>
+      </c>
+    </row>
+    <row r="77" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="16" t="s">
         <v>390</v>
       </c>
@@ -20837,8 +22452,22 @@
       <c r="J77" s="21" t="s">
         <v>394</v>
       </c>
-    </row>
-    <row r="78" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K77" s="51" t="s">
+        <v>1265</v>
+      </c>
+      <c r="L77" s="52">
+        <v>0.4</v>
+      </c>
+      <c r="M77" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K77,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>1</v>
+      </c>
+      <c r="N77" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L77*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K77,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="16" t="s">
         <v>395</v>
       </c>
@@ -20872,8 +22501,22 @@
       <c r="J78" s="21" t="s">
         <v>399</v>
       </c>
-    </row>
-    <row r="79" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K78" s="51" t="s">
+        <v>1274</v>
+      </c>
+      <c r="L78" s="52">
+        <v>0.2</v>
+      </c>
+      <c r="M78" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K78,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>4</v>
+      </c>
+      <c r="N78" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L78*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K78,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2.58</v>
+      </c>
+    </row>
+    <row r="79" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="16" t="s">
         <v>398</v>
       </c>
@@ -20907,8 +22550,22 @@
       <c r="J79" s="21" t="s">
         <v>402</v>
       </c>
-    </row>
-    <row r="80" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K79" s="51" t="s">
+        <v>1268</v>
+      </c>
+      <c r="L79" s="52">
+        <v>-0.5</v>
+      </c>
+      <c r="M79" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K79,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>2</v>
+      </c>
+      <c r="N79" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L79*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K79,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="16" t="s">
         <v>403</v>
       </c>
@@ -20942,8 +22599,22 @@
       <c r="J80" s="21" t="s">
         <v>407</v>
       </c>
-    </row>
-    <row r="81" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K80" s="51" t="s">
+        <v>1268</v>
+      </c>
+      <c r="L80" s="52">
+        <v>0.9</v>
+      </c>
+      <c r="M80" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K80,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>2</v>
+      </c>
+      <c r="N80" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L80*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K80,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="81" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="16" t="s">
         <v>406</v>
       </c>
@@ -20977,8 +22648,22 @@
       <c r="J81" s="21" t="s">
         <v>410</v>
       </c>
-    </row>
-    <row r="82" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K81" s="51" t="s">
+        <v>1268</v>
+      </c>
+      <c r="L81" s="52">
+        <v>-0.9</v>
+      </c>
+      <c r="M81" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K81,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>2</v>
+      </c>
+      <c r="N81" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L81*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K81,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="82" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="16" t="s">
         <v>411</v>
       </c>
@@ -21012,8 +22697,22 @@
       <c r="J82" s="21" t="s">
         <v>415</v>
       </c>
-    </row>
-    <row r="83" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K82" s="51" t="s">
+        <v>1268</v>
+      </c>
+      <c r="L82" s="52">
+        <v>0.5</v>
+      </c>
+      <c r="M82" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K82,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>2</v>
+      </c>
+      <c r="N82" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L82*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K82,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="83" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="16" t="s">
         <v>414</v>
       </c>
@@ -21047,8 +22746,22 @@
       <c r="J83" s="21" t="s">
         <v>418</v>
       </c>
-    </row>
-    <row r="84" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K83" s="51" t="s">
+        <v>1268</v>
+      </c>
+      <c r="L83" s="52">
+        <v>-0.4</v>
+      </c>
+      <c r="M83" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K83,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>2</v>
+      </c>
+      <c r="N83" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L83*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K83,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="16" t="s">
         <v>419</v>
       </c>
@@ -21082,8 +22795,22 @@
       <c r="J84" s="21" t="s">
         <v>423</v>
       </c>
-    </row>
-    <row r="85" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K84" s="51" t="s">
+        <v>1274</v>
+      </c>
+      <c r="L84" s="52">
+        <v>-0.2</v>
+      </c>
+      <c r="M84" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K84,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>4</v>
+      </c>
+      <c r="N84" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L84*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K84,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2.42</v>
+      </c>
+    </row>
+    <row r="85" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="16" t="s">
         <v>422</v>
       </c>
@@ -21117,8 +22844,22 @@
       <c r="J85" s="21" t="s">
         <v>426</v>
       </c>
-    </row>
-    <row r="86" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K85" s="51" t="s">
+        <v>1265</v>
+      </c>
+      <c r="L85" s="52">
+        <v>0.6</v>
+      </c>
+      <c r="M85" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K85,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>1</v>
+      </c>
+      <c r="N85" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L85*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K85,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="86" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="16" t="s">
         <v>427</v>
       </c>
@@ -21152,8 +22893,22 @@
       <c r="J86" s="21" t="s">
         <v>431</v>
       </c>
-    </row>
-    <row r="87" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K86" s="51" t="s">
+        <v>1271</v>
+      </c>
+      <c r="L86" s="52">
+        <v>-0.7</v>
+      </c>
+      <c r="M86" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K86,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>3</v>
+      </c>
+      <c r="N86" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L86*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K86,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2.0099999999999998</v>
+      </c>
+    </row>
+    <row r="87" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="16" t="s">
         <v>430</v>
       </c>
@@ -21187,8 +22942,22 @@
       <c r="J87" s="21" t="s">
         <v>434</v>
       </c>
-    </row>
-    <row r="88" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K87" s="51" t="s">
+        <v>1265</v>
+      </c>
+      <c r="L87" s="52">
+        <v>0.5</v>
+      </c>
+      <c r="M87" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K87,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>1</v>
+      </c>
+      <c r="N87" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L87*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K87,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="88" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="16" t="s">
         <v>435</v>
       </c>
@@ -21222,8 +22991,22 @@
       <c r="J88" s="21" t="s">
         <v>439</v>
       </c>
-    </row>
-    <row r="89" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K88" s="51" t="s">
+        <v>1268</v>
+      </c>
+      <c r="L88" s="52">
+        <v>-0.6</v>
+      </c>
+      <c r="M88" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K88,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>2</v>
+      </c>
+      <c r="N88" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L88*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K88,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="89" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="16" t="s">
         <v>438</v>
       </c>
@@ -21257,8 +23040,22 @@
       <c r="J89" s="21" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="90" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K89" s="51" t="s">
+        <v>1265</v>
+      </c>
+      <c r="L89" s="52">
+        <v>0.5</v>
+      </c>
+      <c r="M89" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K89,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>1</v>
+      </c>
+      <c r="N89" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L89*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K89,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="90" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="16" t="s">
         <v>443</v>
       </c>
@@ -21292,8 +23089,22 @@
       <c r="J90" s="21" t="s">
         <v>447</v>
       </c>
-    </row>
-    <row r="91" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K90" s="51" t="s">
+        <v>1268</v>
+      </c>
+      <c r="L90" s="52">
+        <v>1</v>
+      </c>
+      <c r="M90" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K90,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>2</v>
+      </c>
+      <c r="N90" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L90*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K90,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="91" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="16" t="s">
         <v>446</v>
       </c>
@@ -21327,8 +23138,22 @@
       <c r="J91" s="21" t="s">
         <v>450</v>
       </c>
-    </row>
-    <row r="92" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K91" s="51" t="s">
+        <v>1271</v>
+      </c>
+      <c r="L91" s="52">
+        <v>-0.8</v>
+      </c>
+      <c r="M91" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K91,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>3</v>
+      </c>
+      <c r="N91" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L91*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K91,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>1.94</v>
+      </c>
+    </row>
+    <row r="92" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="16" t="s">
         <v>451</v>
       </c>
@@ -21362,8 +23187,22 @@
       <c r="J92" s="21" t="s">
         <v>455</v>
       </c>
-    </row>
-    <row r="93" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K92" s="51" t="s">
+        <v>1274</v>
+      </c>
+      <c r="L92" s="52">
+        <v>0.4</v>
+      </c>
+      <c r="M92" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K92,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>4</v>
+      </c>
+      <c r="N92" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L92*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K92,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2.66</v>
+      </c>
+    </row>
+    <row r="93" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="16" t="s">
         <v>454</v>
       </c>
@@ -21397,8 +23236,22 @@
       <c r="J93" s="21" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="94" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K93" s="51" t="s">
+        <v>1268</v>
+      </c>
+      <c r="L93" s="52">
+        <v>-0.4</v>
+      </c>
+      <c r="M93" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K93,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>2</v>
+      </c>
+      <c r="N93" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L93*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K93,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="16" t="s">
         <v>459</v>
       </c>
@@ -21432,8 +23285,22 @@
       <c r="J94" s="21" t="s">
         <v>463</v>
       </c>
-    </row>
-    <row r="95" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K94" s="51" t="s">
+        <v>1268</v>
+      </c>
+      <c r="L94" s="52">
+        <v>-0.3</v>
+      </c>
+      <c r="M94" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K94,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>2</v>
+      </c>
+      <c r="N94" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L94*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K94,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="95" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="16" t="s">
         <v>462</v>
       </c>
@@ -21467,8 +23334,22 @@
       <c r="J95" s="21" t="s">
         <v>466</v>
       </c>
-    </row>
-    <row r="96" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K95" s="51" t="s">
+        <v>1265</v>
+      </c>
+      <c r="L95" s="52">
+        <v>0.4</v>
+      </c>
+      <c r="M95" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K95,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>1</v>
+      </c>
+      <c r="N95" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L95*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K95,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="16" t="s">
         <v>467</v>
       </c>
@@ -21502,8 +23383,22 @@
       <c r="J96" s="21" t="s">
         <v>471</v>
       </c>
-    </row>
-    <row r="97" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K96" s="51" t="s">
+        <v>1274</v>
+      </c>
+      <c r="L96" s="52">
+        <v>0.6</v>
+      </c>
+      <c r="M96" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K96,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>4</v>
+      </c>
+      <c r="N96" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L96*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K96,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2.74</v>
+      </c>
+    </row>
+    <row r="97" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="16" t="s">
         <v>470</v>
       </c>
@@ -21537,8 +23432,22 @@
       <c r="J97" s="21" t="s">
         <v>474</v>
       </c>
-    </row>
-    <row r="98" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K97" s="51" t="s">
+        <v>1265</v>
+      </c>
+      <c r="L97" s="52">
+        <v>-0.7</v>
+      </c>
+      <c r="M97" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K97,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>1</v>
+      </c>
+      <c r="N97" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L97*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K97,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="98" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="16" t="s">
         <v>475</v>
       </c>
@@ -21572,8 +23481,22 @@
       <c r="J98" s="21" t="s">
         <v>479</v>
       </c>
-    </row>
-    <row r="99" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K98" s="51" t="s">
+        <v>1274</v>
+      </c>
+      <c r="L98" s="52">
+        <v>-0.3</v>
+      </c>
+      <c r="M98" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K98,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>4</v>
+      </c>
+      <c r="N98" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L98*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K98,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2.38</v>
+      </c>
+    </row>
+    <row r="99" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="16" t="s">
         <v>478</v>
       </c>
@@ -21607,8 +23530,22 @@
       <c r="J99" s="21" t="s">
         <v>482</v>
       </c>
-    </row>
-    <row r="100" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K99" s="51" t="s">
+        <v>1268</v>
+      </c>
+      <c r="L99" s="52">
+        <v>0.6</v>
+      </c>
+      <c r="M99" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K99,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>2</v>
+      </c>
+      <c r="N99" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L99*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K99,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="16" t="s">
         <v>483</v>
       </c>
@@ -21642,8 +23579,22 @@
       <c r="J100" s="21" t="s">
         <v>487</v>
       </c>
-    </row>
-    <row r="101" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K100" s="51" t="s">
+        <v>1268</v>
+      </c>
+      <c r="L100" s="52">
+        <v>-0.4</v>
+      </c>
+      <c r="M100" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K100,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>2</v>
+      </c>
+      <c r="N100" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L100*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K100,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="16" t="s">
         <v>486</v>
       </c>
@@ -21677,8 +23628,22 @@
       <c r="J101" s="21" t="s">
         <v>490</v>
       </c>
-    </row>
-    <row r="102" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K101" s="51" t="s">
+        <v>1268</v>
+      </c>
+      <c r="L101" s="52">
+        <v>0.5</v>
+      </c>
+      <c r="M101" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K101,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>2</v>
+      </c>
+      <c r="N101" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L101*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K101,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="16" t="s">
         <v>491</v>
       </c>
@@ -21712,8 +23677,22 @@
       <c r="J102" s="21" t="s">
         <v>495</v>
       </c>
-    </row>
-    <row r="103" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K102" s="51" t="s">
+        <v>1271</v>
+      </c>
+      <c r="L102" s="52">
+        <v>-0.5</v>
+      </c>
+      <c r="M102" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K102,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>3</v>
+      </c>
+      <c r="N102" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L102*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K102,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2.15</v>
+      </c>
+    </row>
+    <row r="103" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="16" t="s">
         <v>494</v>
       </c>
@@ -21747,8 +23726,22 @@
       <c r="J103" s="21" t="s">
         <v>498</v>
       </c>
-    </row>
-    <row r="104" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K103" s="51" t="s">
+        <v>1268</v>
+      </c>
+      <c r="L103" s="52">
+        <v>0.6</v>
+      </c>
+      <c r="M103" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K103,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>2</v>
+      </c>
+      <c r="N103" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L103*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K103,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="16" t="s">
         <v>499</v>
       </c>
@@ -21782,8 +23775,22 @@
       <c r="J104" s="21" t="s">
         <v>503</v>
       </c>
-    </row>
-    <row r="105" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K104" s="51" t="s">
+        <v>1274</v>
+      </c>
+      <c r="L104" s="52">
+        <v>-0.2</v>
+      </c>
+      <c r="M104" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K104,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>4</v>
+      </c>
+      <c r="N104" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L104*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K104,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2.42</v>
+      </c>
+    </row>
+    <row r="105" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="16" t="s">
         <v>502</v>
       </c>
@@ -21817,8 +23824,22 @@
       <c r="J105" s="21" t="s">
         <v>506</v>
       </c>
-    </row>
-    <row r="106" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K105" s="51" t="s">
+        <v>1265</v>
+      </c>
+      <c r="L105" s="52">
+        <v>0.7</v>
+      </c>
+      <c r="M105" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K105,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>1</v>
+      </c>
+      <c r="N105" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L105*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K105,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>3.55</v>
+      </c>
+    </row>
+    <row r="106" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="16" t="s">
         <v>507</v>
       </c>
@@ -21852,8 +23873,22 @@
       <c r="J106" s="21" t="s">
         <v>511</v>
       </c>
-    </row>
-    <row r="107" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K106" s="51" t="s">
+        <v>1271</v>
+      </c>
+      <c r="L106" s="52">
+        <v>-0.4</v>
+      </c>
+      <c r="M106" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K106,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>3</v>
+      </c>
+      <c r="N106" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L106*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K106,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2.2200000000000002</v>
+      </c>
+    </row>
+    <row r="107" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="16" t="s">
         <v>510</v>
       </c>
@@ -21887,8 +23922,22 @@
       <c r="J107" s="21" t="s">
         <v>514</v>
       </c>
-    </row>
-    <row r="108" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K107" s="51" t="s">
+        <v>1265</v>
+      </c>
+      <c r="L107" s="52">
+        <v>0.5</v>
+      </c>
+      <c r="M107" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K107,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>1</v>
+      </c>
+      <c r="N107" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L107*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K107,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="108" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="16" t="s">
         <v>515</v>
       </c>
@@ -21922,8 +23971,22 @@
       <c r="J108" s="21" t="s">
         <v>519</v>
       </c>
-    </row>
-    <row r="109" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K108" s="51" t="s">
+        <v>1265</v>
+      </c>
+      <c r="L108" s="52">
+        <v>1</v>
+      </c>
+      <c r="M108" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K108,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>1</v>
+      </c>
+      <c r="N108" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L108*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K108,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="109" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="16" t="s">
         <v>518</v>
       </c>
@@ -21957,8 +24020,22 @@
       <c r="J109" s="21" t="s">
         <v>522</v>
       </c>
-    </row>
-    <row r="110" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K109" s="51" t="s">
+        <v>1268</v>
+      </c>
+      <c r="L109" s="52">
+        <v>-0.5</v>
+      </c>
+      <c r="M109" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K109,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>2</v>
+      </c>
+      <c r="N109" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L109*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K109,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="110" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="16" t="s">
         <v>523</v>
       </c>
@@ -21992,8 +24069,22 @@
       <c r="J110" s="21" t="s">
         <v>526</v>
       </c>
-    </row>
-    <row r="111" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K110" s="51" t="s">
+        <v>1274</v>
+      </c>
+      <c r="L110" s="52">
+        <v>-0.4</v>
+      </c>
+      <c r="M110" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K110,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>4</v>
+      </c>
+      <c r="N110" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L110*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K110,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2.34</v>
+      </c>
+    </row>
+    <row r="111" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="16" t="s">
         <v>525</v>
       </c>
@@ -22027,8 +24118,22 @@
       <c r="J111" s="21" t="s">
         <v>529</v>
       </c>
-    </row>
-    <row r="112" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K111" s="51" t="s">
+        <v>1265</v>
+      </c>
+      <c r="L111" s="52">
+        <v>0.6</v>
+      </c>
+      <c r="M111" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K111,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>1</v>
+      </c>
+      <c r="N111" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L111*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K111,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="112" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="16" t="s">
         <v>530</v>
       </c>
@@ -22062,8 +24167,22 @@
       <c r="J112" s="21" t="s">
         <v>534</v>
       </c>
-    </row>
-    <row r="113" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K112" s="51" t="s">
+        <v>1271</v>
+      </c>
+      <c r="L112" s="52">
+        <v>-0.4</v>
+      </c>
+      <c r="M112" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K112,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>3</v>
+      </c>
+      <c r="N112" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L112*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K112,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2.2200000000000002</v>
+      </c>
+    </row>
+    <row r="113" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="16" t="s">
         <v>533</v>
       </c>
@@ -22097,8 +24216,22 @@
       <c r="J113" s="21" t="s">
         <v>537</v>
       </c>
-    </row>
-    <row r="114" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K113" s="51" t="s">
+        <v>1274</v>
+      </c>
+      <c r="L113" s="52">
+        <v>0.4</v>
+      </c>
+      <c r="M113" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K113,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>4</v>
+      </c>
+      <c r="N113" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L113*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K113,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2.66</v>
+      </c>
+    </row>
+    <row r="114" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="16" t="s">
         <v>538</v>
       </c>
@@ -22132,8 +24265,22 @@
       <c r="J114" s="21" t="s">
         <v>542</v>
       </c>
-    </row>
-    <row r="115" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K114" s="51" t="s">
+        <v>1268</v>
+      </c>
+      <c r="L114" s="52">
+        <v>0.3</v>
+      </c>
+      <c r="M114" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K114,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>2</v>
+      </c>
+      <c r="N114" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L114*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K114,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="115" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="16" t="s">
         <v>541</v>
       </c>
@@ -22167,8 +24314,22 @@
       <c r="J115" s="21" t="s">
         <v>545</v>
       </c>
-    </row>
-    <row r="116" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K115" s="51" t="s">
+        <v>1265</v>
+      </c>
+      <c r="L115" s="52">
+        <v>-0.7</v>
+      </c>
+      <c r="M115" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K115,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>1</v>
+      </c>
+      <c r="N115" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L115*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K115,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="116" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="16" t="s">
         <v>546</v>
       </c>
@@ -22202,8 +24363,22 @@
       <c r="J116" s="21" t="s">
         <v>550</v>
       </c>
-    </row>
-    <row r="117" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K116" s="51" t="s">
+        <v>1265</v>
+      </c>
+      <c r="L116" s="52">
+        <v>0.8</v>
+      </c>
+      <c r="M116" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K116,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>1</v>
+      </c>
+      <c r="N116" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L116*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K116,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="117" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="16" t="s">
         <v>549</v>
       </c>
@@ -22237,8 +24412,22 @@
       <c r="J117" s="21" t="s">
         <v>553</v>
       </c>
-    </row>
-    <row r="118" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K117" s="51" t="s">
+        <v>1268</v>
+      </c>
+      <c r="L117" s="52">
+        <v>-0.5</v>
+      </c>
+      <c r="M117" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K117,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>2</v>
+      </c>
+      <c r="N117" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L117*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K117,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="118" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="16" t="s">
         <v>554</v>
       </c>
@@ -22272,8 +24461,22 @@
       <c r="J118" s="21" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="119" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K118" s="51" t="s">
+        <v>1271</v>
+      </c>
+      <c r="L118" s="52">
+        <v>-0.5</v>
+      </c>
+      <c r="M118" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K118,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>3</v>
+      </c>
+      <c r="N118" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L118*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K118,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2.15</v>
+      </c>
+    </row>
+    <row r="119" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="16" t="s">
         <v>557</v>
       </c>
@@ -22307,8 +24510,22 @@
       <c r="J119" s="21" t="s">
         <v>561</v>
       </c>
-    </row>
-    <row r="120" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K119" s="51" t="s">
+        <v>1265</v>
+      </c>
+      <c r="L119" s="52">
+        <v>0.5</v>
+      </c>
+      <c r="M119" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K119,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>1</v>
+      </c>
+      <c r="N119" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L119*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K119,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="120" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="16" t="s">
         <v>562</v>
       </c>
@@ -22342,8 +24559,22 @@
       <c r="J120" s="21" t="s">
         <v>566</v>
       </c>
-    </row>
-    <row r="121" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K120" s="51" t="s">
+        <v>1274</v>
+      </c>
+      <c r="L120" s="52">
+        <v>0.6</v>
+      </c>
+      <c r="M120" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K120,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>4</v>
+      </c>
+      <c r="N120" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L120*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K120,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2.74</v>
+      </c>
+    </row>
+    <row r="121" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="16" t="s">
         <v>565</v>
       </c>
@@ -22377,8 +24608,22 @@
       <c r="J121" s="21" t="s">
         <v>569</v>
       </c>
-    </row>
-    <row r="122" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K121" s="51" t="s">
+        <v>1271</v>
+      </c>
+      <c r="L121" s="52">
+        <v>-0.6</v>
+      </c>
+      <c r="M121" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K121,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>3</v>
+      </c>
+      <c r="N121" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L121*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K121,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2.08</v>
+      </c>
+    </row>
+    <row r="122" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="16" t="s">
         <v>570</v>
       </c>
@@ -22412,8 +24657,22 @@
       <c r="J122" s="21" t="s">
         <v>574</v>
       </c>
-    </row>
-    <row r="123" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K122" s="51" t="s">
+        <v>1271</v>
+      </c>
+      <c r="L122" s="52">
+        <v>-0.7</v>
+      </c>
+      <c r="M122" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K122,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>3</v>
+      </c>
+      <c r="N122" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L122*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K122,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2.0099999999999998</v>
+      </c>
+    </row>
+    <row r="123" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="16" t="s">
         <v>573</v>
       </c>
@@ -22447,8 +24706,22 @@
       <c r="J123" s="21" t="s">
         <v>577</v>
       </c>
-    </row>
-    <row r="124" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K123" s="51" t="s">
+        <v>1268</v>
+      </c>
+      <c r="L123" s="52">
+        <v>0.4</v>
+      </c>
+      <c r="M123" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K123,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>2</v>
+      </c>
+      <c r="N123" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L123*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K123,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="124" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="16" t="s">
         <v>578</v>
       </c>
@@ -22482,8 +24755,22 @@
       <c r="J124" s="21" t="s">
         <v>582</v>
       </c>
-    </row>
-    <row r="125" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K124" s="51" t="s">
+        <v>1268</v>
+      </c>
+      <c r="L124" s="52">
+        <v>0.3</v>
+      </c>
+      <c r="M124" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K124,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>2</v>
+      </c>
+      <c r="N124" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L124*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K124,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="125" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="16" t="s">
         <v>581</v>
       </c>
@@ -22517,8 +24804,22 @@
       <c r="J125" s="21" t="s">
         <v>585</v>
       </c>
-    </row>
-    <row r="126" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K125" s="51" t="s">
+        <v>1274</v>
+      </c>
+      <c r="L125" s="52">
+        <v>-0.3</v>
+      </c>
+      <c r="M125" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K125,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>4</v>
+      </c>
+      <c r="N125" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L125*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K125,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2.38</v>
+      </c>
+    </row>
+    <row r="126" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="16" t="s">
         <v>586</v>
       </c>
@@ -22552,8 +24853,22 @@
       <c r="J126" s="21" t="s">
         <v>590</v>
       </c>
-    </row>
-    <row r="127" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K126" s="51" t="s">
+        <v>1268</v>
+      </c>
+      <c r="L126" s="52">
+        <v>-0.6</v>
+      </c>
+      <c r="M126" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K126,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>2</v>
+      </c>
+      <c r="N126" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L126*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K126,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="127" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="16" t="s">
         <v>589</v>
       </c>
@@ -22587,8 +24902,22 @@
       <c r="J127" s="21" t="s">
         <v>593</v>
       </c>
-    </row>
-    <row r="128" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K127" s="51" t="s">
+        <v>1268</v>
+      </c>
+      <c r="L127" s="52">
+        <v>0.6</v>
+      </c>
+      <c r="M127" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K127,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>2</v>
+      </c>
+      <c r="N127" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L127*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K127,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="128" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="16" t="s">
         <v>594</v>
       </c>
@@ -22622,8 +24951,22 @@
       <c r="J128" s="21" t="s">
         <v>598</v>
       </c>
-    </row>
-    <row r="129" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K128" s="51" t="s">
+        <v>1271</v>
+      </c>
+      <c r="L128" s="52">
+        <v>-0.6</v>
+      </c>
+      <c r="M128" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K128,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>3</v>
+      </c>
+      <c r="N128" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L128*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K128,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2.08</v>
+      </c>
+    </row>
+    <row r="129" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="16" t="s">
         <v>597</v>
       </c>
@@ -22657,8 +25000,22 @@
       <c r="J129" s="21" t="s">
         <v>601</v>
       </c>
-    </row>
-    <row r="130" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K129" s="51" t="s">
+        <v>1268</v>
+      </c>
+      <c r="L129" s="52">
+        <v>0.4</v>
+      </c>
+      <c r="M129" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K129,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>2</v>
+      </c>
+      <c r="N129" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L129*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K129,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="130" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="16" t="s">
         <v>602</v>
       </c>
@@ -22692,8 +25049,22 @@
       <c r="J130" s="21" t="s">
         <v>606</v>
       </c>
-    </row>
-    <row r="131" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K130" s="51" t="s">
+        <v>1268</v>
+      </c>
+      <c r="L130" s="52">
+        <v>0.4</v>
+      </c>
+      <c r="M130" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K130,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>2</v>
+      </c>
+      <c r="N130" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L130*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K130,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="131" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="16" t="s">
         <v>605</v>
       </c>
@@ -22727,8 +25098,22 @@
       <c r="J131" s="21" t="s">
         <v>609</v>
       </c>
-    </row>
-    <row r="132" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K131" s="51" t="s">
+        <v>1271</v>
+      </c>
+      <c r="L131" s="52">
+        <v>-0.5</v>
+      </c>
+      <c r="M131" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K131,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>3</v>
+      </c>
+      <c r="N131" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L131*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K131,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2.15</v>
+      </c>
+    </row>
+    <row r="132" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="16" t="s">
         <v>610</v>
       </c>
@@ -22762,8 +25147,22 @@
       <c r="J132" s="21" t="s">
         <v>614</v>
       </c>
-    </row>
-    <row r="133" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K132" s="51" t="s">
+        <v>1268</v>
+      </c>
+      <c r="L132" s="52">
+        <v>0.3</v>
+      </c>
+      <c r="M132" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K132,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>2</v>
+      </c>
+      <c r="N132" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L132*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K132,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="133" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="16" t="s">
         <v>613</v>
       </c>
@@ -22797,8 +25196,22 @@
       <c r="J133" s="21" t="s">
         <v>617</v>
       </c>
-    </row>
-    <row r="134" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K133" s="51" t="s">
+        <v>1271</v>
+      </c>
+      <c r="L133" s="52">
+        <v>-0.4</v>
+      </c>
+      <c r="M133" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K133,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>3</v>
+      </c>
+      <c r="N133" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L133*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K133,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2.2200000000000002</v>
+      </c>
+    </row>
+    <row r="134" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="16" t="s">
         <v>618</v>
       </c>
@@ -22832,8 +25245,22 @@
       <c r="J134" s="21" t="s">
         <v>622</v>
       </c>
-    </row>
-    <row r="135" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K134" s="51" t="s">
+        <v>1271</v>
+      </c>
+      <c r="L134" s="52">
+        <v>-0.7</v>
+      </c>
+      <c r="M134" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K134,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>3</v>
+      </c>
+      <c r="N134" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L134*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K134,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2.0099999999999998</v>
+      </c>
+    </row>
+    <row r="135" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="16" t="s">
         <v>621</v>
       </c>
@@ -22867,8 +25294,22 @@
       <c r="J135" s="21" t="s">
         <v>625</v>
       </c>
-    </row>
-    <row r="136" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K135" s="51" t="s">
+        <v>1274</v>
+      </c>
+      <c r="L135" s="52">
+        <v>0.3</v>
+      </c>
+      <c r="M135" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K135,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>4</v>
+      </c>
+      <c r="N135" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L135*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K135,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2.62</v>
+      </c>
+    </row>
+    <row r="136" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="16" t="s">
         <v>626</v>
       </c>
@@ -22902,8 +25343,22 @@
       <c r="J136" s="21" t="s">
         <v>630</v>
       </c>
-    </row>
-    <row r="137" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K136" s="51" t="s">
+        <v>1274</v>
+      </c>
+      <c r="L136" s="52">
+        <v>-0.3</v>
+      </c>
+      <c r="M136" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K136,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>4</v>
+      </c>
+      <c r="N136" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L136*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K136,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2.38</v>
+      </c>
+    </row>
+    <row r="137" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="16" t="s">
         <v>629</v>
       </c>
@@ -22937,8 +25392,22 @@
       <c r="J137" s="21" t="s">
         <v>633</v>
       </c>
-    </row>
-    <row r="138" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K137" s="51" t="s">
+        <v>1265</v>
+      </c>
+      <c r="L137" s="52">
+        <v>0.9</v>
+      </c>
+      <c r="M137" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K137,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>1</v>
+      </c>
+      <c r="N137" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L137*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K137,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>3.85</v>
+      </c>
+    </row>
+    <row r="138" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="16" t="s">
         <v>634</v>
       </c>
@@ -22972,8 +25441,22 @@
       <c r="J138" s="21" t="s">
         <v>638</v>
       </c>
-    </row>
-    <row r="139" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K138" s="51" t="s">
+        <v>1265</v>
+      </c>
+      <c r="L138" s="52">
+        <v>0.6</v>
+      </c>
+      <c r="M138" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K138,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>1</v>
+      </c>
+      <c r="N138" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L138*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K138,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="139" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="16" t="s">
         <v>637</v>
       </c>
@@ -23007,8 +25490,22 @@
       <c r="J139" s="21" t="s">
         <v>641</v>
       </c>
-    </row>
-    <row r="140" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K139" s="51" t="s">
+        <v>1268</v>
+      </c>
+      <c r="L139" s="52">
+        <v>-0.5</v>
+      </c>
+      <c r="M139" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K139,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>2</v>
+      </c>
+      <c r="N139" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L139*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K139,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="140" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="16" t="s">
         <v>642</v>
       </c>
@@ -23042,8 +25539,22 @@
       <c r="J140" s="21" t="s">
         <v>646</v>
       </c>
-    </row>
-    <row r="141" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K140" s="51" t="s">
+        <v>1271</v>
+      </c>
+      <c r="L140" s="52">
+        <v>-0.5</v>
+      </c>
+      <c r="M140" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K140,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>3</v>
+      </c>
+      <c r="N140" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L140*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K140,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2.15</v>
+      </c>
+    </row>
+    <row r="141" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="16" t="s">
         <v>645</v>
       </c>
@@ -23077,8 +25588,22 @@
       <c r="J141" s="21" t="s">
         <v>649</v>
       </c>
-    </row>
-    <row r="142" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K141" s="51" t="s">
+        <v>1265</v>
+      </c>
+      <c r="L141" s="52">
+        <v>0.5</v>
+      </c>
+      <c r="M141" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K141,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>1</v>
+      </c>
+      <c r="N141" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L141*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K141,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="142" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="16" t="s">
         <v>650</v>
       </c>
@@ -23112,8 +25637,22 @@
       <c r="J142" s="21" t="s">
         <v>654</v>
       </c>
-    </row>
-    <row r="143" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K142" s="51" t="s">
+        <v>1268</v>
+      </c>
+      <c r="L142" s="52">
+        <v>0.5</v>
+      </c>
+      <c r="M142" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K142,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>2</v>
+      </c>
+      <c r="N142" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L142*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K142,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="143" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="16" t="s">
         <v>653</v>
       </c>
@@ -23147,8 +25686,22 @@
       <c r="J143" s="21" t="s">
         <v>657</v>
       </c>
-    </row>
-    <row r="144" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K143" s="51" t="s">
+        <v>1268</v>
+      </c>
+      <c r="L143" s="52">
+        <v>-0.5</v>
+      </c>
+      <c r="M143" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K143,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>2</v>
+      </c>
+      <c r="N143" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L143*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K143,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="144" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="16" t="s">
         <v>658</v>
       </c>
@@ -23182,8 +25735,22 @@
       <c r="J144" s="21" t="s">
         <v>662</v>
       </c>
-    </row>
-    <row r="145" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K144" s="51" t="s">
+        <v>1271</v>
+      </c>
+      <c r="L144" s="52">
+        <v>-0.4</v>
+      </c>
+      <c r="M144" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K144,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>3</v>
+      </c>
+      <c r="N144" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L144*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K144,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2.2200000000000002</v>
+      </c>
+    </row>
+    <row r="145" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="16" t="s">
         <v>661</v>
       </c>
@@ -23217,8 +25784,22 @@
       <c r="J145" s="21" t="s">
         <v>665</v>
       </c>
-    </row>
-    <row r="146" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K145" s="51" t="s">
+        <v>1274</v>
+      </c>
+      <c r="L145" s="52">
+        <v>0.3</v>
+      </c>
+      <c r="M145" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K145,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>4</v>
+      </c>
+      <c r="N145" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L145*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K145,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2.62</v>
+      </c>
+    </row>
+    <row r="146" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="16" t="s">
         <v>666</v>
       </c>
@@ -23252,8 +25833,22 @@
       <c r="J146" s="21" t="s">
         <v>670</v>
       </c>
-    </row>
-    <row r="147" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K146" s="51" t="s">
+        <v>1268</v>
+      </c>
+      <c r="L146" s="52">
+        <v>-0.6</v>
+      </c>
+      <c r="M146" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K146,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>2</v>
+      </c>
+      <c r="N146" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L146*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K146,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="147" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="16" t="s">
         <v>669</v>
       </c>
@@ -23287,8 +25882,22 @@
       <c r="J147" s="21" t="s">
         <v>673</v>
       </c>
-    </row>
-    <row r="148" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K147" s="51" t="s">
+        <v>1265</v>
+      </c>
+      <c r="L147" s="52">
+        <v>0.7</v>
+      </c>
+      <c r="M147" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K147,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>1</v>
+      </c>
+      <c r="N147" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L147*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K147,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>3.55</v>
+      </c>
+    </row>
+    <row r="148" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="16" t="s">
         <v>674</v>
       </c>
@@ -23322,8 +25931,22 @@
       <c r="J148" s="21" t="s">
         <v>678</v>
       </c>
-    </row>
-    <row r="149" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K148" s="51" t="s">
+        <v>1268</v>
+      </c>
+      <c r="L148" s="52">
+        <v>-0.6</v>
+      </c>
+      <c r="M148" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K148,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>2</v>
+      </c>
+      <c r="N148" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L148*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K148,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="149" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="16" t="s">
         <v>677</v>
       </c>
@@ -23357,8 +25980,22 @@
       <c r="J149" s="21" t="s">
         <v>681</v>
       </c>
-    </row>
-    <row r="150" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K149" s="51" t="s">
+        <v>1265</v>
+      </c>
+      <c r="L149" s="52">
+        <v>0.6</v>
+      </c>
+      <c r="M149" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K149,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>1</v>
+      </c>
+      <c r="N149" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L149*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K149,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="150" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="16" t="s">
         <v>682</v>
       </c>
@@ -23392,8 +26029,22 @@
       <c r="J150" s="21" t="s">
         <v>686</v>
       </c>
-    </row>
-    <row r="151" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K150" s="51" t="s">
+        <v>1268</v>
+      </c>
+      <c r="L150" s="52">
+        <v>0.6</v>
+      </c>
+      <c r="M150" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K150,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>2</v>
+      </c>
+      <c r="N150" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L150*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K150,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="151" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="16" t="s">
         <v>685</v>
       </c>
@@ -23427,8 +26078,22 @@
       <c r="J151" s="21" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="152" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K151" s="51" t="s">
+        <v>1268</v>
+      </c>
+      <c r="L151" s="52">
+        <v>-0.6</v>
+      </c>
+      <c r="M151" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K151,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>2</v>
+      </c>
+      <c r="N151" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L151*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K151,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="152" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="16" t="s">
         <v>690</v>
       </c>
@@ -23462,8 +26127,22 @@
       <c r="J152" s="21" t="s">
         <v>694</v>
       </c>
-    </row>
-    <row r="153" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K152" s="51" t="s">
+        <v>1274</v>
+      </c>
+      <c r="L152" s="52">
+        <v>0.4</v>
+      </c>
+      <c r="M152" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K152,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>4</v>
+      </c>
+      <c r="N152" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L152*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K152,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2.66</v>
+      </c>
+    </row>
+    <row r="153" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="16" t="s">
         <v>693</v>
       </c>
@@ -23497,8 +26176,22 @@
       <c r="J153" s="21" t="s">
         <v>697</v>
       </c>
-    </row>
-    <row r="154" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K153" s="51" t="s">
+        <v>1265</v>
+      </c>
+      <c r="L153" s="52">
+        <v>-0.9</v>
+      </c>
+      <c r="M153" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K153,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>1</v>
+      </c>
+      <c r="N153" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L153*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K153,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>1.1499999999999999</v>
+      </c>
+    </row>
+    <row r="154" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="16" t="s">
         <v>698</v>
       </c>
@@ -23532,8 +26225,22 @@
       <c r="J154" s="21" t="s">
         <v>702</v>
       </c>
-    </row>
-    <row r="155" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K154" s="51" t="s">
+        <v>1271</v>
+      </c>
+      <c r="L154" s="52">
+        <v>-0.7</v>
+      </c>
+      <c r="M154" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K154,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>3</v>
+      </c>
+      <c r="N154" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L154*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K154,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2.0099999999999998</v>
+      </c>
+    </row>
+    <row r="155" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="16" t="s">
         <v>701</v>
       </c>
@@ -23567,8 +26274,22 @@
       <c r="J155" s="21" t="s">
         <v>705</v>
       </c>
-    </row>
-    <row r="156" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K155" s="51" t="s">
+        <v>1274</v>
+      </c>
+      <c r="L155" s="52">
+        <v>0.4</v>
+      </c>
+      <c r="M155" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K155,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>4</v>
+      </c>
+      <c r="N155" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L155*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K155,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2.66</v>
+      </c>
+    </row>
+    <row r="156" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="16" t="s">
         <v>706</v>
       </c>
@@ -23602,8 +26323,22 @@
       <c r="J156" s="21" t="s">
         <v>710</v>
       </c>
-    </row>
-    <row r="157" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K156" s="51" t="s">
+        <v>1274</v>
+      </c>
+      <c r="L156" s="52">
+        <v>0.3</v>
+      </c>
+      <c r="M156" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K156,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>4</v>
+      </c>
+      <c r="N156" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L156*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K156,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2.62</v>
+      </c>
+    </row>
+    <row r="157" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="16" t="s">
         <v>709</v>
       </c>
@@ -23637,8 +26372,22 @@
       <c r="J157" s="21" t="s">
         <v>713</v>
       </c>
-    </row>
-    <row r="158" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K157" s="51" t="s">
+        <v>1271</v>
+      </c>
+      <c r="L157" s="52">
+        <v>-0.6</v>
+      </c>
+      <c r="M157" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K157,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>3</v>
+      </c>
+      <c r="N157" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L157*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K157,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2.08</v>
+      </c>
+    </row>
+    <row r="158" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="16" t="s">
         <v>714</v>
       </c>
@@ -23672,8 +26421,22 @@
       <c r="J158" s="21" t="s">
         <v>718</v>
       </c>
-    </row>
-    <row r="159" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K158" s="51" t="s">
+        <v>1271</v>
+      </c>
+      <c r="L158" s="52">
+        <v>-0.8</v>
+      </c>
+      <c r="M158" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K158,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>3</v>
+      </c>
+      <c r="N158" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L158*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K158,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>1.94</v>
+      </c>
+    </row>
+    <row r="159" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="16" t="s">
         <v>717</v>
       </c>
@@ -23707,8 +26470,22 @@
       <c r="J159" s="21" t="s">
         <v>721</v>
       </c>
-    </row>
-    <row r="160" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K159" s="51" t="s">
+        <v>1265</v>
+      </c>
+      <c r="L159" s="52">
+        <v>0.5</v>
+      </c>
+      <c r="M159" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K159,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>1</v>
+      </c>
+      <c r="N159" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L159*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K159,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="160" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="16" t="s">
         <v>722</v>
       </c>
@@ -23742,8 +26519,22 @@
       <c r="J160" s="21" t="s">
         <v>726</v>
       </c>
-    </row>
-    <row r="161" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K160" s="51" t="s">
+        <v>1268</v>
+      </c>
+      <c r="L160" s="52">
+        <v>-0.3</v>
+      </c>
+      <c r="M160" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K160,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>2</v>
+      </c>
+      <c r="N160" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L160*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K160,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="161" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="16" t="s">
         <v>725</v>
       </c>
@@ -23777,8 +26568,22 @@
       <c r="J161" s="21" t="s">
         <v>729</v>
       </c>
-    </row>
-    <row r="162" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K161" s="51" t="s">
+        <v>1274</v>
+      </c>
+      <c r="L161" s="52">
+        <v>0.3</v>
+      </c>
+      <c r="M161" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K161,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>4</v>
+      </c>
+      <c r="N161" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L161*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K161,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2.62</v>
+      </c>
+    </row>
+    <row r="162" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="16" t="s">
         <v>730</v>
       </c>
@@ -23812,8 +26617,22 @@
       <c r="J162" s="21" t="s">
         <v>734</v>
       </c>
-    </row>
-    <row r="163" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K162" s="51" t="s">
+        <v>1265</v>
+      </c>
+      <c r="L162" s="52">
+        <v>0.9</v>
+      </c>
+      <c r="M162" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K162,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>1</v>
+      </c>
+      <c r="N162" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L162*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K162,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>3.85</v>
+      </c>
+    </row>
+    <row r="163" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="16" t="s">
         <v>733</v>
       </c>
@@ -23847,8 +26666,22 @@
       <c r="J163" s="21" t="s">
         <v>737</v>
       </c>
-    </row>
-    <row r="164" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K163" s="51" t="s">
+        <v>1268</v>
+      </c>
+      <c r="L163" s="52">
+        <v>-0.6</v>
+      </c>
+      <c r="M163" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K163,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>2</v>
+      </c>
+      <c r="N163" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L163*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K163,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="164" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="16" t="s">
         <v>738</v>
       </c>
@@ -23882,8 +26715,22 @@
       <c r="J164" s="21" t="s">
         <v>742</v>
       </c>
-    </row>
-    <row r="165" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K164" s="51" t="s">
+        <v>1274</v>
+      </c>
+      <c r="L164" s="52">
+        <v>0.6</v>
+      </c>
+      <c r="M164" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K164,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>4</v>
+      </c>
+      <c r="N164" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L164*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K164,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2.74</v>
+      </c>
+    </row>
+    <row r="165" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="16" t="s">
         <v>741</v>
       </c>
@@ -23917,8 +26764,22 @@
       <c r="J165" s="21" t="s">
         <v>745</v>
       </c>
-    </row>
-    <row r="166" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K165" s="51" t="s">
+        <v>1268</v>
+      </c>
+      <c r="L165" s="52">
+        <v>-0.4</v>
+      </c>
+      <c r="M165" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K165,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>2</v>
+      </c>
+      <c r="N165" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L165*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K165,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="166" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="16" t="s">
         <v>746</v>
       </c>
@@ -23952,8 +26813,22 @@
       <c r="J166" s="21" t="s">
         <v>750</v>
       </c>
-    </row>
-    <row r="167" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K166" s="51" t="s">
+        <v>1271</v>
+      </c>
+      <c r="L166" s="52">
+        <v>-0.6</v>
+      </c>
+      <c r="M166" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K166,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>3</v>
+      </c>
+      <c r="N166" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L166*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K166,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>2.08</v>
+      </c>
+    </row>
+    <row r="167" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="16" t="s">
         <v>749</v>
       </c>
@@ -23987,9 +26862,44 @@
       <c r="J167" s="21" t="s">
         <v>753</v>
       </c>
+      <c r="K167" s="51" t="s">
+        <v>1265</v>
+      </c>
+      <c r="L167" s="52">
+        <v>0.6</v>
+      </c>
+      <c r="M167" s="53">
+        <f>IFERROR(INDEX('Bond Rules'!$B$4:$B$7,MATCH(K167,'Bond Rules'!$A$4:$A$7,0)),"")</f>
+        <v>1</v>
+      </c>
+      <c r="N167" s="54">
+        <f>IFERROR(ROUND('Bond Rules'!$B$9+L167*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K167,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
+        <v>3.4</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J167" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
+  <autoFilter ref="A1:N167" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
+  <conditionalFormatting sqref="N2:N167">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF8AB4E0"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FFE69C8A"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K167" xr:uid="{887C6CCD-555B-4950-A4DD-AFA8B29D07EC}">
+      <formula1>"Cap,Link,Branch,Frame"</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L167" xr:uid="{6389D932-E31D-4299-9973-772D172EDE55}">
+      <formula1>-1</formula1>
+      <formula2>1</formula2>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
@@ -25438,6 +28348,188 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{707B76BF-2512-40E2-935C-38AB239C315D}">
+  <dimension ref="A1:E17"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="22.7109375" style="32" customWidth="1"/>
+    <col min="2" max="2" width="14.7109375" style="32" customWidth="1"/>
+    <col min="3" max="3" width="22.7109375" style="32" customWidth="1"/>
+    <col min="4" max="4" width="44.7109375" style="32" customWidth="1"/>
+    <col min="5" max="5" width="60.7109375" style="32" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="32"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A1" s="44" t="s">
+        <v>1259</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A3" s="36" t="s">
+        <v>1260</v>
+      </c>
+      <c r="B3" s="36" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C3" s="36" t="s">
+        <v>1262</v>
+      </c>
+      <c r="D3" s="36" t="s">
+        <v>1263</v>
+      </c>
+      <c r="E3" s="36" t="s">
+        <v>1264</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A4" s="47" t="s">
+        <v>1265</v>
+      </c>
+      <c r="B4" s="48">
+        <v>1</v>
+      </c>
+      <c r="C4" s="48">
+        <v>1.5</v>
+      </c>
+      <c r="D4" s="46" t="s">
+        <v>1266</v>
+      </c>
+      <c r="E4" s="46" t="s">
+        <v>1267</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" s="47" t="s">
+        <v>1268</v>
+      </c>
+      <c r="B5" s="48">
+        <v>2</v>
+      </c>
+      <c r="C5" s="48">
+        <v>1</v>
+      </c>
+      <c r="D5" s="46" t="s">
+        <v>1269</v>
+      </c>
+      <c r="E5" s="46" t="s">
+        <v>1270</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" s="47" t="s">
+        <v>1271</v>
+      </c>
+      <c r="B6" s="48">
+        <v>3</v>
+      </c>
+      <c r="C6" s="48">
+        <v>0.7</v>
+      </c>
+      <c r="D6" s="46" t="s">
+        <v>1272</v>
+      </c>
+      <c r="E6" s="46" t="s">
+        <v>1273</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A7" s="47" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B7" s="48">
+        <v>4</v>
+      </c>
+      <c r="C7" s="48">
+        <v>0.4</v>
+      </c>
+      <c r="D7" s="46" t="s">
+        <v>1275</v>
+      </c>
+      <c r="E7" s="46" t="s">
+        <v>1276</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9" s="32" t="s">
+        <v>1277</v>
+      </c>
+      <c r="B9" s="34">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="54" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="56" t="s">
+        <v>1278</v>
+      </c>
+      <c r="B10" s="56"/>
+      <c r="C10" s="56"/>
+      <c r="D10" s="56"/>
+      <c r="E10" s="56"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12" s="45" t="s">
+        <v>1279</v>
+      </c>
+      <c r="B12" s="45" t="s">
+        <v>1280</v>
+      </c>
+      <c r="C12" s="45" t="s">
+        <v>1281</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13" s="50" t="s">
+        <v>1282</v>
+      </c>
+      <c r="B13" s="34">
+        <v>0</v>
+      </c>
+      <c r="C13" s="49" t="s">
+        <v>1283</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14" s="50" t="s">
+        <v>1284</v>
+      </c>
+      <c r="B14" s="34">
+        <v>0.4</v>
+      </c>
+      <c r="C14" s="49" t="s">
+        <v>1285</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A15" s="50" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B15" s="34">
+        <v>1.7</v>
+      </c>
+      <c r="C15" s="49" t="s">
+        <v>1287</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="57" t="s">
+        <v>1288</v>
+      </c>
+      <c r="B17" s="56"/>
+      <c r="C17" s="56"/>
+      <c r="D17" s="56"/>
+      <c r="E17" s="56"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A17:E17"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr>
     <tabColor rgb="FF3A7BD5"/>
@@ -25461,32 +28553,32 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="45" t="s">
+      <c r="A2" s="60" t="s">
         <v>977</v>
       </c>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="44"/>
-      <c r="H2" s="44"/>
-      <c r="I2" s="44"/>
-      <c r="J2" s="44"/>
+      <c r="B2" s="59"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
     </row>
     <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="43" t="s">
+      <c r="A3" s="58" t="s">
         <v>978</v>
       </c>
-      <c r="B3" s="44"/>
-      <c r="C3" s="44"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
-      <c r="G3" s="44"/>
-      <c r="H3" s="44"/>
-      <c r="I3" s="44"/>
-      <c r="J3" s="44"/>
+      <c r="B3" s="59"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
     </row>
     <row r="5" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
@@ -26052,7 +29144,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr>
     <tabColor rgb="FFD9534F"/>
@@ -26076,32 +29168,32 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="45" t="s">
+      <c r="A2" s="60" t="s">
         <v>1036</v>
       </c>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="44"/>
-      <c r="H2" s="44"/>
-      <c r="I2" s="44"/>
-      <c r="J2" s="44"/>
+      <c r="B2" s="59"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
     </row>
     <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="43" t="s">
+      <c r="A3" s="58" t="s">
         <v>1037</v>
       </c>
-      <c r="B3" s="44"/>
-      <c r="C3" s="44"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
-      <c r="G3" s="44"/>
-      <c r="H3" s="44"/>
-      <c r="I3" s="44"/>
-      <c r="J3" s="44"/>
+      <c r="B3" s="59"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
     </row>
     <row r="5" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
@@ -26431,7 +29523,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr>
     <tabColor rgb="FF8B6B3E"/>
@@ -26455,32 +29547,32 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="45" t="s">
+      <c r="A2" s="60" t="s">
         <v>1054</v>
       </c>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="44"/>
-      <c r="H2" s="44"/>
-      <c r="I2" s="44"/>
-      <c r="J2" s="44"/>
+      <c r="B2" s="59"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
     </row>
     <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="43" t="s">
+      <c r="A3" s="58" t="s">
         <v>1037</v>
       </c>
-      <c r="B3" s="44"/>
-      <c r="C3" s="44"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
-      <c r="G3" s="44"/>
-      <c r="H3" s="44"/>
-      <c r="I3" s="44"/>
-      <c r="J3" s="44"/>
+      <c r="B3" s="59"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
     </row>
     <row r="5" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
@@ -26793,385 +29885,6 @@
       <c r="G15" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B15,'Base Runes'!$A:$A,0)),"")</f>
         <v>Shard</v>
-      </c>
-      <c r="H15" s="30"/>
-      <c r="I15" s="10"/>
-      <c r="J15" s="10"/>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="29" t="s">
-        <v>1035</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A3:J3"/>
-    <mergeCell ref="A2:J2"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <sheetPr>
-    <tabColor rgb="FF7FB8A4"/>
-  </sheetPr>
-  <dimension ref="A1:J17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="11" customWidth="1"/>
-    <col min="5" max="6" width="46" customWidth="1"/>
-    <col min="7" max="7" width="16" customWidth="1"/>
-    <col min="8" max="8" width="40" customWidth="1"/>
-    <col min="9" max="10" width="30" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A1" s="25" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="45" t="s">
-        <v>1072</v>
-      </c>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="44"/>
-      <c r="H2" s="44"/>
-      <c r="I2" s="44"/>
-      <c r="J2" s="44"/>
-    </row>
-    <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="43" t="s">
-        <v>1037</v>
-      </c>
-      <c r="B3" s="44"/>
-      <c r="C3" s="44"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
-      <c r="G3" s="44"/>
-      <c r="H3" s="44"/>
-      <c r="I3" s="44"/>
-      <c r="J3" s="44"/>
-    </row>
-    <row r="5" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>979</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>980</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>981</v>
-      </c>
-      <c r="I5" s="8" t="s">
-        <v>982</v>
-      </c>
-      <c r="J5" s="8" t="s">
-        <v>983</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="26">
-        <v>1</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>235</v>
-      </c>
-      <c r="C6" s="27" t="str">
-        <f>IFERROR(INDEX('Base Runes'!$D:$D,MATCH($B6,'Base Runes'!$A:$A,0)),"")</f>
-        <v>Gust</v>
-      </c>
-      <c r="D6" s="28" t="str">
-        <f>IFERROR(INDEX('Base Runes'!$E:$E,MATCH($B6,'Base Runes'!$A:$A,0)),"")</f>
-        <v>ᛄ</v>
-      </c>
-      <c r="E6" s="10" t="s">
-        <v>1073</v>
-      </c>
-      <c r="F6" s="30"/>
-      <c r="G6" s="11" t="str">
-        <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B6,'Base Runes'!$A:$A,0)),"")</f>
-        <v>Lull</v>
-      </c>
-      <c r="H6" s="30"/>
-      <c r="I6" s="10" t="s">
-        <v>1074</v>
-      </c>
-      <c r="J6" s="10"/>
-    </row>
-    <row r="7" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="26">
-        <v>1</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>238</v>
-      </c>
-      <c r="C7" s="27" t="str">
-        <f>IFERROR(INDEX('Base Runes'!$D:$D,MATCH($B7,'Base Runes'!$A:$A,0)),"")</f>
-        <v>Lull</v>
-      </c>
-      <c r="D7" s="28" t="str">
-        <f>IFERROR(INDEX('Base Runes'!$E:$E,MATCH($B7,'Base Runes'!$A:$A,0)),"")</f>
-        <v>ᛅ</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>1075</v>
-      </c>
-      <c r="F7" s="30"/>
-      <c r="G7" s="11" t="str">
-        <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B7,'Base Runes'!$A:$A,0)),"")</f>
-        <v>Gust</v>
-      </c>
-      <c r="H7" s="30"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="10"/>
-    </row>
-    <row r="8" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="26">
-        <v>2</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>243</v>
-      </c>
-      <c r="C8" s="27" t="str">
-        <f>IFERROR(INDEX('Base Runes'!$D:$D,MATCH($B8,'Base Runes'!$A:$A,0)),"")</f>
-        <v>Updraft</v>
-      </c>
-      <c r="D8" s="28" t="str">
-        <f>IFERROR(INDEX('Base Runes'!$E:$E,MATCH($B8,'Base Runes'!$A:$A,0)),"")</f>
-        <v>ᛆ</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>1076</v>
-      </c>
-      <c r="F8" s="30"/>
-      <c r="G8" s="11" t="str">
-        <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B8,'Base Runes'!$A:$A,0)),"")</f>
-        <v>Downdraft</v>
-      </c>
-      <c r="H8" s="30"/>
-      <c r="I8" s="10" t="s">
-        <v>244</v>
-      </c>
-      <c r="J8" s="10"/>
-    </row>
-    <row r="9" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="26">
-        <v>2</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>246</v>
-      </c>
-      <c r="C9" s="27" t="str">
-        <f>IFERROR(INDEX('Base Runes'!$D:$D,MATCH($B9,'Base Runes'!$A:$A,0)),"")</f>
-        <v>Downdraft</v>
-      </c>
-      <c r="D9" s="28" t="str">
-        <f>IFERROR(INDEX('Base Runes'!$E:$E,MATCH($B9,'Base Runes'!$A:$A,0)),"")</f>
-        <v>ᛇ</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>1077</v>
-      </c>
-      <c r="F9" s="30"/>
-      <c r="G9" s="11" t="str">
-        <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B9,'Base Runes'!$A:$A,0)),"")</f>
-        <v>Updraft</v>
-      </c>
-      <c r="H9" s="30"/>
-      <c r="I9" s="10" t="s">
-        <v>248</v>
-      </c>
-      <c r="J9" s="10"/>
-    </row>
-    <row r="10" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="26">
-        <v>3</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>251</v>
-      </c>
-      <c r="C10" s="27" t="str">
-        <f>IFERROR(INDEX('Base Runes'!$D:$D,MATCH($B10,'Base Runes'!$A:$A,0)),"")</f>
-        <v>Shear</v>
-      </c>
-      <c r="D10" s="28" t="str">
-        <f>IFERROR(INDEX('Base Runes'!$E:$E,MATCH($B10,'Base Runes'!$A:$A,0)),"")</f>
-        <v>ᛈ</v>
-      </c>
-      <c r="E10" s="10" t="s">
-        <v>1078</v>
-      </c>
-      <c r="F10" s="30"/>
-      <c r="G10" s="11" t="str">
-        <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B10,'Base Runes'!$A:$A,0)),"")</f>
-        <v>Buffer</v>
-      </c>
-      <c r="H10" s="30"/>
-      <c r="I10" s="10" t="s">
-        <v>1079</v>
-      </c>
-      <c r="J10" s="10"/>
-    </row>
-    <row r="11" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="26">
-        <v>3</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>254</v>
-      </c>
-      <c r="C11" s="27" t="str">
-        <f>IFERROR(INDEX('Base Runes'!$D:$D,MATCH($B11,'Base Runes'!$A:$A,0)),"")</f>
-        <v>Buffer</v>
-      </c>
-      <c r="D11" s="28" t="str">
-        <f>IFERROR(INDEX('Base Runes'!$E:$E,MATCH($B11,'Base Runes'!$A:$A,0)),"")</f>
-        <v>ᛉ</v>
-      </c>
-      <c r="E11" s="10" t="s">
-        <v>1080</v>
-      </c>
-      <c r="F11" s="30"/>
-      <c r="G11" s="11" t="str">
-        <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B11,'Base Runes'!$A:$A,0)),"")</f>
-        <v>Shear</v>
-      </c>
-      <c r="H11" s="30"/>
-      <c r="I11" s="10" t="s">
-        <v>1081</v>
-      </c>
-      <c r="J11" s="10"/>
-    </row>
-    <row r="12" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="26">
-        <v>4</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>259</v>
-      </c>
-      <c r="C12" s="27" t="str">
-        <f>IFERROR(INDEX('Base Runes'!$D:$D,MATCH($B12,'Base Runes'!$A:$A,0)),"")</f>
-        <v>Tailwind</v>
-      </c>
-      <c r="D12" s="28" t="str">
-        <f>IFERROR(INDEX('Base Runes'!$E:$E,MATCH($B12,'Base Runes'!$A:$A,0)),"")</f>
-        <v>ᛊ</v>
-      </c>
-      <c r="E12" s="10" t="s">
-        <v>1082</v>
-      </c>
-      <c r="F12" s="30"/>
-      <c r="G12" s="11" t="str">
-        <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B12,'Base Runes'!$A:$A,0)),"")</f>
-        <v>Headwind</v>
-      </c>
-      <c r="H12" s="30"/>
-      <c r="I12" s="10" t="s">
-        <v>260</v>
-      </c>
-      <c r="J12" s="10"/>
-    </row>
-    <row r="13" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="26">
-        <v>4</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>262</v>
-      </c>
-      <c r="C13" s="27" t="str">
-        <f>IFERROR(INDEX('Base Runes'!$D:$D,MATCH($B13,'Base Runes'!$A:$A,0)),"")</f>
-        <v>Headwind</v>
-      </c>
-      <c r="D13" s="28" t="str">
-        <f>IFERROR(INDEX('Base Runes'!$E:$E,MATCH($B13,'Base Runes'!$A:$A,0)),"")</f>
-        <v>ᛋ</v>
-      </c>
-      <c r="E13" s="10" t="s">
-        <v>1083</v>
-      </c>
-      <c r="F13" s="30"/>
-      <c r="G13" s="11" t="str">
-        <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B13,'Base Runes'!$A:$A,0)),"")</f>
-        <v>Tailwind</v>
-      </c>
-      <c r="H13" s="30"/>
-      <c r="I13" s="10"/>
-      <c r="J13" s="10"/>
-    </row>
-    <row r="14" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="26">
-        <v>5</v>
-      </c>
-      <c r="B14" s="10" t="s">
-        <v>267</v>
-      </c>
-      <c r="C14" s="27" t="str">
-        <f>IFERROR(INDEX('Base Runes'!$D:$D,MATCH($B14,'Base Runes'!$A:$A,0)),"")</f>
-        <v>Whirl</v>
-      </c>
-      <c r="D14" s="28" t="str">
-        <f>IFERROR(INDEX('Base Runes'!$E:$E,MATCH($B14,'Base Runes'!$A:$A,0)),"")</f>
-        <v>ᛌ</v>
-      </c>
-      <c r="E14" s="10" t="s">
-        <v>1084</v>
-      </c>
-      <c r="F14" s="30"/>
-      <c r="G14" s="11" t="str">
-        <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B14,'Base Runes'!$A:$A,0)),"")</f>
-        <v>Disperse</v>
-      </c>
-      <c r="H14" s="30"/>
-      <c r="I14" s="10"/>
-      <c r="J14" s="10"/>
-    </row>
-    <row r="15" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="26">
-        <v>5</v>
-      </c>
-      <c r="B15" s="10" t="s">
-        <v>270</v>
-      </c>
-      <c r="C15" s="27" t="str">
-        <f>IFERROR(INDEX('Base Runes'!$D:$D,MATCH($B15,'Base Runes'!$A:$A,0)),"")</f>
-        <v>Disperse</v>
-      </c>
-      <c r="D15" s="28" t="str">
-        <f>IFERROR(INDEX('Base Runes'!$E:$E,MATCH($B15,'Base Runes'!$A:$A,0)),"")</f>
-        <v>ᛍ</v>
-      </c>
-      <c r="E15" s="10" t="s">
-        <v>1085</v>
-      </c>
-      <c r="F15" s="30"/>
-      <c r="G15" s="11" t="str">
-        <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B15,'Base Runes'!$A:$A,0)),"")</f>
-        <v>Whirl</v>
       </c>
       <c r="H15" s="30"/>
       <c r="I15" s="10"/>

--- a/design/runes-workbook.xlsx
+++ b/design/runes-workbook.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Code\lifesteal-crawler\design\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{641AA2D2-BE15-47F8-AE0E-05657776567F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{684AD401-4726-4428-8974-7DE54CA8E1EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -177,7 +177,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2247" uniqueCount="1280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2432" uniqueCount="1426">
   <si>
     <t>Passage rune workbook</t>
   </si>
@@ -4017,6 +4017,444 @@
   </si>
   <si>
     <t>Rune names used by more than one affinity: none (checked 2026-10-22).</t>
+  </si>
+  <si>
+    <t>Effect (game)</t>
+  </si>
+  <si>
+    <t>reach x1.2; status soaked</t>
+  </si>
+  <si>
+    <t>bonus soaked +0.25; cost x0.9</t>
+  </si>
+  <si>
+    <t>shove +1.5</t>
+  </si>
+  <si>
+    <t>pull +1.5</t>
+  </si>
+  <si>
+    <t>status soaked</t>
+  </si>
+  <si>
+    <t>bonus soaked +0.4</t>
+  </si>
+  <si>
+    <t>status aloft</t>
+  </si>
+  <si>
+    <t>interrupts; status dazed</t>
+  </si>
+  <si>
+    <t>speed x1.3; power x1.1</t>
+  </si>
+  <si>
+    <t>duration x1.4; cost x0.85</t>
+  </si>
+  <si>
+    <t>reach x1.3</t>
+  </si>
+  <si>
+    <t>status mired</t>
+  </si>
+  <si>
+    <t>reach x1.25; power x0.9</t>
+  </si>
+  <si>
+    <t>pierce +1</t>
+  </si>
+  <si>
+    <t>reach x1.2; poise x1.3</t>
+  </si>
+  <si>
+    <t>reflux x0.75</t>
+  </si>
+  <si>
+    <t>status alight</t>
+  </si>
+  <si>
+    <t>reflux x0.7; power x1.1</t>
+  </si>
+  <si>
+    <t>status alight; windup x0.9</t>
+  </si>
+  <si>
+    <t>interrupts</t>
+  </si>
+  <si>
+    <t>reach x1.3; power x1.15; cost x1.15</t>
+  </si>
+  <si>
+    <t>power x1.2; reflux x1.2</t>
+  </si>
+  <si>
+    <t>duration x1.5; status alight</t>
+  </si>
+  <si>
+    <t>status dazed</t>
+  </si>
+  <si>
+    <t>interrupts; status slowed</t>
+  </si>
+  <si>
+    <t>poise x1.3</t>
+  </si>
+  <si>
+    <t>power x1.15; speed x0.9</t>
+  </si>
+  <si>
+    <t>poise x1.5</t>
+  </si>
+  <si>
+    <t>braced</t>
+  </si>
+  <si>
+    <t>power x1.15; cost x0.9</t>
+  </si>
+  <si>
+    <t>status pinned</t>
+  </si>
+  <si>
+    <t>status stunned; cost x1.2</t>
+  </si>
+  <si>
+    <t>shove +1</t>
+  </si>
+  <si>
+    <t>reflux x0.8</t>
+  </si>
+  <si>
+    <t>power x1.2; speed x1.1</t>
+  </si>
+  <si>
+    <t>windup x0.85</t>
+  </si>
+  <si>
+    <t>poise x1.4</t>
+  </si>
+  <si>
+    <t>speed x1.3; reach x1.15</t>
+  </si>
+  <si>
+    <t>status slowed</t>
+  </si>
+  <si>
+    <t>pull +1; reach x1.1</t>
+  </si>
+  <si>
+    <t>reach x1.3; power x0.9</t>
+  </si>
+  <si>
+    <t>power x1.2; speed x1.2</t>
+  </si>
+  <si>
+    <t>marks +1</t>
+  </si>
+  <si>
+    <t>bonus live +0.4</t>
+  </si>
+  <si>
+    <t>jumps +1</t>
+  </si>
+  <si>
+    <t>cost x0.85</t>
+  </si>
+  <si>
+    <t>windup x0.7; speed x1.2</t>
+  </si>
+  <si>
+    <t>status stunned</t>
+  </si>
+  <si>
+    <t>poise x1.3; status dazed</t>
+  </si>
+  <si>
+    <t>speed x1.25</t>
+  </si>
+  <si>
+    <t>duration x1.4; speed x0.8</t>
+  </si>
+  <si>
+    <t>windup x0.75</t>
+  </si>
+  <si>
+    <t>power x1.3; windup x1.4</t>
+  </si>
+  <si>
+    <t>reach x1.1; power x1.05</t>
+  </si>
+  <si>
+    <t>speed x1.2; reach x1.1</t>
+  </si>
+  <si>
+    <t>reach x0.8; power x1.25</t>
+  </si>
+  <si>
+    <t>power x1.2; reach x0.85</t>
+  </si>
+  <si>
+    <t>reach x1.4; power x0.9</t>
+  </si>
+  <si>
+    <t>power x1.3; reach x0.8</t>
+  </si>
+  <si>
+    <t>reach x1.3; power x0.85</t>
+  </si>
+  <si>
+    <t>power x1.25</t>
+  </si>
+  <si>
+    <t>jumps +1; power x0.85</t>
+  </si>
+  <si>
+    <t>reach x1.1; poise x1.1</t>
+  </si>
+  <si>
+    <t>windup x0.9</t>
+  </si>
+  <si>
+    <t>duration x1.5</t>
+  </si>
+  <si>
+    <t>duration x0.6; power x1.25</t>
+  </si>
+  <si>
+    <t>power x1.3; windup x1.3</t>
+  </si>
+  <si>
+    <t>windup x0.7; power x0.9</t>
+  </si>
+  <si>
+    <t>power x1.15; cost x1.15</t>
+  </si>
+  <si>
+    <t>power x1.2; cost x1.1</t>
+  </si>
+  <si>
+    <t>power x1.15; windup x1.1</t>
+  </si>
+  <si>
+    <t>power x1.15; cost x1.1</t>
+  </si>
+  <si>
+    <t>reflux x0.85</t>
+  </si>
+  <si>
+    <t>duration x1.3</t>
+  </si>
+  <si>
+    <t>reach x1.2</t>
+  </si>
+  <si>
+    <t>power x1.1</t>
+  </si>
+  <si>
+    <t>power x1.2; reflux x1.15</t>
+  </si>
+  <si>
+    <t>power x1.05; reach x1.05</t>
+  </si>
+  <si>
+    <t>cost x0.85; power x0.9</t>
+  </si>
+  <si>
+    <t>power x1.25; reflux x1.3</t>
+  </si>
+  <si>
+    <t>duration x1.1; reflux x0.9</t>
+  </si>
+  <si>
+    <t>power x1.15</t>
+  </si>
+  <si>
+    <t>poise x1.2</t>
+  </si>
+  <si>
+    <t>range and area +20%; applies Soaked</t>
+  </si>
+  <si>
+    <t>+25% damage to Soaked targets; essence cost -10%</t>
+  </si>
+  <si>
+    <t>speed +30%; damage +10%</t>
+  </si>
+  <si>
+    <t>duration +40%; essence cost -15%</t>
+  </si>
+  <si>
+    <t>range and area +30%</t>
+  </si>
+  <si>
+    <t>applies Mired</t>
+  </si>
+  <si>
+    <t>range and area +25%; damage -10%</t>
+  </si>
+  <si>
+    <t>passes through one more</t>
+  </si>
+  <si>
+    <t>range and area +20%; poise damage +30%</t>
+  </si>
+  <si>
+    <t>reflux left -25%</t>
+  </si>
+  <si>
+    <t>applies Alight</t>
+  </si>
+  <si>
+    <t>reflux left -30%; damage +10%</t>
+  </si>
+  <si>
+    <t>applies Alight; wind-up and recovery -10%</t>
+  </si>
+  <si>
+    <t>interrupts a wind-up</t>
+  </si>
+  <si>
+    <t>range and area +30%; damage +15%; essence cost +15%</t>
+  </si>
+  <si>
+    <t>pulls 1.5 m</t>
+  </si>
+  <si>
+    <t>damage +20%; reflux left +20%</t>
+  </si>
+  <si>
+    <t>duration +50%; applies Alight</t>
+  </si>
+  <si>
+    <t>applies Dazed</t>
+  </si>
+  <si>
+    <t>interrupts a wind-up; applies Slowed</t>
+  </si>
+  <si>
+    <t>poise damage +30%</t>
+  </si>
+  <si>
+    <t>damage +15%; speed -10%</t>
+  </si>
+  <si>
+    <t>poise damage +50%</t>
+  </si>
+  <si>
+    <t>you are Braced while casting</t>
+  </si>
+  <si>
+    <t>damage +15%; essence cost -10%</t>
+  </si>
+  <si>
+    <t>applies Pinned</t>
+  </si>
+  <si>
+    <t>applies Stunned; essence cost +20%</t>
+  </si>
+  <si>
+    <t>shoves 1 m</t>
+  </si>
+  <si>
+    <t>reflux left -20%</t>
+  </si>
+  <si>
+    <t>damage +20%; speed +10%</t>
+  </si>
+  <si>
+    <t>wind-up and recovery -15%</t>
+  </si>
+  <si>
+    <t>applies Aloft</t>
+  </si>
+  <si>
+    <t>poise damage +40%</t>
+  </si>
+  <si>
+    <t>speed +30%; range and area +15%</t>
+  </si>
+  <si>
+    <t>applies Slowed</t>
+  </si>
+  <si>
+    <t>pulls 1 m; range and area +10%</t>
+  </si>
+  <si>
+    <t>range and area +30%; damage -10%</t>
+  </si>
+  <si>
+    <t>damage +20%; speed +20%</t>
+  </si>
+  <si>
+    <t>adds a Live mark</t>
+  </si>
+  <si>
+    <t>+40% damage to Live targets</t>
+  </si>
+  <si>
+    <t>jumps to one more target</t>
+  </si>
+  <si>
+    <t>essence cost -15%</t>
+  </si>
+  <si>
+    <t>wind-up and recovery -30%; speed +20%</t>
+  </si>
+  <si>
+    <t>applies Stunned</t>
+  </si>
+  <si>
+    <t>poise damage +30%; applies Dazed</t>
+  </si>
+  <si>
+    <t>Rune effects: layers 1-3 (first pass, 2026-10-22)</t>
+  </si>
+  <si>
+    <t>Layer 1: each rune's Effect (game) on Base Runes and Universal Runes. Layer 2: the bond a rune reaches the skill through scales it by bond kind. Layer 3: it fades with each bond between it and the skill's own rune. Effects only count once the word is locked.</t>
+  </si>
+  <si>
+    <t>Bonds from the skill's rune</t>
+  </si>
+  <si>
+    <t>Strength</t>
+  </si>
+  <si>
+    <t>4 or more</t>
+  </si>
+  <si>
+    <t>Rune with more pull</t>
+  </si>
+  <si>
+    <t>Rune with less pull</t>
+  </si>
+  <si>
+    <t>Meaning</t>
+  </si>
+  <si>
+    <t>both blend, each at three-quarters</t>
+  </si>
+  <si>
+    <t>the rune with more pull dominates; the other colours it</t>
+  </si>
+  <si>
+    <t>the weaker rune hands its effect over: the stronger one is amplified, the weaker one's own effect is gone</t>
+  </si>
+  <si>
+    <t>A status applies when strength is at least</t>
+  </si>
+  <si>
+    <t>Lowest multiplier a stat group can reach</t>
+  </si>
+  <si>
+    <t>Highest multiplier a stat group can reach</t>
+  </si>
+  <si>
+    <t>A word must be closed to lock (1 yes, 0 no)</t>
+  </si>
+  <si>
+    <t>The skill's own rune: its Effect names what the skill already does (Surge: the shove). Its bond factors scale that part of the skill, averaged over its bonds: bonded ionically to a stronger rune, Water Bolt loses its shove.</t>
+  </si>
+  <si>
+    <t>Effect syntax (one op per ";"): &lt;group&gt; x&lt;m&gt; multiplies every field of a stat group the skill has: power (damage), reach (range, radius, arc, width), speed, cost, reflux, windup (wind-up and recovery), duration, poise. Also: status &lt;id&gt; [n], shove +&lt;m&gt;, pull +&lt;m&gt;, marks +&lt;n&gt;, jumps +&lt;n&gt;, pierce +&lt;n&gt;, interrupts, braced, bonus &lt;status&gt; +&lt;fraction&gt;. Strength scales each: a multiplier m becomes 1 + (m - 1) x strength; an amount is multiplied by strength. A skill without a group's fields takes a quarter of the change as power instead, so no rune does nothing.</t>
   </si>
 </sst>
 </file>
@@ -4026,7 +4464,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="\+0.0;\-0.0;0.0"/>
   </numFmts>
-  <fonts count="30" x14ac:knownFonts="1">
+  <fonts count="31" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4202,6 +4640,13 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -4249,7 +4694,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -4387,6 +4832,9 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -4400,12 +4848,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -9252,32 +9701,32 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="59" t="s">
+      <c r="A2" s="60" t="s">
         <v>947</v>
       </c>
-      <c r="B2" s="58"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
-      <c r="I2" s="58"/>
-      <c r="J2" s="58"/>
+      <c r="B2" s="59"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
     </row>
     <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="57" t="s">
+      <c r="A3" s="58" t="s">
         <v>929</v>
       </c>
-      <c r="B3" s="58"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="58"/>
+      <c r="B3" s="59"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
     </row>
     <row r="5" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
@@ -9329,12 +9778,14 @@
       <c r="E6" s="10" t="s">
         <v>1213</v>
       </c>
-      <c r="F6" s="60"/>
+      <c r="F6" s="62" t="s">
+        <v>1391</v>
+      </c>
       <c r="G6" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B6,'Base Runes'!$A:$A,0)),"")</f>
         <v>Lull</v>
       </c>
-      <c r="H6" s="60"/>
+      <c r="H6" s="55"/>
       <c r="I6" s="10" t="s">
         <v>948</v>
       </c>
@@ -9358,12 +9809,14 @@
       <c r="E7" s="10" t="s">
         <v>949</v>
       </c>
-      <c r="F7" s="60"/>
+      <c r="F7" s="62" t="s">
+        <v>1392</v>
+      </c>
       <c r="G7" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B7,'Base Runes'!$A:$A,0)),"")</f>
         <v>Blow</v>
       </c>
-      <c r="H7" s="60"/>
+      <c r="H7" s="55"/>
       <c r="I7" s="10"/>
       <c r="J7" s="10"/>
     </row>
@@ -9385,12 +9838,14 @@
       <c r="E8" s="10" t="s">
         <v>1214</v>
       </c>
-      <c r="F8" s="60"/>
+      <c r="F8" s="62" t="s">
+        <v>1393</v>
+      </c>
       <c r="G8" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B8,'Base Runes'!$A:$A,0)),"")</f>
         <v>Buffer</v>
       </c>
-      <c r="H8" s="60"/>
+      <c r="H8" s="55"/>
       <c r="I8" s="10" t="s">
         <v>951</v>
       </c>
@@ -9414,12 +9869,14 @@
       <c r="E9" s="10" t="s">
         <v>952</v>
       </c>
-      <c r="F9" s="60"/>
+      <c r="F9" s="62" t="s">
+        <v>1394</v>
+      </c>
       <c r="G9" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B9,'Base Runes'!$A:$A,0)),"")</f>
         <v>Lash</v>
       </c>
-      <c r="H9" s="60"/>
+      <c r="H9" s="55"/>
       <c r="I9" s="10" t="s">
         <v>953</v>
       </c>
@@ -9443,12 +9900,14 @@
       <c r="E10" s="10" t="s">
         <v>1215</v>
       </c>
-      <c r="F10" s="60"/>
+      <c r="F10" s="62" t="s">
+        <v>1395</v>
+      </c>
       <c r="G10" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B10,'Base Runes'!$A:$A,0)),"")</f>
         <v>Drop</v>
       </c>
-      <c r="H10" s="60"/>
+      <c r="H10" s="55"/>
       <c r="I10" s="10" t="s">
         <v>225</v>
       </c>
@@ -9472,12 +9931,14 @@
       <c r="E11" s="10" t="s">
         <v>950</v>
       </c>
-      <c r="F11" s="60"/>
+      <c r="F11" s="62" t="s">
+        <v>1396</v>
+      </c>
       <c r="G11" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B11,'Base Runes'!$A:$A,0)),"")</f>
         <v>Lift</v>
       </c>
-      <c r="H11" s="60"/>
+      <c r="H11" s="55"/>
       <c r="I11" s="10" t="s">
         <v>229</v>
       </c>
@@ -9501,12 +9962,14 @@
       <c r="E12" s="10" t="s">
         <v>1216</v>
       </c>
-      <c r="F12" s="60"/>
+      <c r="F12" s="62" t="s">
+        <v>1397</v>
+      </c>
       <c r="G12" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B12,'Base Runes'!$A:$A,0)),"")</f>
         <v>Stall</v>
       </c>
-      <c r="H12" s="60"/>
+      <c r="H12" s="55"/>
       <c r="I12" s="10" t="s">
         <v>240</v>
       </c>
@@ -9530,12 +9993,14 @@
       <c r="E13" s="10" t="s">
         <v>1217</v>
       </c>
-      <c r="F13" s="60"/>
+      <c r="F13" s="62" t="s">
+        <v>1398</v>
+      </c>
       <c r="G13" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B13,'Base Runes'!$A:$A,0)),"")</f>
         <v>Carry</v>
       </c>
-      <c r="H13" s="60"/>
+      <c r="H13" s="55"/>
       <c r="I13" s="10"/>
       <c r="J13" s="10"/>
     </row>
@@ -9557,12 +10022,14 @@
       <c r="E14" s="10" t="s">
         <v>954</v>
       </c>
-      <c r="F14" s="60"/>
+      <c r="F14" s="62" t="s">
+        <v>1399</v>
+      </c>
       <c r="G14" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B14,'Base Runes'!$A:$A,0)),"")</f>
         <v>Disperse</v>
       </c>
-      <c r="H14" s="60"/>
+      <c r="H14" s="55"/>
       <c r="I14" s="10"/>
       <c r="J14" s="10"/>
     </row>
@@ -9584,12 +10051,14 @@
       <c r="E15" s="10" t="s">
         <v>955</v>
       </c>
-      <c r="F15" s="60"/>
+      <c r="F15" s="62" t="s">
+        <v>1400</v>
+      </c>
       <c r="G15" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B15,'Base Runes'!$A:$A,0)),"")</f>
         <v>Whirl</v>
       </c>
-      <c r="H15" s="60"/>
+      <c r="H15" s="55"/>
       <c r="I15" s="10"/>
       <c r="J15" s="10"/>
     </row>
@@ -9631,32 +10100,32 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="59" t="s">
+      <c r="A2" s="60" t="s">
         <v>956</v>
       </c>
-      <c r="B2" s="58"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
-      <c r="I2" s="58"/>
-      <c r="J2" s="58"/>
+      <c r="B2" s="59"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
     </row>
     <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="57" t="s">
+      <c r="A3" s="58" t="s">
         <v>929</v>
       </c>
-      <c r="B3" s="58"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="58"/>
+      <c r="B3" s="59"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
     </row>
     <row r="5" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
@@ -9708,12 +10177,14 @@
       <c r="E6" s="10" t="s">
         <v>1218</v>
       </c>
-      <c r="F6" s="60"/>
+      <c r="F6" s="62" t="s">
+        <v>1401</v>
+      </c>
       <c r="G6" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B6,'Base Runes'!$A:$A,0)),"")</f>
         <v>Ground</v>
       </c>
-      <c r="H6" s="60"/>
+      <c r="H6" s="55"/>
       <c r="I6" s="10"/>
       <c r="J6" s="10"/>
     </row>
@@ -9735,12 +10206,14 @@
       <c r="E7" s="10" t="s">
         <v>1219</v>
       </c>
-      <c r="F7" s="60"/>
+      <c r="F7" s="62" t="s">
+        <v>1373</v>
+      </c>
       <c r="G7" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B7,'Base Runes'!$A:$A,0)),"")</f>
         <v>Strike</v>
       </c>
-      <c r="H7" s="60"/>
+      <c r="H7" s="55"/>
       <c r="I7" s="10" t="s">
         <v>962</v>
       </c>
@@ -9764,12 +10237,14 @@
       <c r="E8" s="10" t="s">
         <v>957</v>
       </c>
-      <c r="F8" s="60"/>
+      <c r="F8" s="62" t="s">
+        <v>1402</v>
+      </c>
       <c r="G8" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B8,'Base Runes'!$A:$A,0)),"")</f>
         <v>Discharge</v>
       </c>
-      <c r="H8" s="60"/>
+      <c r="H8" s="55"/>
       <c r="I8" s="10" t="s">
         <v>958</v>
       </c>
@@ -9793,12 +10268,14 @@
       <c r="E9" s="10" t="s">
         <v>1220</v>
       </c>
-      <c r="F9" s="60"/>
+      <c r="F9" s="62" t="s">
+        <v>1403</v>
+      </c>
       <c r="G9" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B9,'Base Runes'!$A:$A,0)),"")</f>
         <v>Charge</v>
       </c>
-      <c r="H9" s="60"/>
+      <c r="H9" s="55"/>
       <c r="I9" s="10" t="s">
         <v>1221</v>
       </c>
@@ -9822,12 +10299,14 @@
       <c r="E10" s="10" t="s">
         <v>959</v>
       </c>
-      <c r="F10" s="60"/>
+      <c r="F10" s="62" t="s">
+        <v>1404</v>
+      </c>
       <c r="G10" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B10,'Base Runes'!$A:$A,0)),"")</f>
         <v>Insulate</v>
       </c>
-      <c r="H10" s="60"/>
+      <c r="H10" s="55"/>
       <c r="I10" s="10" t="s">
         <v>960</v>
       </c>
@@ -9851,12 +10330,14 @@
       <c r="E11" s="10" t="s">
         <v>961</v>
       </c>
-      <c r="F11" s="60"/>
+      <c r="F11" s="62" t="s">
+        <v>1405</v>
+      </c>
       <c r="G11" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B11,'Base Runes'!$A:$A,0)),"")</f>
         <v>Arc</v>
       </c>
-      <c r="H11" s="60"/>
+      <c r="H11" s="55"/>
       <c r="I11" s="10"/>
       <c r="J11" s="10"/>
     </row>
@@ -9878,12 +10359,14 @@
       <c r="E12" s="10" t="s">
         <v>963</v>
       </c>
-      <c r="F12" s="60"/>
+      <c r="F12" s="62" t="s">
+        <v>1406</v>
+      </c>
       <c r="G12" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B12,'Base Runes'!$A:$A,0)),"")</f>
         <v>Stun</v>
       </c>
-      <c r="H12" s="60"/>
+      <c r="H12" s="55"/>
       <c r="I12" s="10" t="s">
         <v>964</v>
       </c>
@@ -9907,12 +10390,14 @@
       <c r="E13" s="10" t="s">
         <v>965</v>
       </c>
-      <c r="F13" s="60"/>
+      <c r="F13" s="62" t="s">
+        <v>1407</v>
+      </c>
       <c r="G13" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B13,'Base Runes'!$A:$A,0)),"")</f>
         <v>Quicken</v>
       </c>
-      <c r="H13" s="60"/>
+      <c r="H13" s="55"/>
       <c r="I13" s="10"/>
       <c r="J13" s="10"/>
     </row>
@@ -9934,12 +10419,14 @@
       <c r="E14" s="10" t="s">
         <v>1222</v>
       </c>
-      <c r="F14" s="60"/>
+      <c r="F14" s="62" t="s">
+        <v>1408</v>
+      </c>
       <c r="G14" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B14,'Base Runes'!$A:$A,0)),"")</f>
         <v>Silence</v>
       </c>
-      <c r="H14" s="60"/>
+      <c r="H14" s="55"/>
       <c r="I14" s="10" t="s">
         <v>1223</v>
       </c>
@@ -9963,12 +10450,14 @@
       <c r="E15" s="10" t="s">
         <v>1224</v>
       </c>
-      <c r="F15" s="60"/>
+      <c r="F15" s="62" t="s">
+        <v>1377</v>
+      </c>
       <c r="G15" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B15,'Base Runes'!$A:$A,0)),"")</f>
         <v>Thunder</v>
       </c>
-      <c r="H15" s="60"/>
+      <c r="H15" s="55"/>
       <c r="I15" s="10"/>
       <c r="J15" s="10"/>
     </row>
@@ -10010,32 +10499,32 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="59" t="s">
+      <c r="A2" s="60" t="s">
         <v>966</v>
       </c>
-      <c r="B2" s="58"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
-      <c r="I2" s="58"/>
-      <c r="J2" s="58"/>
+      <c r="B2" s="59"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
     </row>
     <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="57" t="s">
+      <c r="A3" s="58" t="s">
         <v>967</v>
       </c>
-      <c r="B3" s="58"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="58"/>
+      <c r="B3" s="59"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
     </row>
     <row r="5" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
@@ -10087,12 +10576,12 @@
       <c r="E6" s="10" t="s">
         <v>968</v>
       </c>
-      <c r="F6" s="60"/>
+      <c r="F6" s="55"/>
       <c r="G6" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B6,'Base Runes'!$A:$A,0)),"")</f>
         <v>Thaw</v>
       </c>
-      <c r="H6" s="60"/>
+      <c r="H6" s="55"/>
       <c r="I6" s="10"/>
       <c r="J6" s="10"/>
     </row>
@@ -10114,12 +10603,12 @@
       <c r="E7" s="10" t="s">
         <v>969</v>
       </c>
-      <c r="F7" s="60"/>
+      <c r="F7" s="55"/>
       <c r="G7" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B7,'Base Runes'!$A:$A,0)),"")</f>
         <v>Freeze</v>
       </c>
-      <c r="H7" s="60"/>
+      <c r="H7" s="55"/>
       <c r="I7" s="10"/>
       <c r="J7" s="10"/>
     </row>
@@ -10141,12 +10630,12 @@
       <c r="E8" s="10" t="s">
         <v>971</v>
       </c>
-      <c r="F8" s="60"/>
+      <c r="F8" s="55"/>
       <c r="G8" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B8,'Base Runes'!$A:$A,0)),"")</f>
         <v>Glaze</v>
       </c>
-      <c r="H8" s="60"/>
+      <c r="H8" s="55"/>
       <c r="I8" s="10"/>
       <c r="J8" s="10"/>
     </row>
@@ -10168,12 +10657,12 @@
       <c r="E9" s="10" t="s">
         <v>1225</v>
       </c>
-      <c r="F9" s="60"/>
+      <c r="F9" s="55"/>
       <c r="G9" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B9,'Base Runes'!$A:$A,0)),"")</f>
         <v>Frost</v>
       </c>
-      <c r="H9" s="60"/>
+      <c r="H9" s="55"/>
       <c r="I9" s="10"/>
       <c r="J9" s="10"/>
     </row>
@@ -10195,12 +10684,12 @@
       <c r="E10" s="10" t="s">
         <v>1226</v>
       </c>
-      <c r="F10" s="60"/>
+      <c r="F10" s="55"/>
       <c r="G10" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B10,'Base Runes'!$A:$A,0)),"")</f>
         <v>Melt</v>
       </c>
-      <c r="H10" s="60"/>
+      <c r="H10" s="55"/>
       <c r="I10" s="10"/>
       <c r="J10" s="10"/>
     </row>
@@ -10222,12 +10711,12 @@
       <c r="E11" s="10" t="s">
         <v>1227</v>
       </c>
-      <c r="F11" s="60"/>
+      <c r="F11" s="55"/>
       <c r="G11" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B11,'Base Runes'!$A:$A,0)),"")</f>
         <v>Snow</v>
       </c>
-      <c r="H11" s="60"/>
+      <c r="H11" s="55"/>
       <c r="I11" s="10"/>
       <c r="J11" s="10"/>
     </row>
@@ -10249,12 +10738,12 @@
       <c r="E12" s="10" t="s">
         <v>1228</v>
       </c>
-      <c r="F12" s="60"/>
+      <c r="F12" s="55"/>
       <c r="G12" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B12,'Base Runes'!$A:$A,0)),"")</f>
         <v>Shatter</v>
       </c>
-      <c r="H12" s="60"/>
+      <c r="H12" s="55"/>
       <c r="I12" s="10"/>
       <c r="J12" s="10"/>
     </row>
@@ -10276,12 +10765,12 @@
       <c r="E13" s="10" t="s">
         <v>970</v>
       </c>
-      <c r="F13" s="60"/>
+      <c r="F13" s="55"/>
       <c r="G13" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B13,'Base Runes'!$A:$A,0)),"")</f>
         <v>Rime</v>
       </c>
-      <c r="H13" s="60"/>
+      <c r="H13" s="55"/>
       <c r="I13" s="10"/>
       <c r="J13" s="10"/>
     </row>
@@ -10303,12 +10792,12 @@
       <c r="E14" s="10" t="s">
         <v>972</v>
       </c>
-      <c r="F14" s="60"/>
+      <c r="F14" s="55"/>
       <c r="G14" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B14,'Base Runes'!$A:$A,0)),"")</f>
         <v>Toughen</v>
       </c>
-      <c r="H14" s="60"/>
+      <c r="H14" s="55"/>
       <c r="I14" s="10"/>
       <c r="J14" s="10"/>
     </row>
@@ -10330,12 +10819,12 @@
       <c r="E15" s="10" t="s">
         <v>973</v>
       </c>
-      <c r="F15" s="60"/>
+      <c r="F15" s="55"/>
       <c r="G15" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B15,'Base Runes'!$A:$A,0)),"")</f>
         <v>Brittle</v>
       </c>
-      <c r="H15" s="60"/>
+      <c r="H15" s="55"/>
       <c r="I15" s="10"/>
       <c r="J15" s="10"/>
     </row>
@@ -10377,32 +10866,32 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="59" t="s">
+      <c r="A2" s="60" t="s">
         <v>974</v>
       </c>
-      <c r="B2" s="58"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
-      <c r="I2" s="58"/>
-      <c r="J2" s="58"/>
+      <c r="B2" s="59"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
     </row>
     <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="57" t="s">
+      <c r="A3" s="58" t="s">
         <v>975</v>
       </c>
-      <c r="B3" s="58"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="58"/>
+      <c r="B3" s="59"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
     </row>
     <row r="5" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
@@ -10454,12 +10943,12 @@
       <c r="E6" s="10" t="s">
         <v>976</v>
       </c>
-      <c r="F6" s="60"/>
+      <c r="F6" s="55"/>
       <c r="G6" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B6,'Base Runes'!$A:$A,0)),"")</f>
         <v>Lighten</v>
       </c>
-      <c r="H6" s="60"/>
+      <c r="H6" s="55"/>
       <c r="I6" s="10"/>
       <c r="J6" s="10"/>
     </row>
@@ -10481,12 +10970,12 @@
       <c r="E7" s="10" t="s">
         <v>977</v>
       </c>
-      <c r="F7" s="60"/>
+      <c r="F7" s="55"/>
       <c r="G7" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B7,'Base Runes'!$A:$A,0)),"")</f>
         <v>Darken</v>
       </c>
-      <c r="H7" s="60"/>
+      <c r="H7" s="55"/>
       <c r="I7" s="10"/>
       <c r="J7" s="10"/>
     </row>
@@ -10508,12 +10997,12 @@
       <c r="E8" s="10" t="s">
         <v>1229</v>
       </c>
-      <c r="F8" s="60"/>
+      <c r="F8" s="55"/>
       <c r="G8" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B8,'Base Runes'!$A:$A,0)),"")</f>
         <v>Expose</v>
       </c>
-      <c r="H8" s="60"/>
+      <c r="H8" s="55"/>
       <c r="I8" s="10"/>
       <c r="J8" s="10"/>
     </row>
@@ -10535,12 +11024,12 @@
       <c r="E9" s="10" t="s">
         <v>1230</v>
       </c>
-      <c r="F9" s="60"/>
+      <c r="F9" s="55"/>
       <c r="G9" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B9,'Base Runes'!$A:$A,0)),"")</f>
         <v>Obscure</v>
       </c>
-      <c r="H9" s="60"/>
+      <c r="H9" s="55"/>
       <c r="I9" s="10"/>
       <c r="J9" s="10"/>
     </row>
@@ -10562,12 +11051,12 @@
       <c r="E10" s="10" t="s">
         <v>978</v>
       </c>
-      <c r="F10" s="60"/>
+      <c r="F10" s="55"/>
       <c r="G10" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B10,'Base Runes'!$A:$A,0)),"")</f>
         <v>Pin</v>
       </c>
-      <c r="H10" s="60"/>
+      <c r="H10" s="55"/>
       <c r="I10" s="10"/>
       <c r="J10" s="10"/>
     </row>
@@ -10589,12 +11078,12 @@
       <c r="E11" s="10" t="s">
         <v>979</v>
       </c>
-      <c r="F11" s="60"/>
+      <c r="F11" s="55"/>
       <c r="G11" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B11,'Base Runes'!$A:$A,0)),"")</f>
         <v>Shadowstep</v>
       </c>
-      <c r="H11" s="60"/>
+      <c r="H11" s="55"/>
       <c r="I11" s="10"/>
       <c r="J11" s="10"/>
     </row>
@@ -10616,12 +11105,12 @@
       <c r="E12" s="10" t="s">
         <v>1231</v>
       </c>
-      <c r="F12" s="60"/>
+      <c r="F12" s="55"/>
       <c r="G12" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B12,'Base Runes'!$A:$A,0)),"")</f>
         <v>Resound</v>
       </c>
-      <c r="H12" s="60"/>
+      <c r="H12" s="55"/>
       <c r="I12" s="10"/>
       <c r="J12" s="10"/>
     </row>
@@ -10643,12 +11132,12 @@
       <c r="E13" s="10" t="s">
         <v>1232</v>
       </c>
-      <c r="F13" s="60"/>
+      <c r="F13" s="55"/>
       <c r="G13" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B13,'Base Runes'!$A:$A,0)),"")</f>
         <v>Hush</v>
       </c>
-      <c r="H13" s="60"/>
+      <c r="H13" s="55"/>
       <c r="I13" s="10"/>
       <c r="J13" s="10"/>
     </row>
@@ -10670,12 +11159,12 @@
       <c r="E14" s="10" t="s">
         <v>980</v>
       </c>
-      <c r="F14" s="60"/>
+      <c r="F14" s="55"/>
       <c r="G14" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B14,'Base Runes'!$A:$A,0)),"")</f>
         <v>Disgorge</v>
       </c>
-      <c r="H14" s="60"/>
+      <c r="H14" s="55"/>
       <c r="I14" s="10"/>
       <c r="J14" s="10"/>
     </row>
@@ -10697,12 +11186,12 @@
       <c r="E15" s="10" t="s">
         <v>981</v>
       </c>
-      <c r="F15" s="60"/>
+      <c r="F15" s="55"/>
       <c r="G15" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B15,'Base Runes'!$A:$A,0)),"")</f>
         <v>Devour</v>
       </c>
-      <c r="H15" s="60"/>
+      <c r="H15" s="55"/>
       <c r="I15" s="10"/>
       <c r="J15" s="10"/>
     </row>
@@ -10744,32 +11233,32 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="59" t="s">
+      <c r="A2" s="60" t="s">
         <v>982</v>
       </c>
-      <c r="B2" s="58"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
-      <c r="I2" s="58"/>
-      <c r="J2" s="58"/>
+      <c r="B2" s="59"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
     </row>
     <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="57" t="s">
+      <c r="A3" s="58" t="s">
         <v>983</v>
       </c>
-      <c r="B3" s="58"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="58"/>
+      <c r="B3" s="59"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
     </row>
     <row r="5" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
@@ -10821,12 +11310,12 @@
       <c r="E6" s="10" t="s">
         <v>984</v>
       </c>
-      <c r="F6" s="60"/>
+      <c r="F6" s="55"/>
       <c r="G6" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B6,'Base Runes'!$A:$A,0)),"")</f>
         <v>Rust</v>
       </c>
-      <c r="H6" s="60"/>
+      <c r="H6" s="55"/>
       <c r="I6" s="10"/>
       <c r="J6" s="10"/>
     </row>
@@ -10848,12 +11337,12 @@
       <c r="E7" s="10" t="s">
         <v>985</v>
       </c>
-      <c r="F7" s="60"/>
+      <c r="F7" s="55"/>
       <c r="G7" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B7,'Base Runes'!$A:$A,0)),"")</f>
         <v>Forge</v>
       </c>
-      <c r="H7" s="60"/>
+      <c r="H7" s="55"/>
       <c r="I7" s="10"/>
       <c r="J7" s="10"/>
     </row>
@@ -10875,12 +11364,12 @@
       <c r="E8" s="10" t="s">
         <v>1233</v>
       </c>
-      <c r="F8" s="60"/>
+      <c r="F8" s="55"/>
       <c r="G8" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B8,'Base Runes'!$A:$A,0)),"")</f>
         <v>Sunder</v>
       </c>
-      <c r="H8" s="60"/>
+      <c r="H8" s="55"/>
       <c r="I8" s="10"/>
       <c r="J8" s="10"/>
     </row>
@@ -10902,12 +11391,12 @@
       <c r="E9" s="10" t="s">
         <v>1234</v>
       </c>
-      <c r="F9" s="60"/>
+      <c r="F9" s="55"/>
       <c r="G9" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B9,'Base Runes'!$A:$A,0)),"")</f>
         <v>Fuse</v>
       </c>
-      <c r="H9" s="60"/>
+      <c r="H9" s="55"/>
       <c r="I9" s="10"/>
       <c r="J9" s="10"/>
     </row>
@@ -10929,12 +11418,12 @@
       <c r="E10" s="10" t="s">
         <v>1235</v>
       </c>
-      <c r="F10" s="60"/>
+      <c r="F10" s="55"/>
       <c r="G10" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B10,'Base Runes'!$A:$A,0)),"")</f>
         <v>Breach</v>
       </c>
-      <c r="H10" s="60"/>
+      <c r="H10" s="55"/>
       <c r="I10" s="10"/>
       <c r="J10" s="10"/>
     </row>
@@ -10956,12 +11445,12 @@
       <c r="E11" s="10" t="s">
         <v>1236</v>
       </c>
-      <c r="F11" s="60"/>
+      <c r="F11" s="55"/>
       <c r="G11" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B11,'Base Runes'!$A:$A,0)),"")</f>
         <v>Seal</v>
       </c>
-      <c r="H11" s="60"/>
+      <c r="H11" s="55"/>
       <c r="I11" s="10"/>
       <c r="J11" s="10"/>
     </row>
@@ -10983,12 +11472,12 @@
       <c r="E12" s="10" t="s">
         <v>986</v>
       </c>
-      <c r="F12" s="60"/>
+      <c r="F12" s="55"/>
       <c r="G12" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B12,'Base Runes'!$A:$A,0)),"")</f>
         <v>Dull</v>
       </c>
-      <c r="H12" s="60"/>
+      <c r="H12" s="55"/>
       <c r="I12" s="10"/>
       <c r="J12" s="10"/>
     </row>
@@ -11010,12 +11499,12 @@
       <c r="E13" s="10" t="s">
         <v>987</v>
       </c>
-      <c r="F13" s="60"/>
+      <c r="F13" s="55"/>
       <c r="G13" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B13,'Base Runes'!$A:$A,0)),"")</f>
         <v>Hone</v>
       </c>
-      <c r="H13" s="60"/>
+      <c r="H13" s="55"/>
       <c r="I13" s="10"/>
       <c r="J13" s="10"/>
     </row>
@@ -11037,12 +11526,12 @@
       <c r="E14" s="10" t="s">
         <v>988</v>
       </c>
-      <c r="F14" s="60"/>
+      <c r="F14" s="55"/>
       <c r="G14" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B14,'Base Runes'!$A:$A,0)),"")</f>
         <v>Strip</v>
       </c>
-      <c r="H14" s="60"/>
+      <c r="H14" s="55"/>
       <c r="I14" s="10"/>
       <c r="J14" s="10"/>
     </row>
@@ -11064,12 +11553,12 @@
       <c r="E15" s="10" t="s">
         <v>989</v>
       </c>
-      <c r="F15" s="60"/>
+      <c r="F15" s="55"/>
       <c r="G15" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B15,'Base Runes'!$A:$A,0)),"")</f>
         <v>Plate</v>
       </c>
-      <c r="H15" s="60"/>
+      <c r="H15" s="55"/>
       <c r="I15" s="10"/>
       <c r="J15" s="10"/>
     </row>
@@ -11111,32 +11600,32 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="59" t="s">
+      <c r="A2" s="60" t="s">
         <v>990</v>
       </c>
-      <c r="B2" s="58"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
-      <c r="I2" s="58"/>
-      <c r="J2" s="58"/>
+      <c r="B2" s="59"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
     </row>
     <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="57" t="s">
+      <c r="A3" s="58" t="s">
         <v>991</v>
       </c>
-      <c r="B3" s="58"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="58"/>
+      <c r="B3" s="59"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
     </row>
     <row r="5" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
@@ -11188,12 +11677,12 @@
       <c r="E6" s="10" t="s">
         <v>992</v>
       </c>
-      <c r="F6" s="60"/>
+      <c r="F6" s="55"/>
       <c r="G6" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B6,'Base Runes'!$A:$A,0)),"")</f>
         <v>Staunch</v>
       </c>
-      <c r="H6" s="60"/>
+      <c r="H6" s="55"/>
       <c r="I6" s="10"/>
       <c r="J6" s="10"/>
     </row>
@@ -11215,12 +11704,12 @@
       <c r="E7" s="10" t="s">
         <v>993</v>
       </c>
-      <c r="F7" s="60"/>
+      <c r="F7" s="55"/>
       <c r="G7" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B7,'Base Runes'!$A:$A,0)),"")</f>
         <v>Bleed</v>
       </c>
-      <c r="H7" s="60"/>
+      <c r="H7" s="55"/>
       <c r="I7" s="10"/>
       <c r="J7" s="10"/>
     </row>
@@ -11242,12 +11731,12 @@
       <c r="E8" s="10" t="s">
         <v>994</v>
       </c>
-      <c r="F8" s="60"/>
+      <c r="F8" s="55"/>
       <c r="G8" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B8,'Base Runes'!$A:$A,0)),"")</f>
         <v>Spill</v>
       </c>
-      <c r="H8" s="60"/>
+      <c r="H8" s="55"/>
       <c r="I8" s="10"/>
       <c r="J8" s="10"/>
     </row>
@@ -11269,12 +11758,12 @@
       <c r="E9" s="10" t="s">
         <v>995</v>
       </c>
-      <c r="F9" s="60"/>
+      <c r="F9" s="55"/>
       <c r="G9" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B9,'Base Runes'!$A:$A,0)),"")</f>
         <v>Drink</v>
       </c>
-      <c r="H9" s="60"/>
+      <c r="H9" s="55"/>
       <c r="I9" s="10"/>
       <c r="J9" s="10"/>
     </row>
@@ -11296,12 +11785,12 @@
       <c r="E10" s="10" t="s">
         <v>1237</v>
       </c>
-      <c r="F10" s="60"/>
+      <c r="F10" s="55"/>
       <c r="G10" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B10,'Base Runes'!$A:$A,0)),"")</f>
         <v>Thin</v>
       </c>
-      <c r="H10" s="60"/>
+      <c r="H10" s="55"/>
       <c r="I10" s="10"/>
       <c r="J10" s="10"/>
     </row>
@@ -11323,12 +11812,12 @@
       <c r="E11" s="10" t="s">
         <v>1238</v>
       </c>
-      <c r="F11" s="60"/>
+      <c r="F11" s="55"/>
       <c r="G11" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B11,'Base Runes'!$A:$A,0)),"")</f>
         <v>Clot</v>
       </c>
-      <c r="H11" s="60"/>
+      <c r="H11" s="55"/>
       <c r="I11" s="10"/>
       <c r="J11" s="10"/>
     </row>
@@ -11350,12 +11839,12 @@
       <c r="E12" s="10" t="s">
         <v>996</v>
       </c>
-      <c r="F12" s="60"/>
+      <c r="F12" s="55"/>
       <c r="G12" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B12,'Base Runes'!$A:$A,0)),"")</f>
         <v>Still</v>
       </c>
-      <c r="H12" s="60"/>
+      <c r="H12" s="55"/>
       <c r="I12" s="10"/>
       <c r="J12" s="10"/>
     </row>
@@ -11377,12 +11866,12 @@
       <c r="E13" s="10" t="s">
         <v>997</v>
       </c>
-      <c r="F13" s="60"/>
+      <c r="F13" s="55"/>
       <c r="G13" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B13,'Base Runes'!$A:$A,0)),"")</f>
         <v>Pulse</v>
       </c>
-      <c r="H13" s="60"/>
+      <c r="H13" s="55"/>
       <c r="I13" s="10"/>
       <c r="J13" s="10"/>
     </row>
@@ -11404,12 +11893,12 @@
       <c r="E14" s="10" t="s">
         <v>1239</v>
       </c>
-      <c r="F14" s="60"/>
+      <c r="F14" s="55"/>
       <c r="G14" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B14,'Base Runes'!$A:$A,0)),"")</f>
         <v>Breathe</v>
       </c>
-      <c r="H14" s="60"/>
+      <c r="H14" s="55"/>
       <c r="I14" s="10"/>
       <c r="J14" s="10"/>
     </row>
@@ -11431,12 +11920,12 @@
       <c r="E15" s="10" t="s">
         <v>1240</v>
       </c>
-      <c r="F15" s="60"/>
+      <c r="F15" s="55"/>
       <c r="G15" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B15,'Base Runes'!$A:$A,0)),"")</f>
         <v>Choke</v>
       </c>
-      <c r="H15" s="60"/>
+      <c r="H15" s="55"/>
       <c r="I15" s="10"/>
       <c r="J15" s="10"/>
     </row>
@@ -11478,32 +11967,32 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="59" t="s">
+      <c r="A2" s="60" t="s">
         <v>998</v>
       </c>
-      <c r="B2" s="58"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
-      <c r="I2" s="58"/>
-      <c r="J2" s="58"/>
+      <c r="B2" s="59"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
     </row>
     <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="57" t="s">
+      <c r="A3" s="58" t="s">
         <v>999</v>
       </c>
-      <c r="B3" s="58"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="58"/>
+      <c r="B3" s="59"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
     </row>
     <row r="5" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
@@ -11555,12 +12044,12 @@
       <c r="E6" s="10" t="s">
         <v>1241</v>
       </c>
-      <c r="F6" s="60"/>
+      <c r="F6" s="55"/>
       <c r="G6" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B6,'Base Runes'!$A:$A,0)),"")</f>
         <v>Wither</v>
       </c>
-      <c r="H6" s="60"/>
+      <c r="H6" s="55"/>
       <c r="I6" s="10"/>
       <c r="J6" s="10"/>
     </row>
@@ -11582,12 +12071,12 @@
       <c r="E7" s="10" t="s">
         <v>1000</v>
       </c>
-      <c r="F7" s="60"/>
+      <c r="F7" s="55"/>
       <c r="G7" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B7,'Base Runes'!$A:$A,0)),"")</f>
         <v>Heal</v>
       </c>
-      <c r="H7" s="60"/>
+      <c r="H7" s="55"/>
       <c r="I7" s="10"/>
       <c r="J7" s="10"/>
     </row>
@@ -11609,12 +12098,12 @@
       <c r="E8" s="10" t="s">
         <v>1242</v>
       </c>
-      <c r="F8" s="60"/>
+      <c r="F8" s="55"/>
       <c r="G8" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B8,'Base Runes'!$A:$A,0)),"")</f>
         <v>Exhaust</v>
       </c>
-      <c r="H8" s="60"/>
+      <c r="H8" s="55"/>
       <c r="I8" s="10"/>
       <c r="J8" s="10"/>
     </row>
@@ -11636,12 +12125,12 @@
       <c r="E9" s="10" t="s">
         <v>1243</v>
       </c>
-      <c r="F9" s="60"/>
+      <c r="F9" s="55"/>
       <c r="G9" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B9,'Base Runes'!$A:$A,0)),"")</f>
         <v>Renew</v>
       </c>
-      <c r="H9" s="60"/>
+      <c r="H9" s="55"/>
       <c r="I9" s="10"/>
       <c r="J9" s="10"/>
     </row>
@@ -11663,12 +12152,12 @@
       <c r="E10" s="10" t="s">
         <v>1001</v>
       </c>
-      <c r="F10" s="60"/>
+      <c r="F10" s="55"/>
       <c r="G10" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B10,'Base Runes'!$A:$A,0)),"")</f>
         <v>Weaken</v>
       </c>
-      <c r="H10" s="60"/>
+      <c r="H10" s="55"/>
       <c r="I10" s="10"/>
       <c r="J10" s="10"/>
     </row>
@@ -11690,12 +12179,12 @@
       <c r="E11" s="10" t="s">
         <v>1244</v>
       </c>
-      <c r="F11" s="60"/>
+      <c r="F11" s="55"/>
       <c r="G11" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B11,'Base Runes'!$A:$A,0)),"")</f>
         <v>Strengthen</v>
       </c>
-      <c r="H11" s="60"/>
+      <c r="H11" s="55"/>
       <c r="I11" s="10"/>
       <c r="J11" s="10"/>
     </row>
@@ -11717,12 +12206,12 @@
       <c r="E12" s="10" t="s">
         <v>1245</v>
       </c>
-      <c r="F12" s="60"/>
+      <c r="F12" s="55"/>
       <c r="G12" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B12,'Base Runes'!$A:$A,0)),"")</f>
         <v>Sicken</v>
       </c>
-      <c r="H12" s="60"/>
+      <c r="H12" s="55"/>
       <c r="I12" s="10"/>
       <c r="J12" s="10"/>
     </row>
@@ -11744,12 +12233,12 @@
       <c r="E13" s="10" t="s">
         <v>1246</v>
       </c>
-      <c r="F13" s="60"/>
+      <c r="F13" s="55"/>
       <c r="G13" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B13,'Base Runes'!$A:$A,0)),"")</f>
         <v>Cure</v>
       </c>
-      <c r="H13" s="60"/>
+      <c r="H13" s="55"/>
       <c r="I13" s="10"/>
       <c r="J13" s="10"/>
     </row>
@@ -11771,12 +12260,12 @@
       <c r="E14" s="10" t="s">
         <v>1002</v>
       </c>
-      <c r="F14" s="60"/>
+      <c r="F14" s="55"/>
       <c r="G14" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B14,'Base Runes'!$A:$A,0)),"")</f>
         <v>Arrest</v>
       </c>
-      <c r="H14" s="60"/>
+      <c r="H14" s="55"/>
       <c r="I14" s="10"/>
       <c r="J14" s="10"/>
     </row>
@@ -11798,12 +12287,12 @@
       <c r="E15" s="10" t="s">
         <v>1003</v>
       </c>
-      <c r="F15" s="60"/>
+      <c r="F15" s="55"/>
       <c r="G15" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B15,'Base Runes'!$A:$A,0)),"")</f>
         <v>Regrow</v>
       </c>
-      <c r="H15" s="60"/>
+      <c r="H15" s="55"/>
       <c r="I15" s="10"/>
       <c r="J15" s="10"/>
     </row>
@@ -11845,32 +12334,32 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="59" t="s">
+      <c r="A2" s="60" t="s">
         <v>1004</v>
       </c>
-      <c r="B2" s="58"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
-      <c r="I2" s="58"/>
-      <c r="J2" s="58"/>
+      <c r="B2" s="59"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
     </row>
     <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="57" t="s">
+      <c r="A3" s="58" t="s">
         <v>1005</v>
       </c>
-      <c r="B3" s="58"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="58"/>
+      <c r="B3" s="59"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
     </row>
     <row r="5" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
@@ -11922,12 +12411,12 @@
       <c r="E6" s="10" t="s">
         <v>1006</v>
       </c>
-      <c r="F6" s="60"/>
+      <c r="F6" s="55"/>
       <c r="G6" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B6,'Base Runes'!$A:$A,0)),"")</f>
         <v>Spare</v>
       </c>
-      <c r="H6" s="60"/>
+      <c r="H6" s="55"/>
       <c r="I6" s="10"/>
       <c r="J6" s="10"/>
     </row>
@@ -11949,12 +12438,12 @@
       <c r="E7" s="10" t="s">
         <v>1007</v>
       </c>
-      <c r="F7" s="60"/>
+      <c r="F7" s="55"/>
       <c r="G7" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B7,'Base Runes'!$A:$A,0)),"")</f>
         <v>Kill</v>
       </c>
-      <c r="H7" s="60"/>
+      <c r="H7" s="55"/>
       <c r="I7" s="10"/>
       <c r="J7" s="10"/>
     </row>
@@ -11976,12 +12465,12 @@
       <c r="E8" s="10" t="s">
         <v>1008</v>
       </c>
-      <c r="F8" s="60"/>
+      <c r="F8" s="55"/>
       <c r="G8" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B8,'Base Runes'!$A:$A,0)),"")</f>
         <v>Lay</v>
       </c>
-      <c r="H8" s="60"/>
+      <c r="H8" s="55"/>
       <c r="I8" s="10"/>
       <c r="J8" s="10"/>
     </row>
@@ -12003,12 +12492,12 @@
       <c r="E9" s="10" t="s">
         <v>1009</v>
       </c>
-      <c r="F9" s="60"/>
+      <c r="F9" s="55"/>
       <c r="G9" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B9,'Base Runes'!$A:$A,0)),"")</f>
         <v>Animate</v>
       </c>
-      <c r="H9" s="60"/>
+      <c r="H9" s="55"/>
       <c r="I9" s="10"/>
       <c r="J9" s="10"/>
     </row>
@@ -12030,12 +12519,12 @@
       <c r="E10" s="10" t="s">
         <v>1010</v>
       </c>
-      <c r="F10" s="60"/>
+      <c r="F10" s="55"/>
       <c r="G10" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B10,'Base Runes'!$A:$A,0)),"")</f>
         <v>Preserve</v>
       </c>
-      <c r="H10" s="60"/>
+      <c r="H10" s="55"/>
       <c r="I10" s="10"/>
       <c r="J10" s="10"/>
     </row>
@@ -12057,12 +12546,12 @@
       <c r="E11" s="10" t="s">
         <v>1011</v>
       </c>
-      <c r="F11" s="60"/>
+      <c r="F11" s="55"/>
       <c r="G11" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B11,'Base Runes'!$A:$A,0)),"")</f>
         <v>Rot</v>
       </c>
-      <c r="H11" s="60"/>
+      <c r="H11" s="55"/>
       <c r="I11" s="10"/>
       <c r="J11" s="10"/>
     </row>
@@ -12084,12 +12573,12 @@
       <c r="E12" s="10" t="s">
         <v>1012</v>
       </c>
-      <c r="F12" s="60"/>
+      <c r="F12" s="55"/>
       <c r="G12" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B12,'Base Runes'!$A:$A,0)),"")</f>
         <v>Exorcise</v>
       </c>
-      <c r="H12" s="60"/>
+      <c r="H12" s="55"/>
       <c r="I12" s="10"/>
       <c r="J12" s="10"/>
     </row>
@@ -12111,12 +12600,12 @@
       <c r="E13" s="10" t="s">
         <v>1013</v>
       </c>
-      <c r="F13" s="60"/>
+      <c r="F13" s="55"/>
       <c r="G13" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B13,'Base Runes'!$A:$A,0)),"")</f>
         <v>Haunt</v>
       </c>
-      <c r="H13" s="60"/>
+      <c r="H13" s="55"/>
       <c r="I13" s="10"/>
       <c r="J13" s="10"/>
     </row>
@@ -12138,12 +12627,12 @@
       <c r="E14" s="10" t="s">
         <v>1247</v>
       </c>
-      <c r="F14" s="60"/>
+      <c r="F14" s="55"/>
       <c r="G14" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B14,'Base Runes'!$A:$A,0)),"")</f>
         <v>Manifest</v>
       </c>
-      <c r="H14" s="60"/>
+      <c r="H14" s="55"/>
       <c r="I14" s="10"/>
       <c r="J14" s="10"/>
     </row>
@@ -12165,12 +12654,12 @@
       <c r="E15" s="10" t="s">
         <v>1248</v>
       </c>
-      <c r="F15" s="60"/>
+      <c r="F15" s="55"/>
       <c r="G15" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B15,'Base Runes'!$A:$A,0)),"")</f>
         <v>Vanish</v>
       </c>
-      <c r="H15" s="60"/>
+      <c r="H15" s="55"/>
       <c r="I15" s="10"/>
       <c r="J15" s="10"/>
     </row>
@@ -12212,32 +12701,32 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="59" t="s">
+      <c r="A2" s="60" t="s">
         <v>1014</v>
       </c>
-      <c r="B2" s="58"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
-      <c r="I2" s="58"/>
-      <c r="J2" s="58"/>
+      <c r="B2" s="59"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
     </row>
     <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="57" t="s">
+      <c r="A3" s="58" t="s">
         <v>1015</v>
       </c>
-      <c r="B3" s="58"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="58"/>
+      <c r="B3" s="59"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
     </row>
     <row r="5" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
@@ -12289,12 +12778,12 @@
       <c r="E6" s="10" t="s">
         <v>1249</v>
       </c>
-      <c r="F6" s="60"/>
+      <c r="F6" s="55"/>
       <c r="G6" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B6,'Base Runes'!$A:$A,0)),"")</f>
         <v>Shrink</v>
       </c>
-      <c r="H6" s="60"/>
+      <c r="H6" s="55"/>
       <c r="I6" s="10"/>
       <c r="J6" s="10"/>
     </row>
@@ -12316,12 +12805,12 @@
       <c r="E7" s="10" t="s">
         <v>1250</v>
       </c>
-      <c r="F7" s="60"/>
+      <c r="F7" s="55"/>
       <c r="G7" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B7,'Base Runes'!$A:$A,0)),"")</f>
         <v>Grow</v>
       </c>
-      <c r="H7" s="60"/>
+      <c r="H7" s="55"/>
       <c r="I7" s="10"/>
       <c r="J7" s="10"/>
     </row>
@@ -12343,12 +12832,12 @@
       <c r="E8" s="10" t="s">
         <v>1251</v>
       </c>
-      <c r="F8" s="60"/>
+      <c r="F8" s="55"/>
       <c r="G8" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B8,'Base Runes'!$A:$A,0)),"")</f>
         <v>Wilt</v>
       </c>
-      <c r="H8" s="60"/>
+      <c r="H8" s="55"/>
       <c r="I8" s="10"/>
       <c r="J8" s="10"/>
     </row>
@@ -12370,12 +12859,12 @@
       <c r="E9" s="10" t="s">
         <v>1252</v>
       </c>
-      <c r="F9" s="60"/>
+      <c r="F9" s="55"/>
       <c r="G9" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B9,'Base Runes'!$A:$A,0)),"")</f>
         <v>Sprout</v>
       </c>
-      <c r="H9" s="60"/>
+      <c r="H9" s="55"/>
       <c r="I9" s="10"/>
       <c r="J9" s="10"/>
     </row>
@@ -12397,12 +12886,12 @@
       <c r="E10" s="10" t="s">
         <v>1253</v>
       </c>
-      <c r="F10" s="60"/>
+      <c r="F10" s="55"/>
       <c r="G10" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B10,'Base Runes'!$A:$A,0)),"")</f>
         <v>Blight</v>
       </c>
-      <c r="H10" s="60"/>
+      <c r="H10" s="55"/>
       <c r="I10" s="10"/>
       <c r="J10" s="10"/>
     </row>
@@ -12424,12 +12913,12 @@
       <c r="E11" s="10" t="s">
         <v>1254</v>
       </c>
-      <c r="F11" s="60"/>
+      <c r="F11" s="55"/>
       <c r="G11" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B11,'Base Runes'!$A:$A,0)),"")</f>
         <v>Flourish</v>
       </c>
-      <c r="H11" s="60"/>
+      <c r="H11" s="55"/>
       <c r="I11" s="10"/>
       <c r="J11" s="10"/>
     </row>
@@ -12451,12 +12940,12 @@
       <c r="E12" s="10" t="s">
         <v>1255</v>
       </c>
-      <c r="F12" s="60"/>
+      <c r="F12" s="55"/>
       <c r="G12" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B12,'Base Runes'!$A:$A,0)),"")</f>
         <v>Sow</v>
       </c>
-      <c r="H12" s="60"/>
+      <c r="H12" s="55"/>
       <c r="I12" s="10"/>
       <c r="J12" s="10"/>
     </row>
@@ -12478,12 +12967,12 @@
       <c r="E13" s="10" t="s">
         <v>1018</v>
       </c>
-      <c r="F13" s="60"/>
+      <c r="F13" s="55"/>
       <c r="G13" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B13,'Base Runes'!$A:$A,0)),"")</f>
         <v>Harvest</v>
       </c>
-      <c r="H13" s="60"/>
+      <c r="H13" s="55"/>
       <c r="I13" s="10"/>
       <c r="J13" s="10"/>
     </row>
@@ -12505,12 +12994,12 @@
       <c r="E14" s="10" t="s">
         <v>1016</v>
       </c>
-      <c r="F14" s="60"/>
+      <c r="F14" s="55"/>
       <c r="G14" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B14,'Base Runes'!$A:$A,0)),"")</f>
         <v>Unravel</v>
       </c>
-      <c r="H14" s="60"/>
+      <c r="H14" s="55"/>
       <c r="I14" s="10"/>
       <c r="J14" s="10"/>
     </row>
@@ -12532,12 +13021,12 @@
       <c r="E15" s="10" t="s">
         <v>1017</v>
       </c>
-      <c r="F15" s="60"/>
+      <c r="F15" s="55"/>
       <c r="G15" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B15,'Base Runes'!$A:$A,0)),"")</f>
         <v>Tangle</v>
       </c>
-      <c r="H15" s="60"/>
+      <c r="H15" s="55"/>
       <c r="I15" s="10"/>
       <c r="J15" s="10"/>
     </row>
@@ -12579,32 +13068,32 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="59" t="s">
+      <c r="A2" s="60" t="s">
         <v>1019</v>
       </c>
-      <c r="B2" s="58"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
-      <c r="I2" s="58"/>
-      <c r="J2" s="58"/>
+      <c r="B2" s="59"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
     </row>
     <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="57" t="s">
+      <c r="A3" s="58" t="s">
         <v>1020</v>
       </c>
-      <c r="B3" s="58"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="58"/>
+      <c r="B3" s="59"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
     </row>
     <row r="5" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
@@ -12656,12 +13145,12 @@
       <c r="E6" s="10" t="s">
         <v>1021</v>
       </c>
-      <c r="F6" s="60"/>
+      <c r="F6" s="55"/>
       <c r="G6" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B6,'Base Runes'!$A:$A,0)),"")</f>
         <v>Dim</v>
       </c>
-      <c r="H6" s="60"/>
+      <c r="H6" s="55"/>
       <c r="I6" s="10"/>
       <c r="J6" s="10"/>
     </row>
@@ -12683,12 +13172,12 @@
       <c r="E7" s="10" t="s">
         <v>1256</v>
       </c>
-      <c r="F7" s="60"/>
+      <c r="F7" s="55"/>
       <c r="G7" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B7,'Base Runes'!$A:$A,0)),"")</f>
         <v>Shine</v>
       </c>
-      <c r="H7" s="60"/>
+      <c r="H7" s="55"/>
       <c r="I7" s="10"/>
       <c r="J7" s="10"/>
     </row>
@@ -12710,12 +13199,12 @@
       <c r="E8" s="10" t="s">
         <v>1257</v>
       </c>
-      <c r="F8" s="60"/>
+      <c r="F8" s="55"/>
       <c r="G8" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B8,'Base Runes'!$A:$A,0)),"")</f>
         <v>Glow</v>
       </c>
-      <c r="H8" s="60"/>
+      <c r="H8" s="55"/>
       <c r="I8" s="10"/>
       <c r="J8" s="10"/>
     </row>
@@ -12737,12 +13226,12 @@
       <c r="E9" s="10" t="s">
         <v>1258</v>
       </c>
-      <c r="F9" s="60"/>
+      <c r="F9" s="55"/>
       <c r="G9" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B9,'Base Runes'!$A:$A,0)),"")</f>
         <v>Flash</v>
       </c>
-      <c r="H9" s="60"/>
+      <c r="H9" s="55"/>
       <c r="I9" s="10"/>
       <c r="J9" s="10"/>
     </row>
@@ -12764,12 +13253,12 @@
       <c r="E10" s="10" t="s">
         <v>1259</v>
       </c>
-      <c r="F10" s="60"/>
+      <c r="F10" s="55"/>
       <c r="G10" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B10,'Base Runes'!$A:$A,0)),"")</f>
         <v>Absorb</v>
       </c>
-      <c r="H10" s="60"/>
+      <c r="H10" s="55"/>
       <c r="I10" s="10"/>
       <c r="J10" s="10"/>
     </row>
@@ -12791,12 +13280,12 @@
       <c r="E11" s="10" t="s">
         <v>1260</v>
       </c>
-      <c r="F11" s="60"/>
+      <c r="F11" s="55"/>
       <c r="G11" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B11,'Base Runes'!$A:$A,0)),"")</f>
         <v>Radiate</v>
       </c>
-      <c r="H11" s="60"/>
+      <c r="H11" s="55"/>
       <c r="I11" s="10"/>
       <c r="J11" s="10"/>
     </row>
@@ -12818,12 +13307,12 @@
       <c r="E12" s="10" t="s">
         <v>1261</v>
       </c>
-      <c r="F12" s="60"/>
+      <c r="F12" s="55"/>
       <c r="G12" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B12,'Base Runes'!$A:$A,0)),"")</f>
         <v>Clarity</v>
       </c>
-      <c r="H12" s="60"/>
+      <c r="H12" s="55"/>
       <c r="I12" s="10"/>
       <c r="J12" s="10"/>
     </row>
@@ -12845,12 +13334,12 @@
       <c r="E13" s="10" t="s">
         <v>1022</v>
       </c>
-      <c r="F13" s="60"/>
+      <c r="F13" s="55"/>
       <c r="G13" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B13,'Base Runes'!$A:$A,0)),"")</f>
         <v>Glare</v>
       </c>
-      <c r="H13" s="60"/>
+      <c r="H13" s="55"/>
       <c r="I13" s="10"/>
       <c r="J13" s="10"/>
     </row>
@@ -12872,12 +13361,12 @@
       <c r="E14" s="10" t="s">
         <v>1262</v>
       </c>
-      <c r="F14" s="60"/>
+      <c r="F14" s="55"/>
       <c r="G14" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B14,'Base Runes'!$A:$A,0)),"")</f>
         <v>Bend</v>
       </c>
-      <c r="H14" s="60"/>
+      <c r="H14" s="55"/>
       <c r="I14" s="10"/>
       <c r="J14" s="10"/>
     </row>
@@ -12899,12 +13388,12 @@
       <c r="E15" s="10" t="s">
         <v>1263</v>
       </c>
-      <c r="F15" s="60"/>
+      <c r="F15" s="55"/>
       <c r="G15" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B15,'Base Runes'!$A:$A,0)),"")</f>
         <v>Reflect</v>
       </c>
-      <c r="H15" s="60"/>
+      <c r="H15" s="55"/>
       <c r="I15" s="10"/>
       <c r="J15" s="10"/>
     </row>
@@ -15605,32 +16094,32 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="59" t="s">
+      <c r="A2" s="60" t="s">
         <v>1023</v>
       </c>
-      <c r="B2" s="58"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
-      <c r="I2" s="58"/>
-      <c r="J2" s="58"/>
+      <c r="B2" s="59"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
     </row>
     <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="57" t="s">
+      <c r="A3" s="58" t="s">
         <v>1024</v>
       </c>
-      <c r="B3" s="58"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="58"/>
+      <c r="B3" s="59"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
     </row>
     <row r="5" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
@@ -15682,12 +16171,12 @@
       <c r="E6" s="10" t="s">
         <v>1025</v>
       </c>
-      <c r="F6" s="60"/>
+      <c r="F6" s="55"/>
       <c r="G6" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B6,'Base Runes'!$A:$A,0)),"")</f>
         <v>Wake</v>
       </c>
-      <c r="H6" s="60"/>
+      <c r="H6" s="55"/>
       <c r="I6" s="10"/>
       <c r="J6" s="10"/>
     </row>
@@ -15709,12 +16198,12 @@
       <c r="E7" s="10" t="s">
         <v>1264</v>
       </c>
-      <c r="F7" s="60"/>
+      <c r="F7" s="55"/>
       <c r="G7" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B7,'Base Runes'!$A:$A,0)),"")</f>
         <v>Sleep</v>
       </c>
-      <c r="H7" s="60"/>
+      <c r="H7" s="55"/>
       <c r="I7" s="10"/>
       <c r="J7" s="10"/>
     </row>
@@ -15736,12 +16225,12 @@
       <c r="E8" s="10" t="s">
         <v>1026</v>
       </c>
-      <c r="F8" s="60"/>
+      <c r="F8" s="55"/>
       <c r="G8" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B8,'Base Runes'!$A:$A,0)),"")</f>
         <v>Dispel</v>
       </c>
-      <c r="H8" s="60"/>
+      <c r="H8" s="55"/>
       <c r="I8" s="10"/>
       <c r="J8" s="10"/>
     </row>
@@ -15763,12 +16252,12 @@
       <c r="E9" s="10" t="s">
         <v>1027</v>
       </c>
-      <c r="F9" s="60"/>
+      <c r="F9" s="55"/>
       <c r="G9" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B9,'Base Runes'!$A:$A,0)),"")</f>
         <v>Conjure</v>
       </c>
-      <c r="H9" s="60"/>
+      <c r="H9" s="55"/>
       <c r="I9" s="10"/>
       <c r="J9" s="10"/>
     </row>
@@ -15790,12 +16279,12 @@
       <c r="E10" s="10" t="s">
         <v>1028</v>
       </c>
-      <c r="F10" s="60"/>
+      <c r="F10" s="55"/>
       <c r="G10" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B10,'Base Runes'!$A:$A,0)),"")</f>
         <v>Soothe</v>
       </c>
-      <c r="H10" s="60"/>
+      <c r="H10" s="55"/>
       <c r="I10" s="10"/>
       <c r="J10" s="10"/>
     </row>
@@ -15817,12 +16306,12 @@
       <c r="E11" s="10" t="s">
         <v>1265</v>
       </c>
-      <c r="F11" s="60"/>
+      <c r="F11" s="55"/>
       <c r="G11" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B11,'Base Runes'!$A:$A,0)),"")</f>
         <v>Dread</v>
       </c>
-      <c r="H11" s="60"/>
+      <c r="H11" s="55"/>
       <c r="I11" s="10"/>
       <c r="J11" s="10"/>
     </row>
@@ -15844,12 +16333,12 @@
       <c r="E12" s="10" t="s">
         <v>1266</v>
       </c>
-      <c r="F12" s="60"/>
+      <c r="F12" s="55"/>
       <c r="G12" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B12,'Base Runes'!$A:$A,0)),"")</f>
         <v>Unmask</v>
       </c>
-      <c r="H12" s="60"/>
+      <c r="H12" s="55"/>
       <c r="I12" s="10"/>
       <c r="J12" s="10"/>
     </row>
@@ -15871,12 +16360,12 @@
       <c r="E13" s="10" t="s">
         <v>1267</v>
       </c>
-      <c r="F13" s="60"/>
+      <c r="F13" s="55"/>
       <c r="G13" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B13,'Base Runes'!$A:$A,0)),"")</f>
         <v>Mimic</v>
       </c>
-      <c r="H13" s="60"/>
+      <c r="H13" s="55"/>
       <c r="I13" s="10"/>
       <c r="J13" s="10"/>
     </row>
@@ -15898,12 +16387,12 @@
       <c r="E14" s="10" t="s">
         <v>1029</v>
       </c>
-      <c r="F14" s="60"/>
+      <c r="F14" s="55"/>
       <c r="G14" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B14,'Base Runes'!$A:$A,0)),"")</f>
         <v>Shut</v>
       </c>
-      <c r="H14" s="60"/>
+      <c r="H14" s="55"/>
       <c r="I14" s="10"/>
       <c r="J14" s="10"/>
     </row>
@@ -15925,12 +16414,12 @@
       <c r="E15" s="10" t="s">
         <v>1030</v>
       </c>
-      <c r="F15" s="60"/>
+      <c r="F15" s="55"/>
       <c r="G15" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B15,'Base Runes'!$A:$A,0)),"")</f>
         <v>Whisper</v>
       </c>
-      <c r="H15" s="60"/>
+      <c r="H15" s="55"/>
       <c r="I15" s="10"/>
       <c r="J15" s="10"/>
     </row>
@@ -15972,32 +16461,32 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="59" t="s">
+      <c r="A2" s="60" t="s">
         <v>1031</v>
       </c>
-      <c r="B2" s="58"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
-      <c r="I2" s="58"/>
-      <c r="J2" s="58"/>
+      <c r="B2" s="59"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
     </row>
     <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="57" t="s">
+      <c r="A3" s="58" t="s">
         <v>1020</v>
       </c>
-      <c r="B3" s="58"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="58"/>
+      <c r="B3" s="59"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
     </row>
     <row r="5" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
@@ -16049,12 +16538,12 @@
       <c r="E6" s="10" t="s">
         <v>1032</v>
       </c>
-      <c r="F6" s="60"/>
+      <c r="F6" s="55"/>
       <c r="G6" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B6,'Base Runes'!$A:$A,0)),"")</f>
         <v>Purge</v>
       </c>
-      <c r="H6" s="60"/>
+      <c r="H6" s="55"/>
       <c r="I6" s="10"/>
       <c r="J6" s="10"/>
     </row>
@@ -16076,12 +16565,12 @@
       <c r="E7" s="10" t="s">
         <v>1033</v>
       </c>
-      <c r="F7" s="60"/>
+      <c r="F7" s="55"/>
       <c r="G7" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B7,'Base Runes'!$A:$A,0)),"")</f>
         <v>Poison</v>
       </c>
-      <c r="H7" s="60"/>
+      <c r="H7" s="55"/>
       <c r="I7" s="10"/>
       <c r="J7" s="10"/>
     </row>
@@ -16103,12 +16592,12 @@
       <c r="E8" s="10" t="s">
         <v>1268</v>
       </c>
-      <c r="F8" s="60"/>
+      <c r="F8" s="55"/>
       <c r="G8" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B8,'Base Runes'!$A:$A,0)),"")</f>
         <v>Cleanse</v>
       </c>
-      <c r="H8" s="60"/>
+      <c r="H8" s="55"/>
       <c r="I8" s="10"/>
       <c r="J8" s="10"/>
     </row>
@@ -16130,12 +16619,12 @@
       <c r="E9" s="10" t="s">
         <v>1269</v>
       </c>
-      <c r="F9" s="60"/>
+      <c r="F9" s="55"/>
       <c r="G9" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B9,'Base Runes'!$A:$A,0)),"")</f>
         <v>Contaminate</v>
       </c>
-      <c r="H9" s="60"/>
+      <c r="H9" s="55"/>
       <c r="I9" s="10"/>
       <c r="J9" s="10"/>
     </row>
@@ -16157,12 +16646,12 @@
       <c r="E10" s="10" t="s">
         <v>1270</v>
       </c>
-      <c r="F10" s="60"/>
+      <c r="F10" s="55"/>
       <c r="G10" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B10,'Base Runes'!$A:$A,0)),"")</f>
         <v>Neutralise</v>
       </c>
-      <c r="H10" s="60"/>
+      <c r="H10" s="55"/>
       <c r="I10" s="10"/>
       <c r="J10" s="10"/>
     </row>
@@ -16184,12 +16673,12 @@
       <c r="E11" s="10" t="s">
         <v>1271</v>
       </c>
-      <c r="F11" s="60"/>
+      <c r="F11" s="55"/>
       <c r="G11" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B11,'Base Runes'!$A:$A,0)),"")</f>
         <v>Corrode</v>
       </c>
-      <c r="H11" s="60"/>
+      <c r="H11" s="55"/>
       <c r="I11" s="10"/>
       <c r="J11" s="10"/>
     </row>
@@ -16211,12 +16700,12 @@
       <c r="E12" s="10" t="s">
         <v>1036</v>
       </c>
-      <c r="F12" s="60"/>
+      <c r="F12" s="55"/>
       <c r="G12" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B12,'Base Runes'!$A:$A,0)),"")</f>
         <v>Flush</v>
       </c>
-      <c r="H12" s="60"/>
+      <c r="H12" s="55"/>
       <c r="I12" s="10"/>
       <c r="J12" s="10"/>
     </row>
@@ -16238,12 +16727,12 @@
       <c r="E13" s="10" t="s">
         <v>1037</v>
       </c>
-      <c r="F13" s="60"/>
+      <c r="F13" s="55"/>
       <c r="G13" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B13,'Base Runes'!$A:$A,0)),"")</f>
         <v>Linger</v>
       </c>
-      <c r="H13" s="60"/>
+      <c r="H13" s="55"/>
       <c r="I13" s="10"/>
       <c r="J13" s="10"/>
     </row>
@@ -16265,12 +16754,12 @@
       <c r="E14" s="10" t="s">
         <v>1034</v>
       </c>
-      <c r="F14" s="60"/>
+      <c r="F14" s="55"/>
       <c r="G14" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B14,'Base Runes'!$A:$A,0)),"")</f>
         <v>Stimulate</v>
       </c>
-      <c r="H14" s="60"/>
+      <c r="H14" s="55"/>
       <c r="I14" s="10"/>
       <c r="J14" s="10"/>
     </row>
@@ -16292,12 +16781,12 @@
       <c r="E15" s="10" t="s">
         <v>1035</v>
       </c>
-      <c r="F15" s="60"/>
+      <c r="F15" s="55"/>
       <c r="G15" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B15,'Base Runes'!$A:$A,0)),"")</f>
         <v>Sap</v>
       </c>
-      <c r="H15" s="60"/>
+      <c r="H15" s="55"/>
       <c r="I15" s="10"/>
       <c r="J15" s="10"/>
     </row>
@@ -16339,32 +16828,32 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="59" t="s">
+      <c r="A2" s="60" t="s">
         <v>1038</v>
       </c>
-      <c r="B2" s="58"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
-      <c r="I2" s="58"/>
-      <c r="J2" s="58"/>
+      <c r="B2" s="59"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
     </row>
     <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="57" t="s">
+      <c r="A3" s="58" t="s">
         <v>1039</v>
       </c>
-      <c r="B3" s="58"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="58"/>
+      <c r="B3" s="59"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
     </row>
     <row r="5" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
@@ -16416,12 +16905,12 @@
       <c r="E6" s="10" t="s">
         <v>1272</v>
       </c>
-      <c r="F6" s="60"/>
+      <c r="F6" s="55"/>
       <c r="G6" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B6,'Base Runes'!$A:$A,0)),"")</f>
         <v>Disinfect</v>
       </c>
-      <c r="H6" s="60"/>
+      <c r="H6" s="55"/>
       <c r="I6" s="10"/>
       <c r="J6" s="10"/>
     </row>
@@ -16443,12 +16932,12 @@
       <c r="E7" s="10" t="s">
         <v>1273</v>
       </c>
-      <c r="F7" s="60"/>
+      <c r="F7" s="55"/>
       <c r="G7" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B7,'Base Runes'!$A:$A,0)),"")</f>
         <v>Infect</v>
       </c>
-      <c r="H7" s="60"/>
+      <c r="H7" s="55"/>
       <c r="I7" s="10"/>
       <c r="J7" s="10"/>
     </row>
@@ -16470,12 +16959,12 @@
       <c r="E8" s="10" t="s">
         <v>1043</v>
       </c>
-      <c r="F8" s="60"/>
+      <c r="F8" s="55"/>
       <c r="G8" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B8,'Base Runes'!$A:$A,0)),"")</f>
         <v>Contain</v>
       </c>
-      <c r="H8" s="60"/>
+      <c r="H8" s="55"/>
       <c r="I8" s="10"/>
       <c r="J8" s="10"/>
     </row>
@@ -16497,12 +16986,12 @@
       <c r="E9" s="10" t="s">
         <v>1274</v>
       </c>
-      <c r="F9" s="60"/>
+      <c r="F9" s="55"/>
       <c r="G9" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B9,'Base Runes'!$A:$A,0)),"")</f>
         <v>Spread</v>
       </c>
-      <c r="H9" s="60"/>
+      <c r="H9" s="55"/>
       <c r="I9" s="10"/>
       <c r="J9" s="10"/>
     </row>
@@ -16524,12 +17013,12 @@
       <c r="E10" s="10" t="s">
         <v>1042</v>
       </c>
-      <c r="F10" s="60"/>
+      <c r="F10" s="55"/>
       <c r="G10" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B10,'Base Runes'!$A:$A,0)),"")</f>
         <v>Lance</v>
       </c>
-      <c r="H10" s="60"/>
+      <c r="H10" s="55"/>
       <c r="I10" s="10"/>
       <c r="J10" s="10"/>
     </row>
@@ -16551,12 +17040,12 @@
       <c r="E11" s="10" t="s">
         <v>1275</v>
       </c>
-      <c r="F11" s="60"/>
+      <c r="F11" s="55"/>
       <c r="G11" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B11,'Base Runes'!$A:$A,0)),"")</f>
         <v>Fester</v>
       </c>
-      <c r="H11" s="60"/>
+      <c r="H11" s="55"/>
       <c r="I11" s="10"/>
       <c r="J11" s="10"/>
     </row>
@@ -16578,12 +17067,12 @@
       <c r="E12" s="10" t="s">
         <v>1040</v>
       </c>
-      <c r="F12" s="60"/>
+      <c r="F12" s="55"/>
       <c r="G12" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B12,'Base Runes'!$A:$A,0)),"")</f>
         <v>Clear</v>
       </c>
-      <c r="H12" s="60"/>
+      <c r="H12" s="55"/>
       <c r="I12" s="10"/>
       <c r="J12" s="10"/>
     </row>
@@ -16605,12 +17094,12 @@
       <c r="E13" s="10" t="s">
         <v>1041</v>
       </c>
-      <c r="F13" s="60"/>
+      <c r="F13" s="55"/>
       <c r="G13" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B13,'Base Runes'!$A:$A,0)),"")</f>
         <v>Billow</v>
       </c>
-      <c r="H13" s="60"/>
+      <c r="H13" s="55"/>
       <c r="I13" s="10"/>
       <c r="J13" s="10"/>
     </row>
@@ -16632,12 +17121,12 @@
       <c r="E14" s="10" t="s">
         <v>1276</v>
       </c>
-      <c r="F14" s="60"/>
+      <c r="F14" s="55"/>
       <c r="G14" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B14,'Base Runes'!$A:$A,0)),"")</f>
         <v>Immunise</v>
       </c>
-      <c r="H14" s="60"/>
+      <c r="H14" s="55"/>
       <c r="I14" s="10"/>
       <c r="J14" s="10"/>
     </row>
@@ -16659,12 +17148,12 @@
       <c r="E15" s="10" t="s">
         <v>1277</v>
       </c>
-      <c r="F15" s="60"/>
+      <c r="F15" s="55"/>
       <c r="G15" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B15,'Base Runes'!$A:$A,0)),"")</f>
         <v>Overrun</v>
       </c>
-      <c r="H15" s="60"/>
+      <c r="H15" s="55"/>
       <c r="I15" s="10"/>
       <c r="J15" s="10"/>
     </row>
@@ -18647,7 +19136,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:N167"/>
+  <dimension ref="A1:O167"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -18663,9 +19152,10 @@
     <col min="12" max="12" width="15.7109375" customWidth="1"/>
     <col min="13" max="13" width="9.7109375" customWidth="1"/>
     <col min="14" max="14" width="13.7109375" customWidth="1"/>
+    <col min="15" max="15" width="34.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
         <v>81</v>
       </c>
@@ -18708,8 +19198,11 @@
       <c r="N1" s="35" t="s">
         <v>1101</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O1" s="35" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
         <v>90</v>
       </c>
@@ -18757,8 +19250,11 @@
         <f>IFERROR(ROUND('Bond Rules'!$B$9+L2*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K2,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
         <v>2.08</v>
       </c>
-    </row>
-    <row r="3" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O2" s="61" t="s">
+        <v>1281</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
         <v>93</v>
       </c>
@@ -18806,8 +19302,11 @@
         <f>IFERROR(ROUND('Bond Rules'!$B$9+L3*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K3,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
         <v>3.1</v>
       </c>
-    </row>
-    <row r="4" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O3" s="61" t="s">
+        <v>1282</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="16" t="s">
         <v>98</v>
       </c>
@@ -18855,8 +19354,11 @@
         <f>IFERROR(ROUND('Bond Rules'!$B$9+L4*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K4,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
         <v>1.9</v>
       </c>
-    </row>
-    <row r="5" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O4" s="61" t="s">
+        <v>1283</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
         <v>100</v>
       </c>
@@ -18904,8 +19406,11 @@
         <f>IFERROR(ROUND('Bond Rules'!$B$9+L5*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K5,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
         <v>3.1</v>
       </c>
-    </row>
-    <row r="6" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O5" s="61" t="s">
+        <v>1284</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
         <v>104</v>
       </c>
@@ -18953,8 +19458,11 @@
         <f>IFERROR(ROUND('Bond Rules'!$B$9+L6*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K6,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
         <v>2</v>
       </c>
-    </row>
-    <row r="7" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O6" s="61" t="s">
+        <v>1285</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
         <v>107</v>
       </c>
@@ -19002,8 +19510,11 @@
         <f>IFERROR(ROUND('Bond Rules'!$B$9+L7*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K7,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
         <v>3.7</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O7" s="61" t="s">
+        <v>1286</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="16" t="s">
         <v>111</v>
       </c>
@@ -19051,8 +19562,11 @@
         <f>IFERROR(ROUND('Bond Rules'!$B$9+L8*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K8,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
         <v>2</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O8" s="61" t="s">
+        <v>1287</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
         <v>113</v>
       </c>
@@ -19100,8 +19614,11 @@
         <f>IFERROR(ROUND('Bond Rules'!$B$9+L9*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K9,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
         <v>3.85</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O9" s="61" t="s">
+        <v>1288</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
         <v>117</v>
       </c>
@@ -19149,8 +19666,11 @@
         <f>IFERROR(ROUND('Bond Rules'!$B$9+L10*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K10,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
         <v>1.7</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O10" s="61" t="s">
+        <v>1289</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
         <v>119</v>
       </c>
@@ -19198,8 +19718,11 @@
         <f>IFERROR(ROUND('Bond Rules'!$B$9+L11*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K11,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
         <v>2.8</v>
       </c>
-    </row>
-    <row r="12" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O11" s="61" t="s">
+        <v>1290</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="16" t="s">
         <v>124</v>
       </c>
@@ -19247,8 +19770,11 @@
         <f>IFERROR(ROUND('Bond Rules'!$B$9+L12*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K12,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
         <v>2.1</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O12" s="61" t="s">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="16" t="s">
         <v>126</v>
       </c>
@@ -19296,8 +19822,11 @@
         <f>IFERROR(ROUND('Bond Rules'!$B$9+L13*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K13,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
         <v>2.66</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O13" s="61" t="s">
+        <v>1292</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
         <v>130</v>
       </c>
@@ -19345,8 +19874,11 @@
         <f>IFERROR(ROUND('Bond Rules'!$B$9+L14*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K14,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
         <v>2.0099999999999998</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O14" s="61" t="s">
+        <v>1293</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="16" t="s">
         <v>132</v>
       </c>
@@ -19394,8 +19926,11 @@
         <f>IFERROR(ROUND('Bond Rules'!$B$9+L15*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K15,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
         <v>2.9</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O15" s="61" t="s">
+        <v>1294</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="16" t="s">
         <v>136</v>
       </c>
@@ -19443,8 +19978,11 @@
         <f>IFERROR(ROUND('Bond Rules'!$B$9+L16*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K16,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
         <v>2.15</v>
       </c>
-    </row>
-    <row r="17" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O16" s="61" t="s">
+        <v>1295</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="16" t="s">
         <v>139</v>
       </c>
@@ -19492,8 +20030,11 @@
         <f>IFERROR(ROUND('Bond Rules'!$B$9+L17*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K17,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
         <v>3.25</v>
       </c>
-    </row>
-    <row r="18" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O17" s="61" t="s">
+        <v>1296</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="16" t="s">
         <v>144</v>
       </c>
@@ -19541,8 +20082,11 @@
         <f>IFERROR(ROUND('Bond Rules'!$B$9+L18*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K18,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
         <v>2</v>
       </c>
-    </row>
-    <row r="19" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O18" s="61" t="s">
+        <v>1297</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="16" t="s">
         <v>147</v>
       </c>
@@ -19590,8 +20134,11 @@
         <f>IFERROR(ROUND('Bond Rules'!$B$9+L19*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K19,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
         <v>3.55</v>
       </c>
-    </row>
-    <row r="20" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O19" s="61" t="s">
+        <v>1298</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="16" t="s">
         <v>152</v>
       </c>
@@ -19639,8 +20186,11 @@
         <f>IFERROR(ROUND('Bond Rules'!$B$9+L20*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K20,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
         <v>2.1</v>
       </c>
-    </row>
-    <row r="21" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O20" s="61" t="s">
+        <v>1299</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="s">
         <v>155</v>
       </c>
@@ -19688,8 +20238,11 @@
         <f>IFERROR(ROUND('Bond Rules'!$B$9+L21*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K21,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
         <v>3.4</v>
       </c>
-    </row>
-    <row r="22" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O21" s="61" t="s">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="16" t="s">
         <v>160</v>
       </c>
@@ -19737,8 +20290,11 @@
         <f>IFERROR(ROUND('Bond Rules'!$B$9+L22*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K22,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
         <v>1.8</v>
       </c>
-    </row>
-    <row r="23" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O22" s="61" t="s">
+        <v>1301</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="16" t="s">
         <v>162</v>
       </c>
@@ -19786,8 +20342,11 @@
         <f>IFERROR(ROUND('Bond Rules'!$B$9+L23*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K23,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O23" s="61" t="s">
+        <v>1284</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="16" t="s">
         <v>167</v>
       </c>
@@ -19835,8 +20394,11 @@
         <f>IFERROR(ROUND('Bond Rules'!$B$9+L24*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K24,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
         <v>1.94</v>
       </c>
-    </row>
-    <row r="25" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O24" s="61" t="s">
+        <v>1302</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="16" t="s">
         <v>169</v>
       </c>
@@ -19884,8 +20446,11 @@
         <f>IFERROR(ROUND('Bond Rules'!$B$9+L25*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K25,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
         <v>2.66</v>
       </c>
-    </row>
-    <row r="26" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O25" s="61" t="s">
+        <v>1303</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="16" t="s">
         <v>174</v>
       </c>
@@ -19933,8 +20498,11 @@
         <f>IFERROR(ROUND('Bond Rules'!$B$9+L26*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K26,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
         <v>2.08</v>
       </c>
-    </row>
-    <row r="27" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O26" s="61" t="s">
+        <v>1304</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="16" t="s">
         <v>177</v>
       </c>
@@ -19982,8 +20550,11 @@
         <f>IFERROR(ROUND('Bond Rules'!$B$9+L27*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K27,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
         <v>3.7</v>
       </c>
-    </row>
-    <row r="28" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O27" s="61" t="s">
+        <v>1305</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="16" t="s">
         <v>181</v>
       </c>
@@ -20031,8 +20602,11 @@
         <f>IFERROR(ROUND('Bond Rules'!$B$9+L28*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K28,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
         <v>2.42</v>
       </c>
-    </row>
-    <row r="29" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O28" s="61" t="s">
+        <v>1306</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="16" t="s">
         <v>184</v>
       </c>
@@ -20080,8 +20654,11 @@
         <f>IFERROR(ROUND('Bond Rules'!$B$9+L29*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K29,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O29" s="61" t="s">
+        <v>1292</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
         <v>189</v>
       </c>
@@ -20129,8 +20706,11 @@
         <f>IFERROR(ROUND('Bond Rules'!$B$9+L30*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K30,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
         <v>2.66</v>
       </c>
-    </row>
-    <row r="31" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O30" s="61" t="s">
+        <v>1307</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="16" t="s">
         <v>192</v>
       </c>
@@ -20178,8 +20758,11 @@
         <f>IFERROR(ROUND('Bond Rules'!$B$9+L31*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K31,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
         <v>2.08</v>
       </c>
-    </row>
-    <row r="32" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O31" s="61" t="s">
+        <v>1308</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="16" t="s">
         <v>197</v>
       </c>
@@ -20227,8 +20810,11 @@
         <f>IFERROR(ROUND('Bond Rules'!$B$9+L32*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K32,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
         <v>2.74</v>
       </c>
-    </row>
-    <row r="33" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O32" s="61" t="s">
+        <v>1309</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="16" t="s">
         <v>200</v>
       </c>
@@ -20276,8 +20862,11 @@
         <f>IFERROR(ROUND('Bond Rules'!$B$9+L33*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K33,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
         <v>2.0099999999999998</v>
       </c>
-    </row>
-    <row r="34" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O33" s="61" t="s">
+        <v>1295</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="16" t="s">
         <v>205</v>
       </c>
@@ -20325,8 +20914,11 @@
         <f>IFERROR(ROUND('Bond Rules'!$B$9+L34*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K34,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
         <v>2.1</v>
       </c>
-    </row>
-    <row r="35" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O34" s="61" t="s">
+        <v>1310</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="16" t="s">
         <v>207</v>
       </c>
@@ -20374,8 +20966,11 @@
         <f>IFERROR(ROUND('Bond Rules'!$B$9+L35*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K35,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
         <v>3.55</v>
       </c>
-    </row>
-    <row r="36" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O35" s="61" t="s">
+        <v>1311</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="16" t="s">
         <v>211</v>
       </c>
@@ -20423,8 +21018,11 @@
         <f>IFERROR(ROUND('Bond Rules'!$B$9+L36*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K36,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
         <v>2.2000000000000002</v>
       </c>
-    </row>
-    <row r="37" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O36" s="61" t="s">
+        <v>1294</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="16" t="s">
         <v>213</v>
       </c>
@@ -20472,8 +21070,11 @@
         <f>IFERROR(ROUND('Bond Rules'!$B$9+L37*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K37,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
         <v>3.4</v>
       </c>
-    </row>
-    <row r="38" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O37" s="61" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="16" t="s">
         <v>217</v>
       </c>
@@ -20521,8 +21122,11 @@
         <f>IFERROR(ROUND('Bond Rules'!$B$9+L38*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K38,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
         <v>1.9</v>
       </c>
-    </row>
-    <row r="39" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O38" s="61" t="s">
+        <v>1313</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="16" t="s">
         <v>219</v>
       </c>
@@ -20570,8 +21174,11 @@
         <f>IFERROR(ROUND('Bond Rules'!$B$9+L39*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K39,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
         <v>3.25</v>
       </c>
-    </row>
-    <row r="40" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O39" s="61" t="s">
+        <v>1314</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="16" t="s">
         <v>224</v>
       </c>
@@ -20619,8 +21226,11 @@
         <f>IFERROR(ROUND('Bond Rules'!$B$9+L40*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K40,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
         <v>2.8</v>
       </c>
-    </row>
-    <row r="41" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O40" s="61" t="s">
+        <v>1315</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="16" t="s">
         <v>227</v>
       </c>
@@ -20668,8 +21278,11 @@
         <f>IFERROR(ROUND('Bond Rules'!$B$9+L41*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K41,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
         <v>2.42</v>
       </c>
-    </row>
-    <row r="42" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O41" s="61" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="16" t="s">
         <v>232</v>
       </c>
@@ -20717,8 +21330,11 @@
         <f>IFERROR(ROUND('Bond Rules'!$B$9+L42*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K42,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
         <v>2.1</v>
       </c>
-    </row>
-    <row r="43" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O42" s="61" t="s">
+        <v>1287</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="16" t="s">
         <v>234</v>
       </c>
@@ -20766,8 +21382,11 @@
         <f>IFERROR(ROUND('Bond Rules'!$B$9+L43*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K43,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O43" s="61" t="s">
+        <v>1317</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="16" t="s">
         <v>239</v>
       </c>
@@ -20815,8 +21434,11 @@
         <f>IFERROR(ROUND('Bond Rules'!$B$9+L44*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K44,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
         <v>2</v>
       </c>
-    </row>
-    <row r="45" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O44" s="61" t="s">
+        <v>1318</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="16" t="s">
         <v>242</v>
       </c>
@@ -20864,8 +21486,11 @@
         <f>IFERROR(ROUND('Bond Rules'!$B$9+L45*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K45,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
         <v>3.1</v>
       </c>
-    </row>
-    <row r="46" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O45" s="61" t="s">
+        <v>1319</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="16" t="s">
         <v>246</v>
       </c>
@@ -20913,8 +21538,11 @@
         <f>IFERROR(ROUND('Bond Rules'!$B$9+L46*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K46,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
         <v>2.66</v>
       </c>
-    </row>
-    <row r="47" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O46" s="61" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="16" t="s">
         <v>249</v>
       </c>
@@ -20962,8 +21590,11 @@
         <f>IFERROR(ROUND('Bond Rules'!$B$9+L47*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K47,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
         <v>1.87</v>
       </c>
-    </row>
-    <row r="48" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O47" s="61" t="s">
+        <v>1321</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="16" t="s">
         <v>254</v>
       </c>
@@ -21011,8 +21642,11 @@
         <f>IFERROR(ROUND('Bond Rules'!$B$9+L48*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K48,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
         <v>1.9</v>
       </c>
-    </row>
-    <row r="49" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O48" s="61" t="s">
+        <v>1322</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="16" t="s">
         <v>257</v>
       </c>
@@ -21060,8 +21694,11 @@
         <f>IFERROR(ROUND('Bond Rules'!$B$9+L49*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K49,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
         <v>2.66</v>
       </c>
-    </row>
-    <row r="50" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O49" s="61" t="s">
+        <v>1296</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="16" t="s">
         <v>262</v>
       </c>
@@ -21109,8 +21746,11 @@
         <f>IFERROR(ROUND('Bond Rules'!$B$9+L50*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K50,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
         <v>2.74</v>
       </c>
-    </row>
-    <row r="51" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O50" s="61" t="s">
+        <v>1323</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="16" t="s">
         <v>265</v>
       </c>
@@ -21158,8 +21798,11 @@
         <f>IFERROR(ROUND('Bond Rules'!$B$9+L51*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K51,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="52" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O51" s="61" t="s">
+        <v>1324</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="16" t="s">
         <v>270</v>
       </c>
@@ -21207,8 +21850,11 @@
         <f>IFERROR(ROUND('Bond Rules'!$B$9+L52*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K52,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
         <v>2.15</v>
       </c>
-    </row>
-    <row r="53" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O52" s="61" t="s">
+        <v>1325</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="16" t="s">
         <v>272</v>
       </c>
@@ -21256,8 +21902,11 @@
         <f>IFERROR(ROUND('Bond Rules'!$B$9+L53*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K53,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
         <v>2.95</v>
       </c>
-    </row>
-    <row r="54" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O53" s="61" t="s">
+        <v>1326</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="16" t="s">
         <v>276</v>
       </c>
@@ -21305,8 +21954,11 @@
         <f>IFERROR(ROUND('Bond Rules'!$B$9+L54*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K54,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
         <v>2.1</v>
       </c>
-    </row>
-    <row r="55" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O54" s="61" t="s">
+        <v>1327</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="16" t="s">
         <v>279</v>
       </c>
@@ -21354,8 +22006,11 @@
         <f>IFERROR(ROUND('Bond Rules'!$B$9+L55*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K55,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
         <v>3.55</v>
       </c>
-    </row>
-    <row r="56" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O55" s="61" t="s">
+        <v>1328</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="16" t="s">
         <v>283</v>
       </c>
@@ -21403,8 +22058,11 @@
         <f>IFERROR(ROUND('Bond Rules'!$B$9+L56*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K56,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
         <v>2.0099999999999998</v>
       </c>
-    </row>
-    <row r="57" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O56" s="61" t="s">
+        <v>1329</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="16" t="s">
         <v>285</v>
       </c>
@@ -21452,8 +22110,11 @@
         <f>IFERROR(ROUND('Bond Rules'!$B$9+L57*INDEX('Bond Rules'!$C$4:$C$7,MATCH(K57,'Bond Rules'!$A$4:$A$7,0)),2),"")</f>
         <v>3.25</v>
       </c>
-    </row>
-    <row r="58" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O57" s="61" t="s">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="16" t="s">
         <v>289</v>
       </c>
@@ -21502,7 +22163,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="59" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="16" t="s">
         <v>292</v>
       </c>
@@ -21551,7 +22212,7 @@
         <v>1.9</v>
       </c>
     </row>
-    <row r="60" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="16" t="s">
         <v>297</v>
       </c>
@@ -21600,7 +22261,7 @@
         <v>2.9</v>
       </c>
     </row>
-    <row r="61" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="16" t="s">
         <v>300</v>
       </c>
@@ -21649,7 +22310,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="62" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="16" t="s">
         <v>305</v>
       </c>
@@ -21698,7 +22359,7 @@
         <v>2.15</v>
       </c>
     </row>
-    <row r="63" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="16" t="s">
         <v>308</v>
       </c>
@@ -21747,7 +22408,7 @@
         <v>2.9</v>
       </c>
     </row>
-    <row r="64" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="16" t="s">
         <v>312</v>
       </c>
@@ -26844,7 +27505,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N167" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
   <conditionalFormatting sqref="N2:N167">
     <cfRule type="colorScale" priority="1">
       <colorScale>
@@ -26873,7 +27533,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:G57"/>
+  <dimension ref="A1:H57"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -26882,9 +27542,10 @@
     <col min="5" max="5" width="14" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
     <col min="7" max="7" width="60" customWidth="1"/>
+    <col min="8" max="8" width="34.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
         <v>81</v>
       </c>
@@ -26906,8 +27567,11 @@
       <c r="G1" s="8" t="s">
         <v>681</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H1" s="35" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
         <v>682</v>
       </c>
@@ -26931,8 +27595,11 @@
       <c r="G2" s="24" t="s">
         <v>686</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H2" s="61" t="s">
+        <v>1330</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
         <v>685</v>
       </c>
@@ -26956,8 +27623,11 @@
       <c r="G3" s="24" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H3" s="61" t="s">
+        <v>1331</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="16" t="s">
         <v>690</v>
       </c>
@@ -26981,8 +27651,11 @@
       <c r="G4" s="24" t="s">
         <v>694</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H4" s="61" t="s">
+        <v>1332</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
         <v>693</v>
       </c>
@@ -27006,8 +27679,11 @@
       <c r="G5" s="24" t="s">
         <v>697</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H5" s="61" t="s">
+        <v>1333</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
         <v>698</v>
       </c>
@@ -27031,8 +27707,11 @@
       <c r="G6" s="24" t="s">
         <v>702</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H6" s="61" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
         <v>701</v>
       </c>
@@ -27056,8 +27735,11 @@
       <c r="G7" s="24" t="s">
         <v>705</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H7" s="61" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="16" t="s">
         <v>706</v>
       </c>
@@ -27081,8 +27763,11 @@
       <c r="G8" s="24" t="s">
         <v>710</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H8" s="61" t="s">
+        <v>1287</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
         <v>709</v>
       </c>
@@ -27106,8 +27791,11 @@
       <c r="G9" s="24" t="s">
         <v>713</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H9" s="61" t="s">
+        <v>1306</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
         <v>714</v>
       </c>
@@ -27131,8 +27819,11 @@
       <c r="G10" s="24" t="s">
         <v>718</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H10" s="61" t="s">
+        <v>1321</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
         <v>717</v>
       </c>
@@ -27156,8 +27847,11 @@
       <c r="G11" s="24" t="s">
         <v>721</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H11" s="61" t="s">
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="16" t="s">
         <v>722</v>
       </c>
@@ -27181,8 +27875,11 @@
       <c r="G12" s="24" t="s">
         <v>726</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H12" s="61" t="s">
+        <v>1337</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="16" t="s">
         <v>725</v>
       </c>
@@ -27206,8 +27903,11 @@
       <c r="G13" s="24" t="s">
         <v>729</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H13" s="61" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
         <v>730</v>
       </c>
@@ -27231,8 +27931,11 @@
       <c r="G14" s="24" t="s">
         <v>734</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H14" s="61" t="s">
+        <v>1339</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="16" t="s">
         <v>733</v>
       </c>
@@ -27256,8 +27959,11 @@
       <c r="G15" s="24" t="s">
         <v>737</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H15" s="61" t="s">
+        <v>1340</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="16" t="s">
         <v>738</v>
       </c>
@@ -27281,8 +27987,11 @@
       <c r="G16" s="24" t="s">
         <v>742</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H16" s="61" t="s">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="16" t="s">
         <v>741</v>
       </c>
@@ -27306,8 +28015,11 @@
       <c r="G17" s="24" t="s">
         <v>745</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H17" s="61" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="16" t="s">
         <v>746</v>
       </c>
@@ -27331,8 +28043,11 @@
       <c r="G18" s="24" t="s">
         <v>750</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H18" s="61" t="s">
+        <v>1294</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="16" t="s">
         <v>749</v>
       </c>
@@ -27356,8 +28071,11 @@
       <c r="G19" s="24" t="s">
         <v>753</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H19" s="61" t="s">
+        <v>1343</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="16" t="s">
         <v>754</v>
       </c>
@@ -27381,8 +28099,11 @@
       <c r="G20" s="24" t="s">
         <v>758</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H20" s="61" t="s">
+        <v>1344</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="s">
         <v>757</v>
       </c>
@@ -27406,8 +28127,11 @@
       <c r="G21" s="24" t="s">
         <v>761</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H21" s="61" t="s">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="16" t="s">
         <v>762</v>
       </c>
@@ -27431,8 +28155,11 @@
       <c r="G22" s="24" t="s">
         <v>766</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H22" s="61" t="s">
+        <v>1345</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="16" t="s">
         <v>765</v>
       </c>
@@ -27456,8 +28183,11 @@
       <c r="G23" s="24" t="s">
         <v>769</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H23" s="61" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="16" t="s">
         <v>770</v>
       </c>
@@ -27481,8 +28211,11 @@
       <c r="G24" s="24" t="s">
         <v>774</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H24" s="61" t="s">
+        <v>1347</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="16" t="s">
         <v>773</v>
       </c>
@@ -27506,8 +28239,11 @@
       <c r="G25" s="24" t="s">
         <v>777</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H25" s="61" t="s">
+        <v>1348</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="16" t="s">
         <v>778</v>
       </c>
@@ -27531,8 +28267,11 @@
       <c r="G26" s="24" t="s">
         <v>782</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H26" s="61" t="s">
+        <v>1349</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="16" t="s">
         <v>781</v>
       </c>
@@ -27556,8 +28295,11 @@
       <c r="G27" s="24" t="s">
         <v>785</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H27" s="61" t="s">
+        <v>1350</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="16" t="s">
         <v>786</v>
       </c>
@@ -27581,8 +28323,11 @@
       <c r="G28" s="24" t="s">
         <v>790</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H28" s="61" t="s">
+        <v>1326</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="16" t="s">
         <v>789</v>
       </c>
@@ -27606,8 +28351,11 @@
       <c r="G29" s="24" t="s">
         <v>793</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H29" s="61" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
         <v>794</v>
       </c>
@@ -27631,8 +28379,11 @@
       <c r="G30" s="24" t="s">
         <v>798</v>
       </c>
-    </row>
-    <row r="31" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H30" s="61" t="s">
+        <v>1311</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="16" t="s">
         <v>797</v>
       </c>
@@ -27656,8 +28407,11 @@
       <c r="G31" s="24" t="s">
         <v>801</v>
       </c>
-    </row>
-    <row r="32" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H31" s="61" t="s">
+        <v>1306</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="16" t="s">
         <v>802</v>
       </c>
@@ -27681,8 +28435,11 @@
       <c r="G32" s="24" t="s">
         <v>806</v>
       </c>
-    </row>
-    <row r="33" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H32" s="61" t="s">
+        <v>1284</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="16" t="s">
         <v>805</v>
       </c>
@@ -27706,8 +28463,11 @@
       <c r="G33" s="24" t="s">
         <v>809</v>
       </c>
-    </row>
-    <row r="34" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H33" s="61" t="s">
+        <v>1283</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="16" t="s">
         <v>810</v>
       </c>
@@ -27731,8 +28491,11 @@
       <c r="G34" s="24" t="s">
         <v>814</v>
       </c>
-    </row>
-    <row r="35" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H34" s="61" t="s">
+        <v>1352</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="16" t="s">
         <v>813</v>
       </c>
@@ -27756,8 +28519,11 @@
       <c r="G35" s="24" t="s">
         <v>817</v>
       </c>
-    </row>
-    <row r="36" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H35" s="61" t="s">
+        <v>1353</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="16" t="s">
         <v>818</v>
       </c>
@@ -27781,8 +28547,11 @@
       <c r="G36" s="24" t="s">
         <v>822</v>
       </c>
-    </row>
-    <row r="37" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H36" s="61" t="s">
+        <v>1354</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="16" t="s">
         <v>821</v>
       </c>
@@ -27806,8 +28575,11 @@
       <c r="G37" s="24" t="s">
         <v>825</v>
       </c>
-    </row>
-    <row r="38" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H37" s="61" t="s">
+        <v>1355</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="16" t="s">
         <v>826</v>
       </c>
@@ -27831,8 +28603,11 @@
       <c r="G38" s="24" t="s">
         <v>830</v>
       </c>
-    </row>
-    <row r="39" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H38" s="61" t="s">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="16" t="s">
         <v>829</v>
       </c>
@@ -27856,8 +28631,11 @@
       <c r="G39" s="24" t="s">
         <v>833</v>
       </c>
-    </row>
-    <row r="40" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H39" s="61" t="s">
+        <v>1357</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="16" t="s">
         <v>834</v>
       </c>
@@ -27881,8 +28659,11 @@
       <c r="G40" s="24" t="s">
         <v>838</v>
       </c>
-    </row>
-    <row r="41" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H40" s="61" t="s">
+        <v>1314</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="16" t="s">
         <v>837</v>
       </c>
@@ -27906,8 +28687,11 @@
       <c r="G41" s="24" t="s">
         <v>841</v>
       </c>
-    </row>
-    <row r="42" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H41" s="61" t="s">
+        <v>1319</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="16" t="s">
         <v>842</v>
       </c>
@@ -27931,8 +28715,11 @@
       <c r="G42" s="24" t="s">
         <v>846</v>
       </c>
-    </row>
-    <row r="43" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H42" s="61" t="s">
+        <v>1358</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="16" t="s">
         <v>845</v>
       </c>
@@ -27956,8 +28743,11 @@
       <c r="G43" s="24" t="s">
         <v>849</v>
       </c>
-    </row>
-    <row r="44" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H43" s="61" t="s">
+        <v>1344</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="16" t="s">
         <v>850</v>
       </c>
@@ -27981,8 +28771,11 @@
       <c r="G44" s="24" t="s">
         <v>854</v>
       </c>
-    </row>
-    <row r="45" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H44" s="61" t="s">
+        <v>1314</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="16" t="s">
         <v>853</v>
       </c>
@@ -28006,8 +28799,11 @@
       <c r="G45" s="24" t="s">
         <v>857</v>
       </c>
-    </row>
-    <row r="46" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H45" s="61" t="s">
+        <v>1350</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="16" t="s">
         <v>858</v>
       </c>
@@ -28031,8 +28827,11 @@
       <c r="G46" s="24" t="s">
         <v>862</v>
       </c>
-    </row>
-    <row r="47" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H46" s="61" t="s">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="16" t="s">
         <v>861</v>
       </c>
@@ -28056,8 +28855,11 @@
       <c r="G47" s="24" t="s">
         <v>865</v>
       </c>
-    </row>
-    <row r="48" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H47" s="61" t="s">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="16" t="s">
         <v>866</v>
       </c>
@@ -28081,8 +28883,11 @@
       <c r="G48" s="24" t="s">
         <v>870</v>
       </c>
-    </row>
-    <row r="49" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H48" s="61" t="s">
+        <v>1354</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="16" t="s">
         <v>869</v>
       </c>
@@ -28106,8 +28911,11 @@
       <c r="G49" s="24" t="s">
         <v>873</v>
       </c>
-    </row>
-    <row r="50" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H49" s="61" t="s">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="16" t="s">
         <v>874</v>
       </c>
@@ -28131,8 +28939,11 @@
       <c r="G50" s="24" t="s">
         <v>878</v>
       </c>
-    </row>
-    <row r="51" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H50" s="61" t="s">
+        <v>1326</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="16" t="s">
         <v>877</v>
       </c>
@@ -28156,8 +28967,11 @@
       <c r="G51" s="24" t="s">
         <v>881</v>
       </c>
-    </row>
-    <row r="52" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H51" s="61" t="s">
+        <v>1360</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="16" t="s">
         <v>882</v>
       </c>
@@ -28181,8 +28995,11 @@
       <c r="G52" s="24" t="s">
         <v>885</v>
       </c>
-    </row>
-    <row r="53" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H52" s="61" t="s">
+        <v>1361</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="16" t="s">
         <v>884</v>
       </c>
@@ -28206,8 +29023,11 @@
       <c r="G53" s="24" t="s">
         <v>887</v>
       </c>
-    </row>
-    <row r="54" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H53" s="61" t="s">
+        <v>1362</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="16" t="s">
         <v>888</v>
       </c>
@@ -28231,8 +29051,11 @@
       <c r="G54" s="24" t="s">
         <v>892</v>
       </c>
-    </row>
-    <row r="55" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H54" s="61" t="s">
+        <v>1363</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="16" t="s">
         <v>891</v>
       </c>
@@ -28256,8 +29079,11 @@
       <c r="G55" s="24" t="s">
         <v>895</v>
       </c>
-    </row>
-    <row r="56" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H55" s="61" t="s">
+        <v>1362</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="16" t="s">
         <v>896</v>
       </c>
@@ -28281,8 +29107,11 @@
       <c r="G56" s="24" t="s">
         <v>900</v>
       </c>
-    </row>
-    <row r="57" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H56" s="61" t="s">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="16" t="s">
         <v>899</v>
       </c>
@@ -28305,6 +29134,9 @@
       </c>
       <c r="G57" s="24" t="s">
         <v>903</v>
+      </c>
+      <c r="H57" s="61" t="s">
+        <v>1350</v>
       </c>
     </row>
   </sheetData>
@@ -28315,7 +29147,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{707B76BF-2512-40E2-935C-38AB239C315D}">
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22.7109375" style="31" customWidth="1"/>
@@ -28425,13 +29257,13 @@
       </c>
     </row>
     <row r="10" spans="1:5" ht="54" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="55" t="s">
+      <c r="A10" s="56" t="s">
         <v>1089</v>
       </c>
-      <c r="B10" s="55"/>
-      <c r="C10" s="55"/>
-      <c r="D10" s="55"/>
-      <c r="E10" s="55"/>
+      <c r="B10" s="56"/>
+      <c r="C10" s="56"/>
+      <c r="D10" s="56"/>
+      <c r="E10" s="56"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="44" t="s">
@@ -28478,18 +29310,181 @@
       </c>
     </row>
     <row r="17" spans="1:5" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="56" t="s">
+      <c r="A17" s="57" t="s">
         <v>1099</v>
       </c>
-      <c r="B17" s="55"/>
-      <c r="C17" s="55"/>
-      <c r="D17" s="55"/>
-      <c r="E17" s="55"/>
+      <c r="B17" s="56"/>
+      <c r="C17" s="56"/>
+      <c r="D17" s="56"/>
+      <c r="E17" s="56"/>
+    </row>
+    <row r="19" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="63" t="s">
+        <v>1409</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="56" t="s">
+        <v>1410</v>
+      </c>
+      <c r="B20" s="56"/>
+      <c r="C20" s="56"/>
+      <c r="D20" s="56"/>
+      <c r="E20" s="56"/>
+    </row>
+    <row r="22" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A22" s="35" t="s">
+        <v>1411</v>
+      </c>
+      <c r="B22" s="35" t="s">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A23" s="31">
+        <v>1</v>
+      </c>
+      <c r="B23" s="61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A24" s="31">
+        <v>2</v>
+      </c>
+      <c r="B24" s="61">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A25" s="31">
+        <v>3</v>
+      </c>
+      <c r="B25" s="61">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A26" s="31" t="s">
+        <v>1413</v>
+      </c>
+      <c r="B26" s="61">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A28" s="35" t="s">
+        <v>1090</v>
+      </c>
+      <c r="B28" s="35" t="s">
+        <v>1414</v>
+      </c>
+      <c r="C28" s="35" t="s">
+        <v>1415</v>
+      </c>
+      <c r="D28" s="35" t="s">
+        <v>1416</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A29" s="31" t="s">
+        <v>1093</v>
+      </c>
+      <c r="B29" s="33">
+        <v>0.75</v>
+      </c>
+      <c r="C29" s="33">
+        <v>0.75</v>
+      </c>
+      <c r="D29" s="31" t="s">
+        <v>1417</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A30" s="31" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B30" s="33">
+        <v>1</v>
+      </c>
+      <c r="C30" s="33">
+        <v>0.5</v>
+      </c>
+      <c r="D30" s="31" t="s">
+        <v>1418</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A31" s="31" t="s">
+        <v>1097</v>
+      </c>
+      <c r="B31" s="33">
+        <v>1.5</v>
+      </c>
+      <c r="C31" s="33">
+        <v>0</v>
+      </c>
+      <c r="D31" s="31" t="s">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A33" s="31" t="s">
+        <v>1420</v>
+      </c>
+      <c r="B33" s="33">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A34" s="31" t="s">
+        <v>1421</v>
+      </c>
+      <c r="B34" s="33">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A35" s="31" t="s">
+        <v>1422</v>
+      </c>
+      <c r="B35" s="33">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A36" s="31" t="s">
+        <v>1423</v>
+      </c>
+      <c r="B36" s="33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="56" t="s">
+        <v>1424</v>
+      </c>
+      <c r="B38" s="56"/>
+      <c r="C38" s="56"/>
+      <c r="D38" s="56"/>
+      <c r="E38" s="56"/>
+    </row>
+    <row r="40" spans="1:5" ht="69.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="56" t="s">
+        <v>1425</v>
+      </c>
+      <c r="B40" s="56"/>
+      <c r="C40" s="56"/>
+      <c r="D40" s="56"/>
+      <c r="E40" s="56"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="5">
     <mergeCell ref="A10:E10"/>
     <mergeCell ref="A17:E17"/>
+    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="A38:E38"/>
+    <mergeCell ref="A40:E40"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -28519,32 +29514,32 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="59" t="s">
+      <c r="A2" s="60" t="s">
         <v>904</v>
       </c>
-      <c r="B2" s="58"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
-      <c r="I2" s="58"/>
-      <c r="J2" s="58"/>
+      <c r="B2" s="59"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
     </row>
     <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="57" t="s">
+      <c r="A3" s="58" t="s">
         <v>905</v>
       </c>
-      <c r="B3" s="58"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="58"/>
+      <c r="B3" s="59"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
     </row>
     <row r="5" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
@@ -28596,12 +29591,14 @@
       <c r="E6" s="10" t="s">
         <v>1179</v>
       </c>
-      <c r="F6" s="60"/>
+      <c r="F6" s="62" t="s">
+        <v>1364</v>
+      </c>
       <c r="G6" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B6,'Base Runes'!$A:$A,0)),"")</f>
         <v>Drain</v>
       </c>
-      <c r="H6" s="60"/>
+      <c r="H6" s="55"/>
       <c r="I6" s="10" t="s">
         <v>918</v>
       </c>
@@ -28627,12 +29624,14 @@
       <c r="E7" s="10" t="s">
         <v>1180</v>
       </c>
-      <c r="F7" s="60"/>
+      <c r="F7" s="62" t="s">
+        <v>1365</v>
+      </c>
       <c r="G7" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B7,'Base Runes'!$A:$A,0)),"")</f>
         <v>Flood</v>
       </c>
-      <c r="H7" s="60"/>
+      <c r="H7" s="55"/>
       <c r="I7" s="10"/>
       <c r="J7" s="10"/>
     </row>
@@ -28654,14 +29653,14 @@
       <c r="E8" s="10" t="s">
         <v>911</v>
       </c>
-      <c r="F8" s="61" t="s">
+      <c r="F8" s="10" t="s">
         <v>912</v>
       </c>
       <c r="G8" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B8,'Base Runes'!$A:$A,0)),"")</f>
         <v>Ebb</v>
       </c>
-      <c r="H8" s="61" t="s">
+      <c r="H8" s="10" t="s">
         <v>1181</v>
       </c>
       <c r="I8" s="10" t="s">
@@ -28687,14 +29686,14 @@
       <c r="E9" s="10" t="s">
         <v>914</v>
       </c>
-      <c r="F9" s="61" t="s">
+      <c r="F9" s="10" t="s">
         <v>915</v>
       </c>
       <c r="G9" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B9,'Base Runes'!$A:$A,0)),"")</f>
         <v>Surge</v>
       </c>
-      <c r="H9" s="61" t="s">
+      <c r="H9" s="10" t="s">
         <v>1181</v>
       </c>
       <c r="I9" s="10" t="s">
@@ -28720,14 +29719,14 @@
       <c r="E10" s="10" t="s">
         <v>919</v>
       </c>
-      <c r="F10" s="61" t="s">
+      <c r="F10" s="10" t="s">
         <v>920</v>
       </c>
       <c r="G10" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B10,'Base Runes'!$A:$A,0)),"")</f>
         <v>Dry</v>
       </c>
-      <c r="H10" s="61" t="s">
+      <c r="H10" s="10" t="s">
         <v>1182</v>
       </c>
       <c r="I10" s="10"/>
@@ -28751,14 +29750,14 @@
       <c r="E11" s="10" t="s">
         <v>921</v>
       </c>
-      <c r="F11" s="61" t="s">
+      <c r="F11" s="10" t="s">
         <v>1183</v>
       </c>
       <c r="G11" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B11,'Base Runes'!$A:$A,0)),"")</f>
         <v>Soak</v>
       </c>
-      <c r="H11" s="61" t="s">
+      <c r="H11" s="10" t="s">
         <v>1182</v>
       </c>
       <c r="I11" s="10"/>
@@ -28784,14 +29783,14 @@
       <c r="E12" s="10" t="s">
         <v>1184</v>
       </c>
-      <c r="F12" s="61" t="s">
+      <c r="F12" s="10" t="s">
         <v>1185</v>
       </c>
       <c r="G12" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B12,'Base Runes'!$A:$A,0)),"")</f>
         <v>Drown</v>
       </c>
-      <c r="H12" s="61" t="s">
+      <c r="H12" s="10" t="s">
         <v>1186</v>
       </c>
       <c r="I12" s="10"/>
@@ -28815,14 +29814,14 @@
       <c r="E13" s="10" t="s">
         <v>1187</v>
       </c>
-      <c r="F13" s="61" t="s">
+      <c r="F13" s="10" t="s">
         <v>1188</v>
       </c>
       <c r="G13" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B13,'Base Runes'!$A:$A,0)),"")</f>
         <v>Float</v>
       </c>
-      <c r="H13" s="61" t="s">
+      <c r="H13" s="10" t="s">
         <v>1186</v>
       </c>
       <c r="I13" s="10"/>
@@ -28848,12 +29847,14 @@
       <c r="E14" s="10" t="s">
         <v>1189</v>
       </c>
-      <c r="F14" s="60"/>
+      <c r="F14" s="62" t="s">
+        <v>1366</v>
+      </c>
       <c r="G14" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B14,'Base Runes'!$A:$A,0)),"")</f>
         <v>Drip</v>
       </c>
-      <c r="H14" s="60"/>
+      <c r="H14" s="55"/>
       <c r="I14" s="10" t="s">
         <v>923</v>
       </c>
@@ -28877,12 +29878,14 @@
       <c r="E15" s="10" t="s">
         <v>1190</v>
       </c>
-      <c r="F15" s="60"/>
+      <c r="F15" s="62" t="s">
+        <v>1367</v>
+      </c>
       <c r="G15" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B15,'Base Runes'!$A:$A,0)),"")</f>
         <v>Gush</v>
       </c>
-      <c r="H15" s="60"/>
+      <c r="H15" s="55"/>
       <c r="I15" s="10"/>
       <c r="J15" s="10"/>
     </row>
@@ -28904,12 +29907,14 @@
       <c r="E16" s="10" t="s">
         <v>1191</v>
       </c>
-      <c r="F16" s="60"/>
+      <c r="F16" s="62" t="s">
+        <v>1368</v>
+      </c>
       <c r="G16" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B16,'Base Runes'!$A:$A,0)),"")</f>
         <v>Settle</v>
       </c>
-      <c r="H16" s="60"/>
+      <c r="H16" s="55"/>
       <c r="I16" s="10" t="s">
         <v>917</v>
       </c>
@@ -28933,12 +29938,14 @@
       <c r="E17" s="10" t="s">
         <v>1192</v>
       </c>
-      <c r="F17" s="60"/>
+      <c r="F17" s="62" t="s">
+        <v>1369</v>
+      </c>
       <c r="G17" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B17,'Base Runes'!$A:$A,0)),"")</f>
         <v>Sweep</v>
       </c>
-      <c r="H17" s="60"/>
+      <c r="H17" s="55"/>
       <c r="I17" s="10"/>
       <c r="J17" s="10"/>
     </row>
@@ -28960,12 +29967,14 @@
       <c r="E18" s="10" t="s">
         <v>1193</v>
       </c>
-      <c r="F18" s="60"/>
+      <c r="F18" s="62" t="s">
+        <v>1370</v>
+      </c>
       <c r="G18" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B18,'Base Runes'!$A:$A,0)),"")</f>
         <v>Seep</v>
       </c>
-      <c r="H18" s="60"/>
+      <c r="H18" s="55"/>
       <c r="I18" s="10" t="s">
         <v>925</v>
       </c>
@@ -28989,12 +29998,14 @@
       <c r="E19" s="10" t="s">
         <v>1194</v>
       </c>
-      <c r="F19" s="60"/>
+      <c r="F19" s="62" t="s">
+        <v>1371</v>
+      </c>
       <c r="G19" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B19,'Base Runes'!$A:$A,0)),"")</f>
         <v>Splash</v>
       </c>
-      <c r="H19" s="60"/>
+      <c r="H19" s="55"/>
       <c r="I19" s="10"/>
       <c r="J19" s="10"/>
     </row>
@@ -29016,12 +30027,14 @@
       <c r="E20" s="10" t="s">
         <v>1195</v>
       </c>
-      <c r="F20" s="60"/>
+      <c r="F20" s="62" t="s">
+        <v>1372</v>
+      </c>
       <c r="G20" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B20,'Base Runes'!$A:$A,0)),"")</f>
         <v>Slack</v>
       </c>
-      <c r="H20" s="60"/>
+      <c r="H20" s="55"/>
       <c r="I20" s="10"/>
       <c r="J20" s="10"/>
     </row>
@@ -29043,12 +30056,14 @@
       <c r="E21" s="10" t="s">
         <v>1196</v>
       </c>
-      <c r="F21" s="60"/>
+      <c r="F21" s="62" t="s">
+        <v>1373</v>
+      </c>
       <c r="G21" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B21,'Base Runes'!$A:$A,0)),"")</f>
         <v>Wave</v>
       </c>
-      <c r="H21" s="60"/>
+      <c r="H21" s="55"/>
       <c r="I21" s="10"/>
       <c r="J21" s="10"/>
     </row>
@@ -29090,32 +30105,32 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="59" t="s">
+      <c r="A2" s="60" t="s">
         <v>928</v>
       </c>
-      <c r="B2" s="58"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
-      <c r="I2" s="58"/>
-      <c r="J2" s="58"/>
+      <c r="B2" s="59"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
     </row>
     <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="57" t="s">
+      <c r="A3" s="58" t="s">
         <v>929</v>
       </c>
-      <c r="B3" s="58"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="58"/>
+      <c r="B3" s="59"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
     </row>
     <row r="5" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
@@ -29167,12 +30182,14 @@
       <c r="E6" s="10" t="s">
         <v>1197</v>
       </c>
-      <c r="F6" s="60"/>
+      <c r="F6" s="62" t="s">
+        <v>1374</v>
+      </c>
       <c r="G6" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B6,'Base Runes'!$A:$A,0)),"")</f>
         <v>Quench</v>
       </c>
-      <c r="H6" s="60"/>
+      <c r="H6" s="55"/>
       <c r="I6" s="10" t="s">
         <v>1198</v>
       </c>
@@ -29196,12 +30213,14 @@
       <c r="E7" s="10" t="s">
         <v>1199</v>
       </c>
-      <c r="F7" s="60"/>
+      <c r="F7" s="62" t="s">
+        <v>1375</v>
+      </c>
       <c r="G7" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B7,'Base Runes'!$A:$A,0)),"")</f>
         <v>Burn</v>
       </c>
-      <c r="H7" s="60"/>
+      <c r="H7" s="55"/>
       <c r="I7" s="10"/>
       <c r="J7" s="10"/>
     </row>
@@ -29223,12 +30242,14 @@
       <c r="E8" s="10" t="s">
         <v>1200</v>
       </c>
-      <c r="F8" s="60"/>
+      <c r="F8" s="62" t="s">
+        <v>1376</v>
+      </c>
       <c r="G8" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B8,'Base Runes'!$A:$A,0)),"")</f>
         <v>Snuff</v>
       </c>
-      <c r="H8" s="60"/>
+      <c r="H8" s="55"/>
       <c r="I8" s="10" t="s">
         <v>930</v>
       </c>
@@ -29252,12 +30273,14 @@
       <c r="E9" s="10" t="s">
         <v>1201</v>
       </c>
-      <c r="F9" s="60"/>
+      <c r="F9" s="62" t="s">
+        <v>1377</v>
+      </c>
       <c r="G9" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B9,'Base Runes'!$A:$A,0)),"")</f>
         <v>Ignite</v>
       </c>
-      <c r="H9" s="60"/>
+      <c r="H9" s="55"/>
       <c r="I9" s="10"/>
       <c r="J9" s="10"/>
     </row>
@@ -29279,12 +30302,14 @@
       <c r="E10" s="10" t="s">
         <v>932</v>
       </c>
-      <c r="F10" s="60"/>
+      <c r="F10" s="62" t="s">
+        <v>1378</v>
+      </c>
       <c r="G10" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B10,'Base Runes'!$A:$A,0)),"")</f>
         <v>Implode</v>
       </c>
-      <c r="H10" s="60"/>
+      <c r="H10" s="55"/>
       <c r="I10" s="10" t="s">
         <v>1202</v>
       </c>
@@ -29308,12 +30333,14 @@
       <c r="E11" s="10" t="s">
         <v>933</v>
       </c>
-      <c r="F11" s="60"/>
+      <c r="F11" s="62" t="s">
+        <v>1379</v>
+      </c>
       <c r="G11" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B11,'Base Runes'!$A:$A,0)),"")</f>
         <v>Explode</v>
       </c>
-      <c r="H11" s="60"/>
+      <c r="H11" s="55"/>
       <c r="I11" s="10" t="s">
         <v>934</v>
       </c>
@@ -29337,12 +30364,14 @@
       <c r="E12" s="10" t="s">
         <v>1203</v>
       </c>
-      <c r="F12" s="60"/>
+      <c r="F12" s="62" t="s">
+        <v>1380</v>
+      </c>
       <c r="G12" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B12,'Base Runes'!$A:$A,0)),"")</f>
         <v>Smoulder</v>
       </c>
-      <c r="H12" s="60"/>
+      <c r="H12" s="55"/>
       <c r="I12" s="10" t="s">
         <v>931</v>
       </c>
@@ -29366,12 +30395,14 @@
       <c r="E13" s="10" t="s">
         <v>1204</v>
       </c>
-      <c r="F13" s="60"/>
+      <c r="F13" s="62" t="s">
+        <v>1381</v>
+      </c>
       <c r="G13" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B13,'Base Runes'!$A:$A,0)),"")</f>
         <v>Blaze</v>
       </c>
-      <c r="H13" s="60"/>
+      <c r="H13" s="55"/>
       <c r="I13" s="10" t="s">
         <v>1205</v>
       </c>
@@ -29395,12 +30426,14 @@
       <c r="E14" s="10" t="s">
         <v>1206</v>
       </c>
-      <c r="F14" s="60"/>
+      <c r="F14" s="62" t="s">
+        <v>1382</v>
+      </c>
       <c r="G14" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B14,'Base Runes'!$A:$A,0)),"")</f>
         <v>Smother</v>
       </c>
-      <c r="H14" s="60"/>
+      <c r="H14" s="55"/>
       <c r="I14" s="10"/>
       <c r="J14" s="10"/>
     </row>
@@ -29422,12 +30455,14 @@
       <c r="E15" s="10" t="s">
         <v>1207</v>
       </c>
-      <c r="F15" s="60"/>
+      <c r="F15" s="62" t="s">
+        <v>1383</v>
+      </c>
       <c r="G15" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B15,'Base Runes'!$A:$A,0)),"")</f>
         <v>Flare</v>
       </c>
-      <c r="H15" s="60"/>
+      <c r="H15" s="55"/>
       <c r="I15" s="10"/>
       <c r="J15" s="10"/>
     </row>
@@ -29469,32 +30504,32 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="59" t="s">
+      <c r="A2" s="60" t="s">
         <v>935</v>
       </c>
-      <c r="B2" s="58"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
-      <c r="I2" s="58"/>
-      <c r="J2" s="58"/>
+      <c r="B2" s="59"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
     </row>
     <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="57" t="s">
+      <c r="A3" s="58" t="s">
         <v>929</v>
       </c>
-      <c r="B3" s="58"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="58"/>
+      <c r="B3" s="59"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
     </row>
     <row r="5" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
@@ -29546,12 +30581,14 @@
       <c r="E6" s="10" t="s">
         <v>936</v>
       </c>
-      <c r="F6" s="60"/>
+      <c r="F6" s="62" t="s">
+        <v>1384</v>
+      </c>
       <c r="G6" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B6,'Base Runes'!$A:$A,0)),"")</f>
         <v>Sink</v>
       </c>
-      <c r="H6" s="60"/>
+      <c r="H6" s="55"/>
       <c r="I6" s="10" t="s">
         <v>937</v>
       </c>
@@ -29575,12 +30612,14 @@
       <c r="E7" s="10" t="s">
         <v>938</v>
       </c>
-      <c r="F7" s="60"/>
+      <c r="F7" s="62" t="s">
+        <v>1369</v>
+      </c>
       <c r="G7" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B7,'Base Runes'!$A:$A,0)),"")</f>
         <v>Raise</v>
       </c>
-      <c r="H7" s="60"/>
+      <c r="H7" s="55"/>
       <c r="I7" s="10"/>
       <c r="J7" s="10"/>
     </row>
@@ -29602,12 +30641,14 @@
       <c r="E8" s="10" t="s">
         <v>939</v>
       </c>
-      <c r="F8" s="60"/>
+      <c r="F8" s="62" t="s">
+        <v>1385</v>
+      </c>
       <c r="G8" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B8,'Base Runes'!$A:$A,0)),"")</f>
         <v>Crumble</v>
       </c>
-      <c r="H8" s="60"/>
+      <c r="H8" s="55"/>
       <c r="I8" s="10" t="s">
         <v>940</v>
       </c>
@@ -29631,12 +30672,14 @@
       <c r="E9" s="10" t="s">
         <v>941</v>
       </c>
-      <c r="F9" s="60"/>
+      <c r="F9" s="62" t="s">
+        <v>1386</v>
+      </c>
       <c r="G9" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B9,'Base Runes'!$A:$A,0)),"")</f>
         <v>Harden</v>
       </c>
-      <c r="H9" s="60"/>
+      <c r="H9" s="55"/>
       <c r="I9" s="10" t="s">
         <v>942</v>
       </c>
@@ -29660,12 +30703,14 @@
       <c r="E10" s="10" t="s">
         <v>943</v>
       </c>
-      <c r="F10" s="60"/>
+      <c r="F10" s="62" t="s">
+        <v>1387</v>
+      </c>
       <c r="G10" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B10,'Base Runes'!$A:$A,0)),"")</f>
         <v>Quake</v>
       </c>
-      <c r="H10" s="60"/>
+      <c r="H10" s="55"/>
       <c r="I10" s="10" t="s">
         <v>944</v>
       </c>
@@ -29689,12 +30734,14 @@
       <c r="E11" s="10" t="s">
         <v>945</v>
       </c>
-      <c r="F11" s="60"/>
+      <c r="F11" s="62" t="s">
+        <v>1372</v>
+      </c>
       <c r="G11" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B11,'Base Runes'!$A:$A,0)),"")</f>
         <v>Root</v>
       </c>
-      <c r="H11" s="60"/>
+      <c r="H11" s="55"/>
       <c r="I11" s="10" t="s">
         <v>946</v>
       </c>
@@ -29718,12 +30765,14 @@
       <c r="E12" s="10" t="s">
         <v>1208</v>
       </c>
-      <c r="F12" s="60"/>
+      <c r="F12" s="62" t="s">
+        <v>1388</v>
+      </c>
       <c r="G12" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B12,'Base Runes'!$A:$A,0)),"")</f>
         <v>Bury</v>
       </c>
-      <c r="H12" s="60"/>
+      <c r="H12" s="55"/>
       <c r="I12" s="10" t="s">
         <v>1209</v>
       </c>
@@ -29747,12 +30796,14 @@
       <c r="E13" s="10" t="s">
         <v>1210</v>
       </c>
-      <c r="F13" s="60"/>
+      <c r="F13" s="62" t="s">
+        <v>1389</v>
+      </c>
       <c r="G13" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B13,'Base Runes'!$A:$A,0)),"")</f>
         <v>Dig</v>
       </c>
-      <c r="H13" s="60"/>
+      <c r="H13" s="55"/>
       <c r="I13" s="10"/>
       <c r="J13" s="10"/>
     </row>
@@ -29774,12 +30825,14 @@
       <c r="E14" s="10" t="s">
         <v>1211</v>
       </c>
-      <c r="F14" s="60"/>
+      <c r="F14" s="62" t="s">
+        <v>1371</v>
+      </c>
       <c r="G14" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B14,'Base Runes'!$A:$A,0)),"")</f>
         <v>Collapse</v>
       </c>
-      <c r="H14" s="60"/>
+      <c r="H14" s="55"/>
       <c r="I14" s="10"/>
       <c r="J14" s="10"/>
     </row>
@@ -29801,12 +30854,14 @@
       <c r="E15" s="10" t="s">
         <v>1212</v>
       </c>
-      <c r="F15" s="60"/>
+      <c r="F15" s="62" t="s">
+        <v>1390</v>
+      </c>
       <c r="G15" s="11" t="str">
         <f>IFERROR(INDEX('Base Runes'!$G:$G,MATCH($B15,'Base Runes'!$A:$A,0)),"")</f>
         <v>Tunnel</v>
       </c>
-      <c r="H15" s="60"/>
+      <c r="H15" s="55"/>
       <c r="I15" s="10"/>
       <c r="J15" s="10"/>
     </row>

--- a/design/runes-workbook.xlsx
+++ b/design/runes-workbook.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Code\lifesteal-crawler\design\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E10267EE-787D-47A1-A719-C9DF58AE4238}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB45486B-5F9E-48CC-8F12-E9DA11BA250C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -332,7 +332,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2679" uniqueCount="1674">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2711" uniqueCount="1704">
   <si>
     <t>Passage rune workbook</t>
   </si>
@@ -5354,6 +5354,96 @@
   </si>
   <si>
     <t>2026-10-22: Effect (game) filled for all 166 base runes (the new affinities from their skill drafts), eleven runes revised after the modifier cross-check (hover a changed cell for what it was and why), and every rune's Skills on it filled from design/data-drafts/skills (176 skills).</t>
+  </si>
+  <si>
+    <t>Structure v2: seals as concentric rings (Brent 2026-10-23; first-pass numbers)</t>
+  </si>
+  <si>
+    <t>Each vestige binding forms a seal: a new ring around the skill. Forming a seal you may rework every inner ring and add the new one. Runes on a ring bond to their neighbours on that ring and to runes on the rings just inside and outside. A rune's strength = its ring's fade x the product of every bond's transmission on its path to the skill (each bond's kind factor, read from the side further out). An ionic bond hands the weaker rune's whole effect to the stronger rune.</t>
+  </si>
+  <si>
+    <t>Ring (seal)</t>
+  </si>
+  <si>
+    <t>Runes it adds</t>
+  </si>
+  <si>
+    <t>1 (first binding)</t>
+  </si>
+  <si>
+    <t>5 or more</t>
+  </si>
+  <si>
+    <t>Ring 1 plus the skill's own rune keeps Brent's "level 0 holds 4"; each later seal adds 2 ("+2 per level").</t>
+  </si>
+  <si>
+    <t>Shape trait</t>
+  </si>
+  <si>
+    <t>Needs</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>What it means</t>
+  </si>
+  <si>
+    <t>Closed ring</t>
+  </si>
+  <si>
+    <t>every rune on a ring bonded round it</t>
+  </si>
+  <si>
+    <t>duration x1.2 per closed ring</t>
+  </si>
+  <si>
+    <t>the word holds itself together: the skill lasts longer</t>
+  </si>
+  <si>
+    <t>Great ring</t>
+  </si>
+  <si>
+    <t>a closed ring of 5 or more</t>
+  </si>
+  <si>
+    <t>repeats once at 40%</t>
+  </si>
+  <si>
+    <t>it comes round again</t>
+  </si>
+  <si>
+    <t>Spoke</t>
+  </si>
+  <si>
+    <t>a chain from ring 1 out through 3 or more rings</t>
+  </si>
+  <si>
+    <t>reach x1.15 and speed x1.15 per ring past the second</t>
+  </si>
+  <si>
+    <t>the word reaches out</t>
+  </si>
+  <si>
+    <t>a rune with 3 or more bonds</t>
+  </si>
+  <si>
+    <t>reach (area) x1.15 per branch rune, up to 3</t>
+  </si>
+  <si>
+    <t>the effect spreads</t>
+  </si>
+  <si>
+    <t>Balanced</t>
+  </si>
+  <si>
+    <t>ring 1 full, every bond to the skill the same kind</t>
+  </si>
+  <si>
+    <t>the skill's own rune keeps all of its nature</t>
+  </si>
+  <si>
+    <t>the skill stays itself</t>
   </si>
 </sst>
 </file>
@@ -5741,6 +5831,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -5752,9 +5845,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -10608,32 +10698,32 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="63" t="s">
+      <c r="A2" s="64" t="s">
         <v>942</v>
       </c>
-      <c r="B2" s="62"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
-      <c r="J2" s="62"/>
+      <c r="B2" s="63"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
+      <c r="J2" s="63"/>
     </row>
     <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="61" t="s">
+      <c r="A3" s="62" t="s">
         <v>928</v>
       </c>
-      <c r="B3" s="62"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="62"/>
-      <c r="I3" s="62"/>
-      <c r="J3" s="62"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="63"/>
+      <c r="I3" s="63"/>
+      <c r="J3" s="63"/>
     </row>
     <row r="5" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
@@ -10693,7 +10783,7 @@
         <v>Lull</v>
       </c>
       <c r="H6" s="55"/>
-      <c r="I6" s="64" t="s">
+      <c r="I6" s="59" t="s">
         <v>943</v>
       </c>
       <c r="J6" s="10"/>
@@ -10724,7 +10814,7 @@
         <v>Blow</v>
       </c>
       <c r="H7" s="55"/>
-      <c r="I7" s="64" t="s">
+      <c r="I7" s="59" t="s">
         <v>1550</v>
       </c>
       <c r="J7" s="10"/>
@@ -10755,7 +10845,7 @@
         <v>Buffer</v>
       </c>
       <c r="H8" s="55"/>
-      <c r="I8" s="64" t="s">
+      <c r="I8" s="59" t="s">
         <v>1551</v>
       </c>
       <c r="J8" s="10"/>
@@ -10786,7 +10876,7 @@
         <v>Lash</v>
       </c>
       <c r="H9" s="55"/>
-      <c r="I9" s="64" t="s">
+      <c r="I9" s="59" t="s">
         <v>947</v>
       </c>
       <c r="J9" s="10"/>
@@ -10817,7 +10907,7 @@
         <v>Drop</v>
       </c>
       <c r="H10" s="55"/>
-      <c r="I10" s="64" t="s">
+      <c r="I10" s="59" t="s">
         <v>225</v>
       </c>
       <c r="J10" s="10"/>
@@ -10848,7 +10938,7 @@
         <v>Lift</v>
       </c>
       <c r="H11" s="55"/>
-      <c r="I11" s="64" t="s">
+      <c r="I11" s="59" t="s">
         <v>229</v>
       </c>
       <c r="J11" s="10"/>
@@ -10879,7 +10969,7 @@
         <v>Stall</v>
       </c>
       <c r="H12" s="55"/>
-      <c r="I12" s="64" t="s">
+      <c r="I12" s="59" t="s">
         <v>1552</v>
       </c>
       <c r="J12" s="10"/>
@@ -10910,7 +11000,7 @@
         <v>Carry</v>
       </c>
       <c r="H13" s="55"/>
-      <c r="I13" s="64" t="s">
+      <c r="I13" s="59" t="s">
         <v>1553</v>
       </c>
       <c r="J13" s="10"/>
@@ -10941,7 +11031,7 @@
         <v>Disperse</v>
       </c>
       <c r="H14" s="55"/>
-      <c r="I14" s="64" t="s">
+      <c r="I14" s="59" t="s">
         <v>1554</v>
       </c>
       <c r="J14" s="10"/>
@@ -10972,7 +11062,7 @@
         <v>Whirl</v>
       </c>
       <c r="H15" s="55"/>
-      <c r="I15" s="64" t="s">
+      <c r="I15" s="59" t="s">
         <v>1555</v>
       </c>
       <c r="J15" s="10"/>
@@ -11015,32 +11105,32 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="63" t="s">
+      <c r="A2" s="64" t="s">
         <v>950</v>
       </c>
-      <c r="B2" s="62"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
-      <c r="J2" s="62"/>
+      <c r="B2" s="63"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
+      <c r="J2" s="63"/>
     </row>
     <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="61" t="s">
+      <c r="A3" s="62" t="s">
         <v>928</v>
       </c>
-      <c r="B3" s="62"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="62"/>
-      <c r="I3" s="62"/>
-      <c r="J3" s="62"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="63"/>
+      <c r="I3" s="63"/>
+      <c r="J3" s="63"/>
     </row>
     <row r="5" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
@@ -11100,7 +11190,7 @@
         <v>Ground</v>
       </c>
       <c r="H6" s="55"/>
-      <c r="I6" s="64" t="s">
+      <c r="I6" s="59" t="s">
         <v>1556</v>
       </c>
       <c r="J6" s="10"/>
@@ -11131,7 +11221,7 @@
         <v>Strike</v>
       </c>
       <c r="H7" s="55"/>
-      <c r="I7" s="64" t="s">
+      <c r="I7" s="59" t="s">
         <v>955</v>
       </c>
       <c r="J7" s="10"/>
@@ -11162,7 +11252,7 @@
         <v>Discharge</v>
       </c>
       <c r="H8" s="55"/>
-      <c r="I8" s="64" t="s">
+      <c r="I8" s="59" t="s">
         <v>952</v>
       </c>
       <c r="J8" s="10"/>
@@ -11193,7 +11283,7 @@
         <v>Charge</v>
       </c>
       <c r="H9" s="55"/>
-      <c r="I9" s="64" t="s">
+      <c r="I9" s="59" t="s">
         <v>1210</v>
       </c>
       <c r="J9" s="10"/>
@@ -11224,7 +11314,7 @@
         <v>Insulate</v>
       </c>
       <c r="H10" s="55"/>
-      <c r="I10" s="64" t="s">
+      <c r="I10" s="59" t="s">
         <v>1557</v>
       </c>
       <c r="J10" s="10"/>
@@ -11255,7 +11345,7 @@
         <v>Arc</v>
       </c>
       <c r="H11" s="55"/>
-      <c r="I11" s="64" t="s">
+      <c r="I11" s="59" t="s">
         <v>1558</v>
       </c>
       <c r="J11" s="10"/>
@@ -11286,7 +11376,7 @@
         <v>Stun</v>
       </c>
       <c r="H12" s="55"/>
-      <c r="I12" s="64" t="s">
+      <c r="I12" s="59" t="s">
         <v>1559</v>
       </c>
       <c r="J12" s="10"/>
@@ -11317,7 +11407,7 @@
         <v>Quicken</v>
       </c>
       <c r="H13" s="55"/>
-      <c r="I13" s="64" t="s">
+      <c r="I13" s="59" t="s">
         <v>1560</v>
       </c>
       <c r="J13" s="10"/>
@@ -11348,7 +11438,7 @@
         <v>Silence</v>
       </c>
       <c r="H14" s="55"/>
-      <c r="I14" s="64" t="s">
+      <c r="I14" s="59" t="s">
         <v>1561</v>
       </c>
       <c r="J14" s="10"/>
@@ -11379,7 +11469,7 @@
         <v>Thunder</v>
       </c>
       <c r="H15" s="55"/>
-      <c r="I15" s="64" t="s">
+      <c r="I15" s="59" t="s">
         <v>1562</v>
       </c>
       <c r="J15" s="10"/>
@@ -11422,32 +11512,32 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="63" t="s">
+      <c r="A2" s="64" t="s">
         <v>958</v>
       </c>
-      <c r="B2" s="62"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
-      <c r="J2" s="62"/>
+      <c r="B2" s="63"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
+      <c r="J2" s="63"/>
     </row>
     <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="61" t="s">
+      <c r="A3" s="62" t="s">
         <v>959</v>
       </c>
-      <c r="B3" s="62"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="62"/>
-      <c r="I3" s="62"/>
-      <c r="J3" s="62"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="63"/>
+      <c r="I3" s="63"/>
+      <c r="J3" s="63"/>
     </row>
     <row r="5" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
@@ -11505,7 +11595,7 @@
         <v>Thaw</v>
       </c>
       <c r="H6" s="55"/>
-      <c r="I6" s="64" t="s">
+      <c r="I6" s="59" t="s">
         <v>1563</v>
       </c>
       <c r="J6" s="10"/>
@@ -11534,7 +11624,7 @@
         <v>Freeze</v>
       </c>
       <c r="H7" s="55"/>
-      <c r="I7" s="64" t="s">
+      <c r="I7" s="59" t="s">
         <v>1564</v>
       </c>
       <c r="J7" s="10"/>
@@ -11563,7 +11653,7 @@
         <v>Glaze</v>
       </c>
       <c r="H8" s="55"/>
-      <c r="I8" s="64" t="s">
+      <c r="I8" s="59" t="s">
         <v>1565</v>
       </c>
       <c r="J8" s="10"/>
@@ -11592,7 +11682,7 @@
         <v>Frost</v>
       </c>
       <c r="H9" s="55"/>
-      <c r="I9" s="64" t="s">
+      <c r="I9" s="59" t="s">
         <v>1566</v>
       </c>
       <c r="J9" s="10"/>
@@ -11621,7 +11711,7 @@
         <v>Melt</v>
       </c>
       <c r="H10" s="55"/>
-      <c r="I10" s="64" t="s">
+      <c r="I10" s="59" t="s">
         <v>1567</v>
       </c>
       <c r="J10" s="10"/>
@@ -11650,7 +11740,7 @@
         <v>Snow</v>
       </c>
       <c r="H11" s="55"/>
-      <c r="I11" s="64" t="s">
+      <c r="I11" s="59" t="s">
         <v>1568</v>
       </c>
       <c r="J11" s="10"/>
@@ -11679,7 +11769,7 @@
         <v>Shatter</v>
       </c>
       <c r="H12" s="55"/>
-      <c r="I12" s="64" t="s">
+      <c r="I12" s="59" t="s">
         <v>1569</v>
       </c>
       <c r="J12" s="10"/>
@@ -11708,7 +11798,7 @@
         <v>Rime</v>
       </c>
       <c r="H13" s="55"/>
-      <c r="I13" s="64" t="s">
+      <c r="I13" s="59" t="s">
         <v>1570</v>
       </c>
       <c r="J13" s="10"/>
@@ -11737,7 +11827,7 @@
         <v>Toughen</v>
       </c>
       <c r="H14" s="55"/>
-      <c r="I14" s="64" t="s">
+      <c r="I14" s="59" t="s">
         <v>1571</v>
       </c>
       <c r="J14" s="10"/>
@@ -11766,7 +11856,7 @@
         <v>Brittle</v>
       </c>
       <c r="H15" s="55"/>
-      <c r="I15" s="64" t="s">
+      <c r="I15" s="59" t="s">
         <v>1572</v>
       </c>
       <c r="J15" s="10"/>
@@ -11809,32 +11899,32 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="63" t="s">
+      <c r="A2" s="64" t="s">
         <v>966</v>
       </c>
-      <c r="B2" s="62"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
-      <c r="J2" s="62"/>
+      <c r="B2" s="63"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
+      <c r="J2" s="63"/>
     </row>
     <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="61" t="s">
+      <c r="A3" s="62" t="s">
         <v>967</v>
       </c>
-      <c r="B3" s="62"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="62"/>
-      <c r="I3" s="62"/>
-      <c r="J3" s="62"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="63"/>
+      <c r="I3" s="63"/>
+      <c r="J3" s="63"/>
     </row>
     <row r="5" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
@@ -11892,7 +11982,7 @@
         <v>Lighten</v>
       </c>
       <c r="H6" s="55"/>
-      <c r="I6" s="64" t="s">
+      <c r="I6" s="59" t="s">
         <v>1573</v>
       </c>
       <c r="J6" s="10"/>
@@ -11921,7 +12011,7 @@
         <v>Darken</v>
       </c>
       <c r="H7" s="55"/>
-      <c r="I7" s="64" t="s">
+      <c r="I7" s="59" t="s">
         <v>1574</v>
       </c>
       <c r="J7" s="10"/>
@@ -11950,7 +12040,7 @@
         <v>Expose</v>
       </c>
       <c r="H8" s="55"/>
-      <c r="I8" s="64" t="s">
+      <c r="I8" s="59" t="s">
         <v>1575</v>
       </c>
       <c r="J8" s="10"/>
@@ -11979,7 +12069,7 @@
         <v>Obscure</v>
       </c>
       <c r="H9" s="55"/>
-      <c r="I9" s="64" t="s">
+      <c r="I9" s="59" t="s">
         <v>1576</v>
       </c>
       <c r="J9" s="10"/>
@@ -12008,7 +12098,7 @@
         <v>Pin</v>
       </c>
       <c r="H10" s="55"/>
-      <c r="I10" s="64" t="s">
+      <c r="I10" s="59" t="s">
         <v>1577</v>
       </c>
       <c r="J10" s="10"/>
@@ -12037,7 +12127,7 @@
         <v>Shadowstep</v>
       </c>
       <c r="H11" s="55"/>
-      <c r="I11" s="64" t="s">
+      <c r="I11" s="59" t="s">
         <v>1578</v>
       </c>
       <c r="J11" s="10"/>
@@ -12066,7 +12156,7 @@
         <v>Resound</v>
       </c>
       <c r="H12" s="55"/>
-      <c r="I12" s="64" t="s">
+      <c r="I12" s="59" t="s">
         <v>1579</v>
       </c>
       <c r="J12" s="10"/>
@@ -12095,7 +12185,7 @@
         <v>Hush</v>
       </c>
       <c r="H13" s="55"/>
-      <c r="I13" s="64" t="s">
+      <c r="I13" s="59" t="s">
         <v>1580</v>
       </c>
       <c r="J13" s="10"/>
@@ -12124,7 +12214,7 @@
         <v>Disgorge</v>
       </c>
       <c r="H14" s="55"/>
-      <c r="I14" s="64" t="s">
+      <c r="I14" s="59" t="s">
         <v>1581</v>
       </c>
       <c r="J14" s="10"/>
@@ -12153,7 +12243,7 @@
         <v>Devour</v>
       </c>
       <c r="H15" s="55"/>
-      <c r="I15" s="64" t="s">
+      <c r="I15" s="59" t="s">
         <v>1582</v>
       </c>
       <c r="J15" s="10"/>
@@ -12196,32 +12286,32 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="63" t="s">
+      <c r="A2" s="64" t="s">
         <v>974</v>
       </c>
-      <c r="B2" s="62"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
-      <c r="J2" s="62"/>
+      <c r="B2" s="63"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
+      <c r="J2" s="63"/>
     </row>
     <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="61" t="s">
+      <c r="A3" s="62" t="s">
         <v>975</v>
       </c>
-      <c r="B3" s="62"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="62"/>
-      <c r="I3" s="62"/>
-      <c r="J3" s="62"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="63"/>
+      <c r="I3" s="63"/>
+      <c r="J3" s="63"/>
     </row>
     <row r="5" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
@@ -12279,7 +12369,7 @@
         <v>Rust</v>
       </c>
       <c r="H6" s="55"/>
-      <c r="I6" s="64" t="s">
+      <c r="I6" s="59" t="s">
         <v>1583</v>
       </c>
       <c r="J6" s="10"/>
@@ -12308,7 +12398,7 @@
         <v>Forge</v>
       </c>
       <c r="H7" s="55"/>
-      <c r="I7" s="64" t="s">
+      <c r="I7" s="59" t="s">
         <v>1584</v>
       </c>
       <c r="J7" s="10"/>
@@ -12337,7 +12427,7 @@
         <v>Sunder</v>
       </c>
       <c r="H8" s="55"/>
-      <c r="I8" s="64" t="s">
+      <c r="I8" s="59" t="s">
         <v>1585</v>
       </c>
       <c r="J8" s="10"/>
@@ -12366,7 +12456,7 @@
         <v>Fuse</v>
       </c>
       <c r="H9" s="55"/>
-      <c r="I9" s="64" t="s">
+      <c r="I9" s="59" t="s">
         <v>1586</v>
       </c>
       <c r="J9" s="10"/>
@@ -12395,7 +12485,7 @@
         <v>Breach</v>
       </c>
       <c r="H10" s="55"/>
-      <c r="I10" s="64" t="s">
+      <c r="I10" s="59" t="s">
         <v>1587</v>
       </c>
       <c r="J10" s="10"/>
@@ -12424,7 +12514,7 @@
         <v>Seal</v>
       </c>
       <c r="H11" s="55"/>
-      <c r="I11" s="64" t="s">
+      <c r="I11" s="59" t="s">
         <v>1588</v>
       </c>
       <c r="J11" s="10"/>
@@ -12453,7 +12543,7 @@
         <v>Dull</v>
       </c>
       <c r="H12" s="55"/>
-      <c r="I12" s="64" t="s">
+      <c r="I12" s="59" t="s">
         <v>1589</v>
       </c>
       <c r="J12" s="10"/>
@@ -12482,7 +12572,7 @@
         <v>Hone</v>
       </c>
       <c r="H13" s="55"/>
-      <c r="I13" s="64" t="s">
+      <c r="I13" s="59" t="s">
         <v>1590</v>
       </c>
       <c r="J13" s="10"/>
@@ -12511,7 +12601,7 @@
         <v>Strip</v>
       </c>
       <c r="H14" s="55"/>
-      <c r="I14" s="64" t="s">
+      <c r="I14" s="59" t="s">
         <v>1591</v>
       </c>
       <c r="J14" s="10"/>
@@ -12540,7 +12630,7 @@
         <v>Plate</v>
       </c>
       <c r="H15" s="55"/>
-      <c r="I15" s="64" t="s">
+      <c r="I15" s="59" t="s">
         <v>1592</v>
       </c>
       <c r="J15" s="10"/>
@@ -12583,32 +12673,32 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="63" t="s">
+      <c r="A2" s="64" t="s">
         <v>982</v>
       </c>
-      <c r="B2" s="62"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
-      <c r="J2" s="62"/>
+      <c r="B2" s="63"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
+      <c r="J2" s="63"/>
     </row>
     <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="61" t="s">
+      <c r="A3" s="62" t="s">
         <v>983</v>
       </c>
-      <c r="B3" s="62"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="62"/>
-      <c r="I3" s="62"/>
-      <c r="J3" s="62"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="63"/>
+      <c r="I3" s="63"/>
+      <c r="J3" s="63"/>
     </row>
     <row r="5" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
@@ -12666,7 +12756,7 @@
         <v>Staunch</v>
       </c>
       <c r="H6" s="55"/>
-      <c r="I6" s="64" t="s">
+      <c r="I6" s="59" t="s">
         <v>1593</v>
       </c>
       <c r="J6" s="10"/>
@@ -12695,7 +12785,7 @@
         <v>Bleed</v>
       </c>
       <c r="H7" s="55"/>
-      <c r="I7" s="64" t="s">
+      <c r="I7" s="59" t="s">
         <v>1594</v>
       </c>
       <c r="J7" s="10"/>
@@ -12724,7 +12814,7 @@
         <v>Spill</v>
       </c>
       <c r="H8" s="55"/>
-      <c r="I8" s="64" t="s">
+      <c r="I8" s="59" t="s">
         <v>1595</v>
       </c>
       <c r="J8" s="10"/>
@@ -12753,7 +12843,7 @@
         <v>Drink</v>
       </c>
       <c r="H9" s="55"/>
-      <c r="I9" s="64" t="s">
+      <c r="I9" s="59" t="s">
         <v>1596</v>
       </c>
       <c r="J9" s="10"/>
@@ -12782,7 +12872,7 @@
         <v>Thin</v>
       </c>
       <c r="H10" s="55"/>
-      <c r="I10" s="64" t="s">
+      <c r="I10" s="59" t="s">
         <v>1597</v>
       </c>
       <c r="J10" s="10"/>
@@ -12811,7 +12901,7 @@
         <v>Clot</v>
       </c>
       <c r="H11" s="55"/>
-      <c r="I11" s="64" t="s">
+      <c r="I11" s="59" t="s">
         <v>1598</v>
       </c>
       <c r="J11" s="10"/>
@@ -12840,7 +12930,7 @@
         <v>Still</v>
       </c>
       <c r="H12" s="55"/>
-      <c r="I12" s="64" t="s">
+      <c r="I12" s="59" t="s">
         <v>1599</v>
       </c>
       <c r="J12" s="10"/>
@@ -12869,7 +12959,7 @@
         <v>Pulse</v>
       </c>
       <c r="H13" s="55"/>
-      <c r="I13" s="64" t="s">
+      <c r="I13" s="59" t="s">
         <v>1600</v>
       </c>
       <c r="J13" s="10"/>
@@ -12898,7 +12988,7 @@
         <v>Breathe</v>
       </c>
       <c r="H14" s="55"/>
-      <c r="I14" s="64" t="s">
+      <c r="I14" s="59" t="s">
         <v>1601</v>
       </c>
       <c r="J14" s="10"/>
@@ -12927,7 +13017,7 @@
         <v>Choke</v>
       </c>
       <c r="H15" s="55"/>
-      <c r="I15" s="64" t="s">
+      <c r="I15" s="59" t="s">
         <v>1602</v>
       </c>
       <c r="J15" s="10"/>
@@ -12970,32 +13060,32 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="63" t="s">
+      <c r="A2" s="64" t="s">
         <v>990</v>
       </c>
-      <c r="B2" s="62"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
-      <c r="J2" s="62"/>
+      <c r="B2" s="63"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
+      <c r="J2" s="63"/>
     </row>
     <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="61" t="s">
+      <c r="A3" s="62" t="s">
         <v>991</v>
       </c>
-      <c r="B3" s="62"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="62"/>
-      <c r="I3" s="62"/>
-      <c r="J3" s="62"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="63"/>
+      <c r="I3" s="63"/>
+      <c r="J3" s="63"/>
     </row>
     <row r="5" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
@@ -13053,7 +13143,7 @@
         <v>Wither</v>
       </c>
       <c r="H6" s="55"/>
-      <c r="I6" s="64" t="s">
+      <c r="I6" s="59" t="s">
         <v>1603</v>
       </c>
       <c r="J6" s="10"/>
@@ -13082,7 +13172,7 @@
         <v>Heal</v>
       </c>
       <c r="H7" s="55"/>
-      <c r="I7" s="64" t="s">
+      <c r="I7" s="59" t="s">
         <v>1604</v>
       </c>
       <c r="J7" s="10"/>
@@ -13111,7 +13201,7 @@
         <v>Exhaust</v>
       </c>
       <c r="H8" s="55"/>
-      <c r="I8" s="64" t="s">
+      <c r="I8" s="59" t="s">
         <v>1605</v>
       </c>
       <c r="J8" s="10"/>
@@ -13140,7 +13230,7 @@
         <v>Renew</v>
       </c>
       <c r="H9" s="55"/>
-      <c r="I9" s="64" t="s">
+      <c r="I9" s="59" t="s">
         <v>1606</v>
       </c>
       <c r="J9" s="10"/>
@@ -13169,7 +13259,7 @@
         <v>Weaken</v>
       </c>
       <c r="H10" s="55"/>
-      <c r="I10" s="64" t="s">
+      <c r="I10" s="59" t="s">
         <v>1607</v>
       </c>
       <c r="J10" s="10"/>
@@ -13198,7 +13288,7 @@
         <v>Strengthen</v>
       </c>
       <c r="H11" s="55"/>
-      <c r="I11" s="64" t="s">
+      <c r="I11" s="59" t="s">
         <v>1608</v>
       </c>
       <c r="J11" s="10"/>
@@ -13227,7 +13317,7 @@
         <v>Sicken</v>
       </c>
       <c r="H12" s="55"/>
-      <c r="I12" s="64" t="s">
+      <c r="I12" s="59" t="s">
         <v>1609</v>
       </c>
       <c r="J12" s="10"/>
@@ -13256,7 +13346,7 @@
         <v>Cure</v>
       </c>
       <c r="H13" s="55"/>
-      <c r="I13" s="64" t="s">
+      <c r="I13" s="59" t="s">
         <v>1610</v>
       </c>
       <c r="J13" s="10"/>
@@ -13285,7 +13375,7 @@
         <v>Arrest</v>
       </c>
       <c r="H14" s="55"/>
-      <c r="I14" s="64" t="s">
+      <c r="I14" s="59" t="s">
         <v>1611</v>
       </c>
       <c r="J14" s="10"/>
@@ -13314,7 +13404,7 @@
         <v>Regrow</v>
       </c>
       <c r="H15" s="55"/>
-      <c r="I15" s="64" t="s">
+      <c r="I15" s="59" t="s">
         <v>1612</v>
       </c>
       <c r="J15" s="10"/>
@@ -13357,32 +13447,32 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="63" t="s">
+      <c r="A2" s="64" t="s">
         <v>996</v>
       </c>
-      <c r="B2" s="62"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
-      <c r="J2" s="62"/>
+      <c r="B2" s="63"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
+      <c r="J2" s="63"/>
     </row>
     <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="61" t="s">
+      <c r="A3" s="62" t="s">
         <v>997</v>
       </c>
-      <c r="B3" s="62"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="62"/>
-      <c r="I3" s="62"/>
-      <c r="J3" s="62"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="63"/>
+      <c r="I3" s="63"/>
+      <c r="J3" s="63"/>
     </row>
     <row r="5" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
@@ -13440,7 +13530,7 @@
         <v>Spare</v>
       </c>
       <c r="H6" s="55"/>
-      <c r="I6" s="64" t="s">
+      <c r="I6" s="59" t="s">
         <v>1613</v>
       </c>
       <c r="J6" s="10"/>
@@ -13469,7 +13559,7 @@
         <v>Kill</v>
       </c>
       <c r="H7" s="55"/>
-      <c r="I7" s="64" t="s">
+      <c r="I7" s="59" t="s">
         <v>1614</v>
       </c>
       <c r="J7" s="10"/>
@@ -13498,7 +13588,7 @@
         <v>Lay</v>
       </c>
       <c r="H8" s="55"/>
-      <c r="I8" s="64" t="s">
+      <c r="I8" s="59" t="s">
         <v>1615</v>
       </c>
       <c r="J8" s="10"/>
@@ -13527,7 +13617,7 @@
         <v>Animate</v>
       </c>
       <c r="H9" s="55"/>
-      <c r="I9" s="64" t="s">
+      <c r="I9" s="59" t="s">
         <v>1616</v>
       </c>
       <c r="J9" s="10"/>
@@ -13556,7 +13646,7 @@
         <v>Preserve</v>
       </c>
       <c r="H10" s="55"/>
-      <c r="I10" s="64" t="s">
+      <c r="I10" s="59" t="s">
         <v>1617</v>
       </c>
       <c r="J10" s="10"/>
@@ -13585,7 +13675,7 @@
         <v>Rot</v>
       </c>
       <c r="H11" s="55"/>
-      <c r="I11" s="64" t="s">
+      <c r="I11" s="59" t="s">
         <v>1618</v>
       </c>
       <c r="J11" s="10"/>
@@ -13614,7 +13704,7 @@
         <v>Exorcise</v>
       </c>
       <c r="H12" s="55"/>
-      <c r="I12" s="64" t="s">
+      <c r="I12" s="59" t="s">
         <v>1619</v>
       </c>
       <c r="J12" s="10"/>
@@ -13643,7 +13733,7 @@
         <v>Haunt</v>
       </c>
       <c r="H13" s="55"/>
-      <c r="I13" s="64" t="s">
+      <c r="I13" s="59" t="s">
         <v>1620</v>
       </c>
       <c r="J13" s="10"/>
@@ -13672,7 +13762,7 @@
         <v>Manifest</v>
       </c>
       <c r="H14" s="55"/>
-      <c r="I14" s="64" t="s">
+      <c r="I14" s="59" t="s">
         <v>1621</v>
       </c>
       <c r="J14" s="10"/>
@@ -13701,7 +13791,7 @@
         <v>Vanish</v>
       </c>
       <c r="H15" s="55"/>
-      <c r="I15" s="64" t="s">
+      <c r="I15" s="59" t="s">
         <v>1622</v>
       </c>
       <c r="J15" s="10"/>
@@ -13744,32 +13834,32 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="63" t="s">
+      <c r="A2" s="64" t="s">
         <v>1006</v>
       </c>
-      <c r="B2" s="62"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
-      <c r="J2" s="62"/>
+      <c r="B2" s="63"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
+      <c r="J2" s="63"/>
     </row>
     <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="61" t="s">
+      <c r="A3" s="62" t="s">
         <v>1007</v>
       </c>
-      <c r="B3" s="62"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="62"/>
-      <c r="I3" s="62"/>
-      <c r="J3" s="62"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="63"/>
+      <c r="I3" s="63"/>
+      <c r="J3" s="63"/>
     </row>
     <row r="5" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
@@ -13827,7 +13917,7 @@
         <v>Shrink</v>
       </c>
       <c r="H6" s="55"/>
-      <c r="I6" s="64" t="s">
+      <c r="I6" s="59" t="s">
         <v>1623</v>
       </c>
       <c r="J6" s="10"/>
@@ -13856,7 +13946,7 @@
         <v>Grow</v>
       </c>
       <c r="H7" s="55"/>
-      <c r="I7" s="64" t="s">
+      <c r="I7" s="59" t="s">
         <v>1624</v>
       </c>
       <c r="J7" s="10"/>
@@ -13885,7 +13975,7 @@
         <v>Wilt</v>
       </c>
       <c r="H8" s="55"/>
-      <c r="I8" s="64" t="s">
+      <c r="I8" s="59" t="s">
         <v>1625</v>
       </c>
       <c r="J8" s="10"/>
@@ -13914,7 +14004,7 @@
         <v>Sprout</v>
       </c>
       <c r="H9" s="55"/>
-      <c r="I9" s="64" t="s">
+      <c r="I9" s="59" t="s">
         <v>1626</v>
       </c>
       <c r="J9" s="10"/>
@@ -13943,7 +14033,7 @@
         <v>Blight</v>
       </c>
       <c r="H10" s="55"/>
-      <c r="I10" s="64" t="s">
+      <c r="I10" s="59" t="s">
         <v>1627</v>
       </c>
       <c r="J10" s="10"/>
@@ -13972,7 +14062,7 @@
         <v>Flourish</v>
       </c>
       <c r="H11" s="55"/>
-      <c r="I11" s="64" t="s">
+      <c r="I11" s="59" t="s">
         <v>1628</v>
       </c>
       <c r="J11" s="10"/>
@@ -14001,7 +14091,7 @@
         <v>Sow</v>
       </c>
       <c r="H12" s="55"/>
-      <c r="I12" s="64" t="s">
+      <c r="I12" s="59" t="s">
         <v>1629</v>
       </c>
       <c r="J12" s="10"/>
@@ -14030,7 +14120,7 @@
         <v>Harvest</v>
       </c>
       <c r="H13" s="55"/>
-      <c r="I13" s="64" t="s">
+      <c r="I13" s="59" t="s">
         <v>1630</v>
       </c>
       <c r="J13" s="10"/>
@@ -14059,7 +14149,7 @@
         <v>Unravel</v>
       </c>
       <c r="H14" s="55"/>
-      <c r="I14" s="64" t="s">
+      <c r="I14" s="59" t="s">
         <v>1631</v>
       </c>
       <c r="J14" s="10"/>
@@ -14088,7 +14178,7 @@
         <v>Tangle</v>
       </c>
       <c r="H15" s="55"/>
-      <c r="I15" s="64" t="s">
+      <c r="I15" s="59" t="s">
         <v>1632</v>
       </c>
       <c r="J15" s="10"/>
@@ -14131,32 +14221,32 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="63" t="s">
+      <c r="A2" s="64" t="s">
         <v>1011</v>
       </c>
-      <c r="B2" s="62"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
-      <c r="J2" s="62"/>
+      <c r="B2" s="63"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
+      <c r="J2" s="63"/>
     </row>
     <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="61" t="s">
+      <c r="A3" s="62" t="s">
         <v>1012</v>
       </c>
-      <c r="B3" s="62"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="62"/>
-      <c r="I3" s="62"/>
-      <c r="J3" s="62"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="63"/>
+      <c r="I3" s="63"/>
+      <c r="J3" s="63"/>
     </row>
     <row r="5" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
@@ -14214,7 +14304,7 @@
         <v>Dim</v>
       </c>
       <c r="H6" s="55"/>
-      <c r="I6" s="64" t="s">
+      <c r="I6" s="59" t="s">
         <v>1633</v>
       </c>
       <c r="J6" s="10"/>
@@ -14243,7 +14333,7 @@
         <v>Shine</v>
       </c>
       <c r="H7" s="55"/>
-      <c r="I7" s="64" t="s">
+      <c r="I7" s="59" t="s">
         <v>1634</v>
       </c>
       <c r="J7" s="10"/>
@@ -14272,7 +14362,7 @@
         <v>Glow</v>
       </c>
       <c r="H8" s="55"/>
-      <c r="I8" s="64" t="s">
+      <c r="I8" s="59" t="s">
         <v>1635</v>
       </c>
       <c r="J8" s="10"/>
@@ -14301,7 +14391,7 @@
         <v>Flash</v>
       </c>
       <c r="H9" s="55"/>
-      <c r="I9" s="64" t="s">
+      <c r="I9" s="59" t="s">
         <v>1636</v>
       </c>
       <c r="J9" s="10"/>
@@ -14330,7 +14420,7 @@
         <v>Absorb</v>
       </c>
       <c r="H10" s="55"/>
-      <c r="I10" s="64" t="s">
+      <c r="I10" s="59" t="s">
         <v>1637</v>
       </c>
       <c r="J10" s="10"/>
@@ -14359,7 +14449,7 @@
         <v>Radiate</v>
       </c>
       <c r="H11" s="55"/>
-      <c r="I11" s="64" t="s">
+      <c r="I11" s="59" t="s">
         <v>1638</v>
       </c>
       <c r="J11" s="10"/>
@@ -14388,7 +14478,7 @@
         <v>Clarity</v>
       </c>
       <c r="H12" s="55"/>
-      <c r="I12" s="64" t="s">
+      <c r="I12" s="59" t="s">
         <v>1639</v>
       </c>
       <c r="J12" s="10"/>
@@ -14417,7 +14507,7 @@
         <v>Glare</v>
       </c>
       <c r="H13" s="55"/>
-      <c r="I13" s="64" t="s">
+      <c r="I13" s="59" t="s">
         <v>1640</v>
       </c>
       <c r="J13" s="10"/>
@@ -14446,7 +14536,7 @@
         <v>Bend</v>
       </c>
       <c r="H14" s="55"/>
-      <c r="I14" s="64" t="s">
+      <c r="I14" s="59" t="s">
         <v>1641</v>
       </c>
       <c r="J14" s="10"/>
@@ -14475,7 +14565,7 @@
         <v>Reflect</v>
       </c>
       <c r="H15" s="55"/>
-      <c r="I15" s="64" t="s">
+      <c r="I15" s="59" t="s">
         <v>1642</v>
       </c>
       <c r="J15" s="10"/>
@@ -17177,32 +17267,32 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="63" t="s">
+      <c r="A2" s="64" t="s">
         <v>1015</v>
       </c>
-      <c r="B2" s="62"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
-      <c r="J2" s="62"/>
+      <c r="B2" s="63"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
+      <c r="J2" s="63"/>
     </row>
     <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="61" t="s">
+      <c r="A3" s="62" t="s">
         <v>1016</v>
       </c>
-      <c r="B3" s="62"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="62"/>
-      <c r="I3" s="62"/>
-      <c r="J3" s="62"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="63"/>
+      <c r="I3" s="63"/>
+      <c r="J3" s="63"/>
     </row>
     <row r="5" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
@@ -17260,7 +17350,7 @@
         <v>Wake</v>
       </c>
       <c r="H6" s="55"/>
-      <c r="I6" s="64" t="s">
+      <c r="I6" s="59" t="s">
         <v>1643</v>
       </c>
       <c r="J6" s="10"/>
@@ -17289,7 +17379,7 @@
         <v>Sleep</v>
       </c>
       <c r="H7" s="55"/>
-      <c r="I7" s="64" t="s">
+      <c r="I7" s="59" t="s">
         <v>1644</v>
       </c>
       <c r="J7" s="10"/>
@@ -17318,7 +17408,7 @@
         <v>Dispel</v>
       </c>
       <c r="H8" s="55"/>
-      <c r="I8" s="64" t="s">
+      <c r="I8" s="59" t="s">
         <v>1645</v>
       </c>
       <c r="J8" s="10"/>
@@ -17347,7 +17437,7 @@
         <v>Conjure</v>
       </c>
       <c r="H9" s="55"/>
-      <c r="I9" s="64" t="s">
+      <c r="I9" s="59" t="s">
         <v>1646</v>
       </c>
       <c r="J9" s="10"/>
@@ -17376,7 +17466,7 @@
         <v>Soothe</v>
       </c>
       <c r="H10" s="55"/>
-      <c r="I10" s="64" t="s">
+      <c r="I10" s="59" t="s">
         <v>1647</v>
       </c>
       <c r="J10" s="10"/>
@@ -17405,7 +17495,7 @@
         <v>Dread</v>
       </c>
       <c r="H11" s="55"/>
-      <c r="I11" s="64" t="s">
+      <c r="I11" s="59" t="s">
         <v>1648</v>
       </c>
       <c r="J11" s="10"/>
@@ -17434,7 +17524,7 @@
         <v>Unmask</v>
       </c>
       <c r="H12" s="55"/>
-      <c r="I12" s="64" t="s">
+      <c r="I12" s="59" t="s">
         <v>1649</v>
       </c>
       <c r="J12" s="10"/>
@@ -17463,7 +17553,7 @@
         <v>Mimic</v>
       </c>
       <c r="H13" s="55"/>
-      <c r="I13" s="64" t="s">
+      <c r="I13" s="59" t="s">
         <v>1650</v>
       </c>
       <c r="J13" s="10"/>
@@ -17492,7 +17582,7 @@
         <v>Shut</v>
       </c>
       <c r="H14" s="55"/>
-      <c r="I14" s="64" t="s">
+      <c r="I14" s="59" t="s">
         <v>1651</v>
       </c>
       <c r="J14" s="10"/>
@@ -17521,7 +17611,7 @@
         <v>Whisper</v>
       </c>
       <c r="H15" s="55"/>
-      <c r="I15" s="64" t="s">
+      <c r="I15" s="59" t="s">
         <v>1652</v>
       </c>
       <c r="J15" s="10"/>
@@ -17564,32 +17654,32 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="63" t="s">
+      <c r="A2" s="64" t="s">
         <v>1023</v>
       </c>
-      <c r="B2" s="62"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
-      <c r="J2" s="62"/>
+      <c r="B2" s="63"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
+      <c r="J2" s="63"/>
     </row>
     <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="61" t="s">
+      <c r="A3" s="62" t="s">
         <v>1012</v>
       </c>
-      <c r="B3" s="62"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="62"/>
-      <c r="I3" s="62"/>
-      <c r="J3" s="62"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="63"/>
+      <c r="I3" s="63"/>
+      <c r="J3" s="63"/>
     </row>
     <row r="5" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
@@ -17647,7 +17737,7 @@
         <v>Purge</v>
       </c>
       <c r="H6" s="55"/>
-      <c r="I6" s="64" t="s">
+      <c r="I6" s="59" t="s">
         <v>1653</v>
       </c>
       <c r="J6" s="10"/>
@@ -17676,7 +17766,7 @@
         <v>Poison</v>
       </c>
       <c r="H7" s="55"/>
-      <c r="I7" s="64" t="s">
+      <c r="I7" s="59" t="s">
         <v>1654</v>
       </c>
       <c r="J7" s="10"/>
@@ -17705,7 +17795,7 @@
         <v>Cleanse</v>
       </c>
       <c r="H8" s="55"/>
-      <c r="I8" s="64" t="s">
+      <c r="I8" s="59" t="s">
         <v>1655</v>
       </c>
       <c r="J8" s="10"/>
@@ -17734,7 +17824,7 @@
         <v>Contaminate</v>
       </c>
       <c r="H9" s="55"/>
-      <c r="I9" s="64" t="s">
+      <c r="I9" s="59" t="s">
         <v>1656</v>
       </c>
       <c r="J9" s="10"/>
@@ -17763,7 +17853,7 @@
         <v>Neutralise</v>
       </c>
       <c r="H10" s="55"/>
-      <c r="I10" s="64" t="s">
+      <c r="I10" s="59" t="s">
         <v>1657</v>
       </c>
       <c r="J10" s="10"/>
@@ -17792,7 +17882,7 @@
         <v>Corrode</v>
       </c>
       <c r="H11" s="55"/>
-      <c r="I11" s="64" t="s">
+      <c r="I11" s="59" t="s">
         <v>1658</v>
       </c>
       <c r="J11" s="10"/>
@@ -17821,7 +17911,7 @@
         <v>Flush</v>
       </c>
       <c r="H12" s="55"/>
-      <c r="I12" s="64" t="s">
+      <c r="I12" s="59" t="s">
         <v>1659</v>
       </c>
       <c r="J12" s="10"/>
@@ -17850,7 +17940,7 @@
         <v>Linger</v>
       </c>
       <c r="H13" s="55"/>
-      <c r="I13" s="64" t="s">
+      <c r="I13" s="59" t="s">
         <v>1660</v>
       </c>
       <c r="J13" s="10"/>
@@ -17879,7 +17969,7 @@
         <v>Stimulate</v>
       </c>
       <c r="H14" s="55"/>
-      <c r="I14" s="64" t="s">
+      <c r="I14" s="59" t="s">
         <v>1661</v>
       </c>
       <c r="J14" s="10"/>
@@ -17908,7 +17998,7 @@
         <v>Sap</v>
       </c>
       <c r="H15" s="55"/>
-      <c r="I15" s="64" t="s">
+      <c r="I15" s="59" t="s">
         <v>1662</v>
       </c>
       <c r="J15" s="10"/>
@@ -17951,32 +18041,32 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="63" t="s">
+      <c r="A2" s="64" t="s">
         <v>1030</v>
       </c>
-      <c r="B2" s="62"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
-      <c r="J2" s="62"/>
+      <c r="B2" s="63"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
+      <c r="J2" s="63"/>
     </row>
     <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="61" t="s">
+      <c r="A3" s="62" t="s">
         <v>1031</v>
       </c>
-      <c r="B3" s="62"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="62"/>
-      <c r="I3" s="62"/>
-      <c r="J3" s="62"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="63"/>
+      <c r="I3" s="63"/>
+      <c r="J3" s="63"/>
     </row>
     <row r="5" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
@@ -18034,7 +18124,7 @@
         <v>Disinfect</v>
       </c>
       <c r="H6" s="55"/>
-      <c r="I6" s="64" t="s">
+      <c r="I6" s="59" t="s">
         <v>1663</v>
       </c>
       <c r="J6" s="10"/>
@@ -18063,7 +18153,7 @@
         <v>Infect</v>
       </c>
       <c r="H7" s="55"/>
-      <c r="I7" s="64" t="s">
+      <c r="I7" s="59" t="s">
         <v>1609</v>
       </c>
       <c r="J7" s="10"/>
@@ -18092,7 +18182,7 @@
         <v>Contain</v>
       </c>
       <c r="H8" s="55"/>
-      <c r="I8" s="64" t="s">
+      <c r="I8" s="59" t="s">
         <v>1664</v>
       </c>
       <c r="J8" s="10"/>
@@ -18121,7 +18211,7 @@
         <v>Spread</v>
       </c>
       <c r="H9" s="55"/>
-      <c r="I9" s="64" t="s">
+      <c r="I9" s="59" t="s">
         <v>1665</v>
       </c>
       <c r="J9" s="10"/>
@@ -18150,7 +18240,7 @@
         <v>Lance</v>
       </c>
       <c r="H10" s="55"/>
-      <c r="I10" s="64" t="s">
+      <c r="I10" s="59" t="s">
         <v>1666</v>
       </c>
       <c r="J10" s="10"/>
@@ -18179,7 +18269,7 @@
         <v>Fester</v>
       </c>
       <c r="H11" s="55"/>
-      <c r="I11" s="64" t="s">
+      <c r="I11" s="59" t="s">
         <v>1667</v>
       </c>
       <c r="J11" s="10"/>
@@ -18208,7 +18298,7 @@
         <v>Clear</v>
       </c>
       <c r="H12" s="55"/>
-      <c r="I12" s="64" t="s">
+      <c r="I12" s="59" t="s">
         <v>1668</v>
       </c>
       <c r="J12" s="10"/>
@@ -18237,7 +18327,7 @@
         <v>Billow</v>
       </c>
       <c r="H13" s="55"/>
-      <c r="I13" s="64" t="s">
+      <c r="I13" s="59" t="s">
         <v>1669</v>
       </c>
       <c r="J13" s="10"/>
@@ -18266,7 +18356,7 @@
         <v>Immunise</v>
       </c>
       <c r="H14" s="55"/>
-      <c r="I14" s="64" t="s">
+      <c r="I14" s="59" t="s">
         <v>1670</v>
       </c>
       <c r="J14" s="10"/>
@@ -18295,7 +18385,7 @@
         <v>Overrun</v>
       </c>
       <c r="H15" s="55"/>
-      <c r="I15" s="64" t="s">
+      <c r="I15" s="59" t="s">
         <v>1671</v>
       </c>
       <c r="J15" s="10"/>
@@ -30620,7 +30710,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{707B76BF-2512-40E2-935C-38AB239C315D}">
-  <dimension ref="A1:E40"/>
+  <dimension ref="A1:E59"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22.7109375" style="31" customWidth="1"/>
@@ -30730,13 +30820,13 @@
       </c>
     </row>
     <row r="10" spans="1:5" ht="54" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="59" t="s">
+      <c r="A10" s="60" t="s">
         <v>1081</v>
       </c>
-      <c r="B10" s="59"/>
-      <c r="C10" s="59"/>
-      <c r="D10" s="59"/>
-      <c r="E10" s="59"/>
+      <c r="B10" s="60"/>
+      <c r="C10" s="60"/>
+      <c r="D10" s="60"/>
+      <c r="E10" s="60"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="44" t="s">
@@ -30783,13 +30873,13 @@
       </c>
     </row>
     <row r="17" spans="1:5" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="60" t="s">
+      <c r="A17" s="61" t="s">
         <v>1091</v>
       </c>
-      <c r="B17" s="59"/>
-      <c r="C17" s="59"/>
-      <c r="D17" s="59"/>
-      <c r="E17" s="59"/>
+      <c r="B17" s="60"/>
+      <c r="C17" s="60"/>
+      <c r="D17" s="60"/>
+      <c r="E17" s="60"/>
     </row>
     <row r="19" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="58" t="s">
@@ -30797,13 +30887,13 @@
       </c>
     </row>
     <row r="20" spans="1:5" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="59" t="s">
+      <c r="A20" s="60" t="s">
         <v>1392</v>
       </c>
-      <c r="B20" s="59"/>
-      <c r="C20" s="59"/>
-      <c r="D20" s="59"/>
-      <c r="E20" s="59"/>
+      <c r="B20" s="60"/>
+      <c r="C20" s="60"/>
+      <c r="D20" s="60"/>
+      <c r="E20" s="60"/>
     </row>
     <row r="22" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A22" s="35" t="s">
@@ -30934,25 +31024,200 @@
       </c>
     </row>
     <row r="38" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="59" t="s">
+      <c r="A38" s="60" t="s">
         <v>1406</v>
       </c>
-      <c r="B38" s="59"/>
-      <c r="C38" s="59"/>
-      <c r="D38" s="59"/>
-      <c r="E38" s="59"/>
+      <c r="B38" s="60"/>
+      <c r="C38" s="60"/>
+      <c r="D38" s="60"/>
+      <c r="E38" s="60"/>
     </row>
     <row r="40" spans="1:5" ht="110.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="59" t="s">
+      <c r="A40" s="60" t="s">
         <v>1672</v>
       </c>
-      <c r="B40" s="59"/>
-      <c r="C40" s="59"/>
-      <c r="D40" s="59"/>
-      <c r="E40" s="59"/>
+      <c r="B40" s="60"/>
+      <c r="C40" s="60"/>
+      <c r="D40" s="60"/>
+      <c r="E40" s="60"/>
+    </row>
+    <row r="43" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A43" s="58" t="s">
+        <v>1674</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="56.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="60" t="s">
+        <v>1675</v>
+      </c>
+      <c r="B44" s="60"/>
+      <c r="C44" s="60"/>
+      <c r="D44" s="60"/>
+      <c r="E44" s="60"/>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A46" s="35" t="s">
+        <v>1676</v>
+      </c>
+      <c r="B46" s="35" t="s">
+        <v>766</v>
+      </c>
+      <c r="C46" s="35" t="s">
+        <v>1677</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A47" s="40" t="s">
+        <v>1678</v>
+      </c>
+      <c r="B47" s="33">
+        <v>1</v>
+      </c>
+      <c r="C47" s="33">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A48" s="40">
+        <v>2</v>
+      </c>
+      <c r="B48" s="33">
+        <v>0.6</v>
+      </c>
+      <c r="C48" s="33">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A49" s="40">
+        <v>3</v>
+      </c>
+      <c r="B49" s="33">
+        <v>0.4</v>
+      </c>
+      <c r="C49" s="33">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A50" s="40">
+        <v>4</v>
+      </c>
+      <c r="B50" s="33">
+        <v>0.25</v>
+      </c>
+      <c r="C50" s="33">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A51" s="40" t="s">
+        <v>1679</v>
+      </c>
+      <c r="B51" s="33">
+        <v>0.15</v>
+      </c>
+      <c r="C51" s="33">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" ht="63.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="60" t="s">
+        <v>1680</v>
+      </c>
+      <c r="B52" s="60"/>
+      <c r="C52" s="60"/>
+      <c r="D52" s="60"/>
+      <c r="E52" s="60"/>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A54" s="35" t="s">
+        <v>1681</v>
+      </c>
+      <c r="B54" s="35" t="s">
+        <v>1682</v>
+      </c>
+      <c r="C54" s="35" t="s">
+        <v>1683</v>
+      </c>
+      <c r="D54" s="35" t="s">
+        <v>1684</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A55" s="40" t="s">
+        <v>1685</v>
+      </c>
+      <c r="B55" s="40" t="s">
+        <v>1686</v>
+      </c>
+      <c r="C55" s="33" t="s">
+        <v>1687</v>
+      </c>
+      <c r="D55" s="40" t="s">
+        <v>1688</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A56" s="40" t="s">
+        <v>1689</v>
+      </c>
+      <c r="B56" s="40" t="s">
+        <v>1690</v>
+      </c>
+      <c r="C56" s="33" t="s">
+        <v>1691</v>
+      </c>
+      <c r="D56" s="40" t="s">
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" ht="51" x14ac:dyDescent="0.2">
+      <c r="A57" s="40" t="s">
+        <v>1693</v>
+      </c>
+      <c r="B57" s="40" t="s">
+        <v>1694</v>
+      </c>
+      <c r="C57" s="33" t="s">
+        <v>1695</v>
+      </c>
+      <c r="D57" s="40" t="s">
+        <v>1696</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A58" s="40" t="s">
+        <v>1074</v>
+      </c>
+      <c r="B58" s="40" t="s">
+        <v>1697</v>
+      </c>
+      <c r="C58" s="33" t="s">
+        <v>1698</v>
+      </c>
+      <c r="D58" s="40" t="s">
+        <v>1699</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A59" s="40" t="s">
+        <v>1700</v>
+      </c>
+      <c r="B59" s="40" t="s">
+        <v>1701</v>
+      </c>
+      <c r="C59" s="33" t="s">
+        <v>1702</v>
+      </c>
+      <c r="D59" s="40" t="s">
+        <v>1703</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="7">
+    <mergeCell ref="A44:E44"/>
+    <mergeCell ref="A52:E52"/>
     <mergeCell ref="A10:E10"/>
     <mergeCell ref="A17:E17"/>
     <mergeCell ref="A20:E20"/>
@@ -30987,32 +31252,32 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="63" t="s">
+      <c r="A2" s="64" t="s">
         <v>903</v>
       </c>
-      <c r="B2" s="62"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
-      <c r="J2" s="62"/>
+      <c r="B2" s="63"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
+      <c r="J2" s="63"/>
     </row>
     <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="61" t="s">
+      <c r="A3" s="62" t="s">
         <v>904</v>
       </c>
-      <c r="B3" s="62"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="62"/>
-      <c r="I3" s="62"/>
-      <c r="J3" s="62"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="63"/>
+      <c r="I3" s="63"/>
+      <c r="J3" s="63"/>
     </row>
     <row r="5" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
@@ -31072,7 +31337,7 @@
         <v>Drain</v>
       </c>
       <c r="H6" s="55"/>
-      <c r="I6" s="64" t="s">
+      <c r="I6" s="59" t="s">
         <v>917</v>
       </c>
       <c r="J6" s="10" t="s">
@@ -31105,7 +31370,7 @@
         <v>Flood</v>
       </c>
       <c r="H7" s="55"/>
-      <c r="I7" s="64" t="s">
+      <c r="I7" s="59" t="s">
         <v>1525</v>
       </c>
       <c r="J7" s="10"/>
@@ -31138,7 +31403,7 @@
       <c r="H8" s="10" t="s">
         <v>1173</v>
       </c>
-      <c r="I8" s="64" t="s">
+      <c r="I8" s="59" t="s">
         <v>912</v>
       </c>
       <c r="J8" s="10"/>
@@ -31171,7 +31436,7 @@
       <c r="H9" s="10" t="s">
         <v>1173</v>
       </c>
-      <c r="I9" s="64" t="s">
+      <c r="I9" s="59" t="s">
         <v>915</v>
       </c>
       <c r="J9" s="10"/>
@@ -31204,7 +31469,7 @@
       <c r="H10" s="10" t="s">
         <v>1174</v>
       </c>
-      <c r="I10" s="64" t="s">
+      <c r="I10" s="59" t="s">
         <v>1526</v>
       </c>
       <c r="J10" s="10"/>
@@ -31237,7 +31502,7 @@
       <c r="H11" s="10" t="s">
         <v>1174</v>
       </c>
-      <c r="I11" s="64" t="s">
+      <c r="I11" s="59" t="s">
         <v>1527</v>
       </c>
       <c r="J11" s="10" t="s">
@@ -31272,7 +31537,7 @@
       <c r="H12" s="10" t="s">
         <v>1178</v>
       </c>
-      <c r="I12" s="64" t="s">
+      <c r="I12" s="59" t="s">
         <v>1528</v>
       </c>
       <c r="J12" s="10"/>
@@ -31305,7 +31570,7 @@
       <c r="H13" s="10" t="s">
         <v>1178</v>
       </c>
-      <c r="I13" s="64" t="s">
+      <c r="I13" s="59" t="s">
         <v>1529</v>
       </c>
       <c r="J13" s="10" t="s">
@@ -31338,7 +31603,7 @@
         <v>Drip</v>
       </c>
       <c r="H14" s="55"/>
-      <c r="I14" s="64" t="s">
+      <c r="I14" s="59" t="s">
         <v>922</v>
       </c>
       <c r="J14" s="10"/>
@@ -31369,7 +31634,7 @@
         <v>Gush</v>
       </c>
       <c r="H15" s="55"/>
-      <c r="I15" s="64" t="s">
+      <c r="I15" s="59" t="s">
         <v>1530</v>
       </c>
       <c r="J15" s="10"/>
@@ -31400,7 +31665,7 @@
         <v>Settle</v>
       </c>
       <c r="H16" s="55"/>
-      <c r="I16" s="64" t="s">
+      <c r="I16" s="59" t="s">
         <v>916</v>
       </c>
       <c r="J16" s="10"/>
@@ -31431,7 +31696,7 @@
         <v>Sweep</v>
       </c>
       <c r="H17" s="55"/>
-      <c r="I17" s="64" t="s">
+      <c r="I17" s="59" t="s">
         <v>1531</v>
       </c>
       <c r="J17" s="10"/>
@@ -31462,7 +31727,7 @@
         <v>Seep</v>
       </c>
       <c r="H18" s="55"/>
-      <c r="I18" s="64" t="s">
+      <c r="I18" s="59" t="s">
         <v>924</v>
       </c>
       <c r="J18" s="10"/>
@@ -31493,7 +31758,7 @@
         <v>Splash</v>
       </c>
       <c r="H19" s="55"/>
-      <c r="I19" s="64" t="s">
+      <c r="I19" s="59" t="s">
         <v>1532</v>
       </c>
       <c r="J19" s="10"/>
@@ -31524,7 +31789,7 @@
         <v>Slack</v>
       </c>
       <c r="H20" s="55"/>
-      <c r="I20" s="64" t="s">
+      <c r="I20" s="59" t="s">
         <v>1533</v>
       </c>
       <c r="J20" s="10"/>
@@ -31555,7 +31820,7 @@
         <v>Wave</v>
       </c>
       <c r="H21" s="55"/>
-      <c r="I21" s="64" t="s">
+      <c r="I21" s="59" t="s">
         <v>1534</v>
       </c>
       <c r="J21" s="10"/>
@@ -31598,32 +31863,32 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="63" t="s">
+      <c r="A2" s="64" t="s">
         <v>927</v>
       </c>
-      <c r="B2" s="62"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
-      <c r="J2" s="62"/>
+      <c r="B2" s="63"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
+      <c r="J2" s="63"/>
     </row>
     <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="61" t="s">
+      <c r="A3" s="62" t="s">
         <v>928</v>
       </c>
-      <c r="B3" s="62"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="62"/>
-      <c r="I3" s="62"/>
-      <c r="J3" s="62"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="63"/>
+      <c r="I3" s="63"/>
+      <c r="J3" s="63"/>
     </row>
     <row r="5" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
@@ -31683,7 +31948,7 @@
         <v>Quench</v>
       </c>
       <c r="H6" s="55"/>
-      <c r="I6" s="64" t="s">
+      <c r="I6" s="59" t="s">
         <v>1535</v>
       </c>
       <c r="J6" s="10"/>
@@ -31714,7 +31979,7 @@
         <v>Burn</v>
       </c>
       <c r="H7" s="55"/>
-      <c r="I7" s="64" t="s">
+      <c r="I7" s="59" t="s">
         <v>1536</v>
       </c>
       <c r="J7" s="10"/>
@@ -31745,7 +32010,7 @@
         <v>Snuff</v>
       </c>
       <c r="H8" s="55"/>
-      <c r="I8" s="64" t="s">
+      <c r="I8" s="59" t="s">
         <v>1537</v>
       </c>
       <c r="J8" s="10"/>
@@ -31776,7 +32041,7 @@
         <v>Ignite</v>
       </c>
       <c r="H9" s="55"/>
-      <c r="I9" s="64" t="s">
+      <c r="I9" s="59" t="s">
         <v>1538</v>
       </c>
       <c r="J9" s="10"/>
@@ -31807,7 +32072,7 @@
         <v>Implode</v>
       </c>
       <c r="H10" s="55"/>
-      <c r="I10" s="64" t="s">
+      <c r="I10" s="59" t="s">
         <v>1193</v>
       </c>
       <c r="J10" s="10"/>
@@ -31838,7 +32103,7 @@
         <v>Explode</v>
       </c>
       <c r="H11" s="55"/>
-      <c r="I11" s="64" t="s">
+      <c r="I11" s="59" t="s">
         <v>931</v>
       </c>
       <c r="J11" s="10"/>
@@ -31869,7 +32134,7 @@
         <v>Smoulder</v>
       </c>
       <c r="H12" s="55"/>
-      <c r="I12" s="64" t="s">
+      <c r="I12" s="59" t="s">
         <v>1539</v>
       </c>
       <c r="J12" s="10"/>
@@ -31900,7 +32165,7 @@
         <v>Blaze</v>
       </c>
       <c r="H13" s="55"/>
-      <c r="I13" s="64" t="s">
+      <c r="I13" s="59" t="s">
         <v>1540</v>
       </c>
       <c r="J13" s="10"/>
@@ -31931,7 +32196,7 @@
         <v>Smother</v>
       </c>
       <c r="H14" s="55"/>
-      <c r="I14" s="64" t="s">
+      <c r="I14" s="59" t="s">
         <v>1541</v>
       </c>
       <c r="J14" s="10"/>
@@ -31962,7 +32227,7 @@
         <v>Flare</v>
       </c>
       <c r="H15" s="55"/>
-      <c r="I15" s="64" t="s">
+      <c r="I15" s="59" t="s">
         <v>1542</v>
       </c>
       <c r="J15" s="10"/>
@@ -32005,32 +32270,32 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="63" t="s">
+      <c r="A2" s="64" t="s">
         <v>932</v>
       </c>
-      <c r="B2" s="62"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
-      <c r="J2" s="62"/>
+      <c r="B2" s="63"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
+      <c r="J2" s="63"/>
     </row>
     <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="61" t="s">
+      <c r="A3" s="62" t="s">
         <v>928</v>
       </c>
-      <c r="B3" s="62"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="62"/>
-      <c r="I3" s="62"/>
-      <c r="J3" s="62"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="63"/>
+      <c r="I3" s="63"/>
+      <c r="J3" s="63"/>
     </row>
     <row r="5" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
@@ -32090,7 +32355,7 @@
         <v>Sink</v>
       </c>
       <c r="H6" s="55"/>
-      <c r="I6" s="64" t="s">
+      <c r="I6" s="59" t="s">
         <v>1543</v>
       </c>
       <c r="J6" s="10"/>
@@ -32121,7 +32386,7 @@
         <v>Raise</v>
       </c>
       <c r="H7" s="55"/>
-      <c r="I7" s="64" t="s">
+      <c r="I7" s="59" t="s">
         <v>1544</v>
       </c>
       <c r="J7" s="10"/>
@@ -32152,7 +32417,7 @@
         <v>Crumble</v>
       </c>
       <c r="H8" s="55"/>
-      <c r="I8" s="64" t="s">
+      <c r="I8" s="59" t="s">
         <v>936</v>
       </c>
       <c r="J8" s="10"/>
@@ -32183,7 +32448,7 @@
         <v>Harden</v>
       </c>
       <c r="H9" s="55"/>
-      <c r="I9" s="64" t="s">
+      <c r="I9" s="59" t="s">
         <v>1545</v>
       </c>
       <c r="J9" s="10"/>
@@ -32214,7 +32479,7 @@
         <v>Quake</v>
       </c>
       <c r="H10" s="55"/>
-      <c r="I10" s="64" t="s">
+      <c r="I10" s="59" t="s">
         <v>939</v>
       </c>
       <c r="J10" s="10"/>
@@ -32245,7 +32510,7 @@
         <v>Root</v>
       </c>
       <c r="H11" s="55"/>
-      <c r="I11" s="64" t="s">
+      <c r="I11" s="59" t="s">
         <v>941</v>
       </c>
       <c r="J11" s="10"/>
@@ -32276,7 +32541,7 @@
         <v>Bury</v>
       </c>
       <c r="H12" s="55"/>
-      <c r="I12" s="64" t="s">
+      <c r="I12" s="59" t="s">
         <v>1546</v>
       </c>
       <c r="J12" s="10"/>
@@ -32307,7 +32572,7 @@
         <v>Dig</v>
       </c>
       <c r="H13" s="55"/>
-      <c r="I13" s="64" t="s">
+      <c r="I13" s="59" t="s">
         <v>1547</v>
       </c>
       <c r="J13" s="10"/>
@@ -32338,7 +32603,7 @@
         <v>Collapse</v>
       </c>
       <c r="H14" s="55"/>
-      <c r="I14" s="64" t="s">
+      <c r="I14" s="59" t="s">
         <v>1548</v>
       </c>
       <c r="J14" s="10"/>
@@ -32369,7 +32634,7 @@
         <v>Tunnel</v>
       </c>
       <c r="H15" s="55"/>
-      <c r="I15" s="64" t="s">
+      <c r="I15" s="59" t="s">
         <v>1549</v>
       </c>
       <c r="J15" s="10"/>

--- a/design/runes-workbook.xlsx
+++ b/design/runes-workbook.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Code\lifesteal-crawler\design\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB45486B-5F9E-48CC-8F12-E9DA11BA250C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BD8F037-8EBA-4471-AF20-5E9B3D76011B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -332,7 +332,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2711" uniqueCount="1704">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2731" uniqueCount="1723">
   <si>
     <t>Passage rune workbook</t>
   </si>
@@ -5444,6 +5444,63 @@
   </si>
   <si>
     <t>the skill stays itself</t>
+  </si>
+  <si>
+    <t>Strength on on/off effects, and ionic conversion (Brent 2026-10-23; first-pass numbers)</t>
+  </si>
+  <si>
+    <t>Dominance must pay: an on/off effect (a status, an interrupt) also grows with strength, and in an ionic bond nothing is lost - what the weaker side gives up is converted into the stronger rune's strength.</t>
+  </si>
+  <si>
+    <t>Knob</t>
+  </si>
+  <si>
+    <t>What it does</t>
+  </si>
+  <si>
+    <t>Status duration per strength</t>
+  </si>
+  <si>
+    <t>a status lasts base x strength (above 1 it lasts longer)</t>
+  </si>
+  <si>
+    <t>Status duration cap</t>
+  </si>
+  <si>
+    <t>longest a status can be stretched, as a multiple of its base</t>
+  </si>
+  <si>
+    <t>Extra stack per strength above 1</t>
+  </si>
+  <si>
+    <t>each full 1.0 of strength above 1 adds a stack (where the status stacks)</t>
+  </si>
+  <si>
+    <t>Interrupt becomes silence above strength</t>
+  </si>
+  <si>
+    <t>an interrupt at higher strength also stops casting</t>
+  </si>
+  <si>
+    <t>Silence seconds per strength above 1</t>
+  </si>
+  <si>
+    <t>how long the silence lasts per 1.0 of strength above the line</t>
+  </si>
+  <si>
+    <t>Ionic conversion rate</t>
+  </si>
+  <si>
+    <t>share of what the weaker side gives up that is added to the stronger rune's strength</t>
+  </si>
+  <si>
+    <t>Converted strength cap</t>
+  </si>
+  <si>
+    <t>the most strength a rune can reach by conversion</t>
+  </si>
+  <si>
+    <t>Example: Drown takes Wave (ionic) on Tidal Bore. Wave gives up all of its nature (reach, stagger, carry), so Drown's strength goes 1.5 -&gt; 2.5: its interrupt becomes a 2.25 s silence and Dazed lasts 2.5x as long.</t>
   </si>
 </sst>
 </file>
@@ -30710,7 +30767,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{707B76BF-2512-40E2-935C-38AB239C315D}">
-  <dimension ref="A1:E59"/>
+  <dimension ref="A1:E74"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22.7109375" style="31" customWidth="1"/>
@@ -31214,8 +31271,121 @@
         <v>1703</v>
       </c>
     </row>
+    <row r="62" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A62" s="58" t="s">
+        <v>1704</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="60" t="s">
+        <v>1705</v>
+      </c>
+      <c r="B63" s="60"/>
+      <c r="C63" s="60"/>
+      <c r="D63" s="60"/>
+      <c r="E63" s="60"/>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A65" s="35" t="s">
+        <v>1706</v>
+      </c>
+      <c r="B65" s="35" t="s">
+        <v>1048</v>
+      </c>
+      <c r="C65" s="35" t="s">
+        <v>1707</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A66" s="40" t="s">
+        <v>1708</v>
+      </c>
+      <c r="B66" s="33">
+        <v>1</v>
+      </c>
+      <c r="C66" s="40" t="s">
+        <v>1709</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A67" s="40" t="s">
+        <v>1710</v>
+      </c>
+      <c r="B67" s="33">
+        <v>2.5</v>
+      </c>
+      <c r="C67" s="40" t="s">
+        <v>1711</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A68" s="40" t="s">
+        <v>1712</v>
+      </c>
+      <c r="B68" s="33">
+        <v>1</v>
+      </c>
+      <c r="C68" s="40" t="s">
+        <v>1713</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A69" s="40" t="s">
+        <v>1714</v>
+      </c>
+      <c r="B69" s="33">
+        <v>1</v>
+      </c>
+      <c r="C69" s="40" t="s">
+        <v>1715</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A70" s="40" t="s">
+        <v>1716</v>
+      </c>
+      <c r="B70" s="33">
+        <v>1.5</v>
+      </c>
+      <c r="C70" s="40" t="s">
+        <v>1717</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" ht="51" x14ac:dyDescent="0.2">
+      <c r="A71" s="40" t="s">
+        <v>1718</v>
+      </c>
+      <c r="B71" s="33">
+        <v>1</v>
+      </c>
+      <c r="C71" s="40" t="s">
+        <v>1719</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A72" s="40" t="s">
+        <v>1720</v>
+      </c>
+      <c r="B72" s="33">
+        <v>3</v>
+      </c>
+      <c r="C72" s="40" t="s">
+        <v>1721</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A74" s="60" t="s">
+        <v>1722</v>
+      </c>
+      <c r="B74" s="60"/>
+      <c r="C74" s="60"/>
+      <c r="D74" s="60"/>
+      <c r="E74" s="60"/>
+    </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="9">
+    <mergeCell ref="A63:E63"/>
+    <mergeCell ref="A74:E74"/>
     <mergeCell ref="A44:E44"/>
     <mergeCell ref="A52:E52"/>
     <mergeCell ref="A10:E10"/>
